--- a/input/11_Avoided_Cost.xlsx
+++ b/input/11_Avoided_Cost.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29421"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="273" documentId="11_D6D74F8E03DABB52AC860ED093673A573CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19B42D8E-609A-43A6-B8E3-0ED1849F8508}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/market_inputs/input/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="274" documentId="11_D6D74F8E03DABB52AC860ED093673A573CED4083" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FFCB218-A51F-4E6F-AB68-93DDED54BB38}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Input (AC)" sheetId="4" r:id="rId1"/>
@@ -949,7 +954,7 @@
   <numFmts count="1">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1450,34 +1455,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1486,18 +1472,37 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1834,15 +1839,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4132D354-D3C7-4660-A75F-9010AC3D8AE5}">
   <dimension ref="A1:BW51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="12" max="12" width="12.140625" customWidth="1"/>
     <col min="30" max="30" width="42.5703125" customWidth="1"/>
     <col min="46" max="46" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="20" customWidth="1"/>
     <col min="75" max="75" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:75">
+    <row r="1" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -2069,7 +2075,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" spans="1:75">
+    <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2247,27 +2253,27 @@
         <f>GHG!AJ25</f>
         <v>20.08863036</v>
       </c>
-      <c r="AT2" s="94">
+      <c r="AT2" s="82">
         <f>GHG!B89</f>
         <v>1.4870000000000001E-4</v>
       </c>
-      <c r="AU2" s="94">
+      <c r="AU2" s="82">
         <f>GHG!C89</f>
         <v>1.5770000000000001E-4</v>
       </c>
-      <c r="AV2" s="94">
+      <c r="AV2" s="82">
         <f>GHG!D89</f>
         <v>1.9340000000000001E-4</v>
       </c>
-      <c r="AW2" s="94">
+      <c r="AW2" s="82">
         <f>GHG!E89</f>
         <v>1.9909999999999999E-4</v>
       </c>
-      <c r="AX2" s="94">
+      <c r="AX2" s="82">
         <f>GHG!F89</f>
         <v>9.0350000000000001E-5</v>
       </c>
-      <c r="AY2" s="94">
+      <c r="AY2" s="82">
         <f>GHG!G89</f>
         <v>9.0350000000000001E-5</v>
       </c>
@@ -2368,7 +2374,7 @@
         <v>8.0634279999999992E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:75">
+    <row r="3" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2546,27 +2552,27 @@
         <f>GHG!AJ26</f>
         <v>20.46237232</v>
       </c>
-      <c r="AT3" s="94">
+      <c r="AT3" s="82">
         <f>GHG!B90</f>
         <v>1.6281499999999999E-4</v>
       </c>
-      <c r="AU3" s="94">
+      <c r="AU3" s="82">
         <f>GHG!C90</f>
         <v>1.74535E-4</v>
       </c>
-      <c r="AV3" s="94">
+      <c r="AV3" s="82">
         <f>GHG!D90</f>
         <v>2.08679E-4</v>
       </c>
-      <c r="AW3" s="94">
+      <c r="AW3" s="82">
         <f>GHG!E90</f>
         <v>2.1098199999999999E-4</v>
       </c>
-      <c r="AX3" s="94">
+      <c r="AX3" s="82">
         <f>GHG!F90</f>
         <v>9.7139500000000001E-5</v>
       </c>
-      <c r="AY3" s="94">
+      <c r="AY3" s="82">
         <f>GHG!G90</f>
         <v>9.7139500000000001E-5</v>
       </c>
@@ -2667,7 +2673,7 @@
         <v>8.3512699999999992E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:75">
+    <row r="4" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2845,27 +2851,27 @@
         <f>GHG!AJ27</f>
         <v>20.83611428</v>
       </c>
-      <c r="AT4" s="94">
+      <c r="AT4" s="82">
         <f>GHG!B91</f>
         <v>1.77331E-4</v>
       </c>
-      <c r="AU4" s="94">
+      <c r="AU4" s="82">
         <f>GHG!C91</f>
         <v>1.9188399999999999E-4</v>
       </c>
-      <c r="AV4" s="94">
+      <c r="AV4" s="82">
         <f>GHG!D91</f>
         <v>2.2436099999999999E-4</v>
       </c>
-      <c r="AW4" s="94">
+      <c r="AW4" s="82">
         <f>GHG!E91</f>
         <v>2.2318199999999999E-4</v>
       </c>
-      <c r="AX4" s="94">
+      <c r="AX4" s="82">
         <f>GHG!F91</f>
         <v>1.0412900000000001E-4</v>
       </c>
-      <c r="AY4" s="94">
+      <c r="AY4" s="82">
         <f>GHG!G91</f>
         <v>1.0412900000000001E-4</v>
       </c>
@@ -2966,7 +2972,7 @@
         <v>8.6429509999999994E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:75">
+    <row r="5" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3144,27 +3150,27 @@
         <f>GHG!AJ28</f>
         <v>21.11642075</v>
       </c>
-      <c r="AT5" s="94">
+      <c r="AT5" s="82">
         <f>GHG!B92</f>
         <v>1.92277E-4</v>
       </c>
-      <c r="AU5" s="94">
+      <c r="AU5" s="82">
         <f>GHG!C92</f>
         <v>2.0976299999999999E-4</v>
       </c>
-      <c r="AV5" s="94">
+      <c r="AV5" s="82">
         <f>GHG!D92</f>
         <v>2.4048400000000001E-4</v>
       </c>
-      <c r="AW5" s="94">
+      <c r="AW5" s="82">
         <f>GHG!E92</f>
         <v>2.35689E-4</v>
       </c>
-      <c r="AX5" s="94">
+      <c r="AX5" s="82">
         <f>GHG!F92</f>
         <v>1.1131199999999999E-4</v>
       </c>
-      <c r="AY5" s="94">
+      <c r="AY5" s="82">
         <f>GHG!G92</f>
         <v>1.1131199999999999E-4</v>
       </c>
@@ -3265,7 +3271,7 @@
         <v>8.9307929999999994E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:75">
+    <row r="6" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3443,27 +3449,27 @@
         <f>GHG!AJ29</f>
         <v>21.49016271</v>
       </c>
-      <c r="AT6" s="94">
+      <c r="AT6" s="82">
         <f>GHG!B93</f>
         <v>2.0766200000000001E-4</v>
       </c>
-      <c r="AU6" s="94">
+      <c r="AU6" s="82">
         <f>GHG!C93</f>
         <v>2.2818E-4</v>
       </c>
-      <c r="AV6" s="94">
+      <c r="AV6" s="82">
         <f>GHG!D93</f>
         <v>2.5705500000000001E-4</v>
       </c>
-      <c r="AW6" s="94">
+      <c r="AW6" s="82">
         <f>GHG!E93</f>
         <v>2.4850799999999999E-4</v>
       </c>
-      <c r="AX6" s="94">
+      <c r="AX6" s="82">
         <f>GHG!F93</f>
         <v>1.1869199999999999E-4</v>
       </c>
-      <c r="AY6" s="94">
+      <c r="AY6" s="82">
         <f>GHG!G93</f>
         <v>1.1869199999999999E-4</v>
       </c>
@@ -3564,7 +3570,7 @@
         <v>9.2224739999999996E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:75">
+    <row r="7" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3742,27 +3748,27 @@
         <f>GHG!AJ30</f>
         <v>21.86390467</v>
       </c>
-      <c r="AT7" s="94">
+      <c r="AT7" s="82">
         <f>GHG!B94</f>
         <v>1.7613500000000001E-4</v>
       </c>
-      <c r="AU7" s="94">
+      <c r="AU7" s="82">
         <f>GHG!C94</f>
         <v>1.9337600000000001E-4</v>
       </c>
-      <c r="AV7" s="94">
+      <c r="AV7" s="82">
         <f>GHG!D94</f>
         <v>2.1795699999999999E-4</v>
       </c>
-      <c r="AW7" s="94">
+      <c r="AW7" s="82">
         <f>GHG!E94</f>
         <v>2.1005399999999999E-4</v>
       </c>
-      <c r="AX7" s="94">
+      <c r="AX7" s="82">
         <f>GHG!F94</f>
         <v>9.9674199999999995E-5</v>
       </c>
-      <c r="AY7" s="94">
+      <c r="AY7" s="82">
         <f>GHG!G94</f>
         <v>9.9674199999999995E-5</v>
       </c>
@@ -3863,7 +3869,7 @@
         <v>9.5563709999999993E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:75">
+    <row r="8" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4041,27 +4047,27 @@
         <f>GHG!AJ31</f>
         <v>22.144211139999999</v>
       </c>
-      <c r="AT8" s="94">
+      <c r="AT8" s="82">
         <f>GHG!B95</f>
         <v>1.4329800000000001E-4</v>
       </c>
-      <c r="AU8" s="94">
+      <c r="AU8" s="82">
         <f>GHG!C95</f>
         <v>1.57128E-4</v>
       </c>
-      <c r="AV8" s="94">
+      <c r="AV8" s="82">
         <f>GHG!D95</f>
         <v>1.7723500000000001E-4</v>
       </c>
-      <c r="AW8" s="94">
+      <c r="AW8" s="82">
         <f>GHG!E95</f>
         <v>1.70006E-4</v>
       </c>
-      <c r="AX8" s="94">
+      <c r="AX8" s="82">
         <f>GHG!F95</f>
         <v>7.9871399999999996E-5</v>
       </c>
-      <c r="AY8" s="94">
+      <c r="AY8" s="82">
         <f>GHG!G95</f>
         <v>7.9871399999999996E-5</v>
       </c>
@@ -4162,7 +4168,7 @@
         <v>9.8941059999999997E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:75">
+    <row r="9" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4340,27 +4346,27 @@
         <f>GHG!AJ32</f>
         <v>22.5179531</v>
       </c>
-      <c r="AT9" s="94">
+      <c r="AT9" s="82">
         <f>GHG!B96</f>
         <v>1.09151E-4</v>
       </c>
-      <c r="AU9" s="94">
+      <c r="AU9" s="82">
         <f>GHG!C96</f>
         <v>1.19434E-4</v>
       </c>
-      <c r="AV9" s="94">
+      <c r="AV9" s="82">
         <f>GHG!D96</f>
         <v>1.34888E-4</v>
       </c>
-      <c r="AW9" s="94">
+      <c r="AW9" s="82">
         <f>GHG!E96</f>
         <v>1.2836299999999999E-4</v>
       </c>
-      <c r="AX9" s="94">
+      <c r="AX9" s="82">
         <f>GHG!F96</f>
         <v>5.9283200000000002E-5</v>
       </c>
-      <c r="AY9" s="94">
+      <c r="AY9" s="82">
         <f>GHG!G96</f>
         <v>5.9283200000000002E-5</v>
       </c>
@@ -4461,7 +4467,7 @@
         <v>1.0231841E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:75">
+    <row r="10" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4639,27 +4645,27 @@
         <f>GHG!AJ33</f>
         <v>22.89169506</v>
       </c>
-      <c r="AT10" s="94">
+      <c r="AT10" s="82">
         <f>GHG!B97</f>
         <v>7.3694400000000004E-5</v>
       </c>
-      <c r="AU10" s="94">
+      <c r="AU10" s="82">
         <f>GHG!C97</f>
         <v>8.0294499999999995E-5</v>
       </c>
-      <c r="AV10" s="94">
+      <c r="AV10" s="82">
         <f>GHG!D97</f>
         <v>9.0917199999999997E-5</v>
       </c>
-      <c r="AW10" s="94">
+      <c r="AW10" s="82">
         <f>GHG!E97</f>
         <v>8.5125900000000004E-5</v>
       </c>
-      <c r="AX10" s="94">
+      <c r="AX10" s="82">
         <f>GHG!F97</f>
         <v>3.7908999999999999E-5</v>
       </c>
-      <c r="AY10" s="94">
+      <c r="AY10" s="82">
         <f>GHG!G97</f>
         <v>3.7908999999999999E-5</v>
       </c>
@@ -4760,7 +4766,7 @@
         <v>1.0569577E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:75">
+    <row r="11" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4938,27 +4944,27 @@
         <f>GHG!AJ34</f>
         <v>23.172001529999999</v>
       </c>
-      <c r="AT11" s="94">
+      <c r="AT11" s="82">
         <f>GHG!B98</f>
         <v>3.6929299999999999E-5</v>
       </c>
-      <c r="AU11" s="94">
+      <c r="AU11" s="82">
         <f>GHG!C98</f>
         <v>3.9711600000000001E-5</v>
       </c>
-      <c r="AV11" s="94">
+      <c r="AV11" s="82">
         <f>GHG!D98</f>
         <v>4.5324000000000002E-5</v>
       </c>
-      <c r="AW11" s="94">
+      <c r="AW11" s="82">
         <f>GHG!E98</f>
         <v>4.0296200000000002E-5</v>
       </c>
-      <c r="AX11" s="94">
+      <c r="AX11" s="82">
         <f>GHG!F98</f>
         <v>1.57502E-5</v>
       </c>
-      <c r="AY11" s="94">
+      <c r="AY11" s="82">
         <f>GHG!G98</f>
         <v>1.57502E-5</v>
       </c>
@@ -5059,7 +5065,7 @@
         <v>1.0907312000000001E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:75">
+    <row r="12" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5237,27 +5243,27 @@
         <f>GHG!AJ35</f>
         <v>23.54574349</v>
       </c>
-      <c r="AT12" s="94">
+      <c r="AT12" s="82">
         <f>GHG!B99</f>
         <v>3.4757700000000001E-5</v>
       </c>
-      <c r="AU12" s="94">
+      <c r="AU12" s="82">
         <f>GHG!C99</f>
         <v>3.6894999999999998E-5</v>
       </c>
-      <c r="AV12" s="94">
+      <c r="AV12" s="82">
         <f>GHG!D99</f>
         <v>4.1325600000000003E-5</v>
       </c>
-      <c r="AW12" s="94">
+      <c r="AW12" s="82">
         <f>GHG!E99</f>
         <v>3.6943999999999997E-5</v>
       </c>
-      <c r="AX12" s="94">
+      <c r="AX12" s="82">
         <f>GHG!F99</f>
         <v>1.4959200000000001E-5</v>
       </c>
-      <c r="AY12" s="94">
+      <c r="AY12" s="82">
         <f>GHG!G99</f>
         <v>1.4959200000000001E-5</v>
       </c>
@@ -5358,7 +5364,7 @@
         <v>1.1241209E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:75">
+    <row r="13" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5536,27 +5542,27 @@
         <f>GHG!AJ36</f>
         <v>23.91948545</v>
       </c>
-      <c r="AT13" s="94">
+      <c r="AT13" s="82">
         <f>GHG!B100</f>
         <v>3.2491099999999998E-5</v>
       </c>
-      <c r="AU13" s="94">
+      <c r="AU13" s="82">
         <f>GHG!C100</f>
         <v>3.39599E-5</v>
       </c>
-      <c r="AV13" s="94">
+      <c r="AV13" s="82">
         <f>GHG!D100</f>
         <v>3.7165500000000002E-5</v>
       </c>
-      <c r="AW13" s="94">
+      <c r="AW13" s="82">
         <f>GHG!E100</f>
         <v>3.3454999999999997E-5</v>
       </c>
-      <c r="AX13" s="94">
+      <c r="AX13" s="82">
         <f>GHG!F100</f>
         <v>1.41322E-5</v>
       </c>
-      <c r="AY13" s="94">
+      <c r="AY13" s="82">
         <f>GHG!G100</f>
         <v>1.41322E-5</v>
       </c>
@@ -5657,7 +5663,7 @@
         <v>1.1578944000000001E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:75">
+    <row r="14" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5835,27 +5841,27 @@
         <f>GHG!AJ37</f>
         <v>24.199791919999999</v>
       </c>
-      <c r="AT14" s="94">
+      <c r="AT14" s="82">
         <f>GHG!B101</f>
         <v>3.01296E-5</v>
       </c>
-      <c r="AU14" s="94">
+      <c r="AU14" s="82">
         <f>GHG!C101</f>
         <v>3.09065E-5</v>
       </c>
-      <c r="AV14" s="94">
+      <c r="AV14" s="82">
         <f>GHG!D101</f>
         <v>3.2843799999999999E-5</v>
       </c>
-      <c r="AW14" s="94">
+      <c r="AW14" s="82">
         <f>GHG!E101</f>
         <v>2.9829099999999999E-5</v>
       </c>
-      <c r="AX14" s="94">
+      <c r="AX14" s="82">
         <f>GHG!F101</f>
         <v>1.32692E-5</v>
       </c>
-      <c r="AY14" s="94">
+      <c r="AY14" s="82">
         <f>GHG!G101</f>
         <v>1.32692E-5</v>
       </c>
@@ -5956,7 +5962,7 @@
         <v>1.1916680000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:75">
+    <row r="15" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -6134,27 +6140,27 @@
         <f>GHG!AJ38</f>
         <v>24.573533879999999</v>
       </c>
-      <c r="AT15" s="94">
+      <c r="AT15" s="82">
         <f>GHG!B102</f>
         <v>2.7673000000000001E-5</v>
       </c>
-      <c r="AU15" s="94">
+      <c r="AU15" s="82">
         <f>GHG!C102</f>
         <v>2.77346E-5</v>
       </c>
-      <c r="AV15" s="94">
+      <c r="AV15" s="82">
         <f>GHG!D102</f>
         <v>2.83604E-5</v>
       </c>
-      <c r="AW15" s="94">
+      <c r="AW15" s="82">
         <f>GHG!E102</f>
         <v>2.6066399999999998E-5</v>
       </c>
-      <c r="AX15" s="94">
+      <c r="AX15" s="82">
         <f>GHG!F102</f>
         <v>1.2370300000000001E-5</v>
       </c>
-      <c r="AY15" s="94">
+      <c r="AY15" s="82">
         <f>GHG!G102</f>
         <v>1.2370300000000001E-5</v>
       </c>
@@ -6255,7 +6261,7 @@
         <v>1.2254414999999999E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:75">
+    <row r="16" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -6433,27 +6439,27 @@
         <f>GHG!AJ39</f>
         <v>24.94727584</v>
       </c>
-      <c r="AT16" s="94">
+      <c r="AT16" s="82">
         <f>GHG!B103</f>
         <v>2.51216E-5</v>
       </c>
-      <c r="AU16" s="94">
+      <c r="AU16" s="82">
         <f>GHG!C103</f>
         <v>2.4444399999999999E-5</v>
       </c>
-      <c r="AV16" s="94">
+      <c r="AV16" s="82">
         <f>GHG!D103</f>
         <v>2.37154E-5</v>
       </c>
-      <c r="AW16" s="94">
+      <c r="AW16" s="82">
         <f>GHG!E103</f>
         <v>2.2166799999999999E-5</v>
       </c>
-      <c r="AX16" s="94">
+      <c r="AX16" s="82">
         <f>GHG!F103</f>
         <v>1.1435499999999999E-5</v>
       </c>
-      <c r="AY16" s="94">
+      <c r="AY16" s="82">
         <f>GHG!G103</f>
         <v>1.1435499999999999E-5</v>
       </c>
@@ -6554,7 +6560,7 @@
         <v>1.2588312000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:75">
+    <row r="17" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -6732,27 +6738,27 @@
         <f>GHG!AJ40</f>
         <v>25.3210178</v>
       </c>
-      <c r="AT17" s="94">
+      <c r="AT17" s="82">
         <f>GHG!B104</f>
         <v>2.4383700000000002E-5</v>
       </c>
-      <c r="AU17" s="94">
+      <c r="AU17" s="82">
         <f>GHG!C104</f>
         <v>2.3556700000000001E-5</v>
       </c>
-      <c r="AV17" s="94">
+      <c r="AV17" s="82">
         <f>GHG!D104</f>
         <v>2.40706E-5</v>
       </c>
-      <c r="AW17" s="94">
+      <c r="AW17" s="82">
         <f>GHG!E104</f>
         <v>2.2178E-5</v>
       </c>
-      <c r="AX17" s="94">
+      <c r="AX17" s="82">
         <f>GHG!F104</f>
         <v>1.10157E-5</v>
       </c>
-      <c r="AY17" s="94">
+      <c r="AY17" s="82">
         <f>GHG!G104</f>
         <v>1.10157E-5</v>
       </c>
@@ -6853,7 +6859,7 @@
         <v>1.2952913E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:75">
+    <row r="18" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -7031,27 +7037,27 @@
         <f>GHG!AJ41</f>
         <v>25.69475976</v>
       </c>
-      <c r="AT18" s="94">
+      <c r="AT18" s="82">
         <f>GHG!B105</f>
         <v>2.36042E-5</v>
       </c>
-      <c r="AU18" s="94">
+      <c r="AU18" s="82">
         <f>GHG!C105</f>
         <v>2.2622599999999999E-5</v>
       </c>
-      <c r="AV18" s="94">
+      <c r="AV18" s="82">
         <f>GHG!D105</f>
         <v>2.4423400000000001E-5</v>
       </c>
-      <c r="AW18" s="94">
+      <c r="AW18" s="82">
         <f>GHG!E105</f>
         <v>2.2175699999999998E-5</v>
       </c>
-      <c r="AX18" s="94">
+      <c r="AX18" s="82">
         <f>GHG!F105</f>
         <v>1.0574000000000001E-5</v>
       </c>
-      <c r="AY18" s="94">
+      <c r="AY18" s="82">
         <f>GHG!G105</f>
         <v>1.0574000000000001E-5</v>
       </c>
@@ -7152,7 +7158,7 @@
         <v>1.3321351E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:75">
+    <row r="19" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -7330,27 +7336,27 @@
         <f>GHG!AJ42</f>
         <v>26.06850172</v>
       </c>
-      <c r="AT19" s="94">
+      <c r="AT19" s="82">
         <f>GHG!B106</f>
         <v>2.2807600000000002E-5</v>
       </c>
-      <c r="AU19" s="94">
+      <c r="AU19" s="82">
         <f>GHG!C106</f>
         <v>2.1665300000000001E-5</v>
       </c>
-      <c r="AV19" s="94">
+      <c r="AV19" s="82">
         <f>GHG!D106</f>
         <v>2.4800600000000001E-5</v>
       </c>
-      <c r="AW19" s="94">
+      <c r="AW19" s="82">
         <f>GHG!E106</f>
         <v>2.2183899999999999E-5</v>
       </c>
-      <c r="AX19" s="94">
+      <c r="AX19" s="82">
         <f>GHG!F106</f>
         <v>1.0121200000000001E-5</v>
       </c>
-      <c r="AY19" s="94">
+      <c r="AY19" s="82">
         <f>GHG!G106</f>
         <v>1.0121200000000001E-5</v>
       </c>
@@ -7451,7 +7457,7 @@
         <v>1.3685951E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:75">
+    <row r="20" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -7629,27 +7635,27 @@
         <f>GHG!AJ43</f>
         <v>26.442243680000001</v>
       </c>
-      <c r="AT20" s="94">
+      <c r="AT20" s="82">
         <f>GHG!B107</f>
         <v>2.1920300000000001E-5</v>
       </c>
-      <c r="AU20" s="94">
+      <c r="AU20" s="82">
         <f>GHG!C107</f>
         <v>2.0614900000000001E-5</v>
       </c>
-      <c r="AV20" s="94">
+      <c r="AV20" s="82">
         <f>GHG!D107</f>
         <v>2.5122000000000001E-5</v>
       </c>
-      <c r="AW20" s="94">
+      <c r="AW20" s="82">
         <f>GHG!E107</f>
         <v>2.2130800000000002E-5</v>
       </c>
-      <c r="AX20" s="94">
+      <c r="AX20" s="82">
         <f>GHG!F107</f>
         <v>9.6248199999999994E-6</v>
       </c>
-      <c r="AY20" s="94">
+      <c r="AY20" s="82">
         <f>GHG!G107</f>
         <v>9.6248199999999994E-6</v>
       </c>
@@ -7750,7 +7756,7 @@
         <v>1.4050551999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:75">
+    <row r="21" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -7928,27 +7934,27 @@
         <f>GHG!AJ44</f>
         <v>26.815985640000001</v>
       </c>
-      <c r="AT21" s="94">
+      <c r="AT21" s="82">
         <f>GHG!B108</f>
         <v>2.1015699999999999E-5</v>
       </c>
-      <c r="AU21" s="94">
+      <c r="AU21" s="82">
         <f>GHG!C108</f>
         <v>1.9541199999999999E-5</v>
       </c>
-      <c r="AV21" s="94">
+      <c r="AV21" s="82">
         <f>GHG!D108</f>
         <v>2.54676E-5</v>
       </c>
-      <c r="AW21" s="94">
+      <c r="AW21" s="82">
         <f>GHG!E108</f>
         <v>2.2087899999999999E-5</v>
       </c>
-      <c r="AX21" s="94">
+      <c r="AX21" s="82">
         <f>GHG!F108</f>
         <v>9.1172999999999999E-6</v>
       </c>
-      <c r="AY21" s="94">
+      <c r="AY21" s="82">
         <f>GHG!G108</f>
         <v>9.1172999999999999E-6</v>
       </c>
@@ -8049,7 +8055,7 @@
         <v>1.4415152000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:75">
+    <row r="22" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8227,27 +8233,27 @@
         <f>GHG!AJ45</f>
         <v>27.189727600000001</v>
       </c>
-      <c r="AT22" s="94">
+      <c r="AT22" s="82">
         <f>GHG!B109</f>
         <v>2.04922E-5</v>
       </c>
-      <c r="AU22" s="94">
+      <c r="AU22" s="82">
         <f>GHG!C109</f>
         <v>1.9177999999999998E-5</v>
       </c>
-      <c r="AV22" s="94">
+      <c r="AV22" s="82">
         <f>GHG!D109</f>
         <v>2.5058E-5</v>
       </c>
-      <c r="AW22" s="94">
+      <c r="AW22" s="82">
         <f>GHG!E109</f>
         <v>2.1879299999999999E-5</v>
       </c>
-      <c r="AX22" s="94">
+      <c r="AX22" s="82">
         <f>GHG!F109</f>
         <v>9.1438000000000004E-6</v>
       </c>
-      <c r="AY22" s="94">
+      <c r="AY22" s="82">
         <f>GHG!G109</f>
         <v>9.1438000000000004E-6</v>
       </c>
@@ -8348,7 +8354,7 @@
         <v>1.4779753E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:75">
+    <row r="23" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8526,27 +8532,27 @@
         <f>GHG!AJ46</f>
         <v>27.656905049999999</v>
       </c>
-      <c r="AT23" s="94">
+      <c r="AT23" s="82">
         <f>GHG!B110</f>
         <v>1.99406E-5</v>
       </c>
-      <c r="AU23" s="94">
+      <c r="AU23" s="82">
         <f>GHG!C110</f>
         <v>1.8792700000000001E-5</v>
       </c>
-      <c r="AV23" s="94">
+      <c r="AV23" s="82">
         <f>GHG!D110</f>
         <v>2.4621699999999998E-5</v>
       </c>
-      <c r="AW23" s="94">
+      <c r="AW23" s="82">
         <f>GHG!E110</f>
         <v>2.1652299999999999E-5</v>
       </c>
-      <c r="AX23" s="94">
+      <c r="AX23" s="82">
         <f>GHG!F110</f>
         <v>9.1663299999999994E-6</v>
       </c>
-      <c r="AY23" s="94">
+      <c r="AY23" s="82">
         <f>GHG!G110</f>
         <v>9.1663299999999994E-6</v>
       </c>
@@ -8647,7 +8653,7 @@
         <v>1.5144352999999999E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:75">
+    <row r="24" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8825,27 +8831,27 @@
         <f>GHG!AJ47</f>
         <v>28.030647009999999</v>
       </c>
-      <c r="AT24" s="94">
+      <c r="AT24" s="82">
         <f>GHG!B111</f>
         <v>1.93612E-5</v>
       </c>
-      <c r="AU24" s="94">
+      <c r="AU24" s="82">
         <f>GHG!C111</f>
         <v>1.8385499999999999E-5</v>
       </c>
-      <c r="AV24" s="94">
+      <c r="AV24" s="82">
         <f>GHG!D111</f>
         <v>2.4159E-5</v>
       </c>
-      <c r="AW24" s="94">
+      <c r="AW24" s="82">
         <f>GHG!E111</f>
         <v>2.14071E-5</v>
       </c>
-      <c r="AX24" s="94">
+      <c r="AX24" s="82">
         <f>GHG!F111</f>
         <v>9.1849900000000003E-6</v>
       </c>
-      <c r="AY24" s="94">
+      <c r="AY24" s="82">
         <f>GHG!G111</f>
         <v>9.1849900000000003E-6</v>
       </c>
@@ -8946,7 +8952,7 @@
         <v>1.5508954E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:75">
+    <row r="25" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -9124,27 +9130,27 @@
         <f>GHG!AJ48</f>
         <v>28.404388969999999</v>
       </c>
-      <c r="AT25" s="94">
+      <c r="AT25" s="82">
         <f>GHG!B112</f>
         <v>1.8753499999999999E-5</v>
       </c>
-      <c r="AU25" s="94">
+      <c r="AU25" s="82">
         <f>GHG!C112</f>
         <v>1.7956099999999999E-5</v>
       </c>
-      <c r="AV25" s="94">
+      <c r="AV25" s="82">
         <f>GHG!D112</f>
         <v>2.3669300000000001E-5</v>
       </c>
-      <c r="AW25" s="94">
+      <c r="AW25" s="82">
         <f>GHG!E112</f>
         <v>2.1143200000000001E-5</v>
       </c>
-      <c r="AX25" s="94">
+      <c r="AX25" s="82">
         <f>GHG!F112</f>
         <v>9.1995700000000004E-6</v>
       </c>
-      <c r="AY25" s="94">
+      <c r="AY25" s="82">
         <f>GHG!G112</f>
         <v>9.1995700000000004E-6</v>
       </c>
@@ -9245,7 +9251,7 @@
         <v>1.5873554000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:75">
+    <row r="26" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -9423,27 +9429,27 @@
         <f>GHG!AJ49</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT26" s="94">
+      <c r="AT26" s="82">
         <f>GHG!B113</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU26" s="94">
+      <c r="AU26" s="82">
         <f>GHG!C113</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV26" s="94">
+      <c r="AV26" s="82">
         <f>GHG!D113</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW26" s="94">
+      <c r="AW26" s="82">
         <f>GHG!E113</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX26" s="94">
+      <c r="AX26" s="82">
         <f>GHG!F113</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY26" s="94">
+      <c r="AY26" s="82">
         <f>GHG!G113</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -9544,7 +9550,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:75">
+    <row r="27" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -9722,27 +9728,27 @@
         <f>GHG!AJ50</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT27" s="94">
+      <c r="AT27" s="82">
         <f>GHG!B114</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU27" s="94">
+      <c r="AU27" s="82">
         <f>GHG!C114</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV27" s="94">
+      <c r="AV27" s="82">
         <f>GHG!D114</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW27" s="94">
+      <c r="AW27" s="82">
         <f>GHG!E114</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX27" s="94">
+      <c r="AX27" s="82">
         <f>GHG!F114</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY27" s="94">
+      <c r="AY27" s="82">
         <f>GHG!G114</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -9843,7 +9849,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:75">
+    <row r="28" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -10021,27 +10027,27 @@
         <f>GHG!AJ51</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT28" s="94">
+      <c r="AT28" s="82">
         <f>GHG!B115</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU28" s="94">
+      <c r="AU28" s="82">
         <f>GHG!C115</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV28" s="94">
+      <c r="AV28" s="82">
         <f>GHG!D115</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW28" s="94">
+      <c r="AW28" s="82">
         <f>GHG!E115</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX28" s="94">
+      <c r="AX28" s="82">
         <f>GHG!F115</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY28" s="94">
+      <c r="AY28" s="82">
         <f>GHG!G115</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -10142,7 +10148,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:75">
+    <row r="29" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -10320,27 +10326,27 @@
         <f>GHG!AJ52</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT29" s="94">
+      <c r="AT29" s="82">
         <f>GHG!B116</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU29" s="94">
+      <c r="AU29" s="82">
         <f>GHG!C116</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV29" s="94">
+      <c r="AV29" s="82">
         <f>GHG!D116</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW29" s="94">
+      <c r="AW29" s="82">
         <f>GHG!E116</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX29" s="94">
+      <c r="AX29" s="82">
         <f>GHG!F116</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY29" s="94">
+      <c r="AY29" s="82">
         <f>GHG!G116</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -10441,7 +10447,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:75">
+    <row r="30" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -10619,27 +10625,27 @@
         <f>GHG!AJ53</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT30" s="94">
+      <c r="AT30" s="82">
         <f>GHG!B117</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU30" s="94">
+      <c r="AU30" s="82">
         <f>GHG!C117</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV30" s="94">
+      <c r="AV30" s="82">
         <f>GHG!D117</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW30" s="94">
+      <c r="AW30" s="82">
         <f>GHG!E117</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX30" s="94">
+      <c r="AX30" s="82">
         <f>GHG!F117</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY30" s="94">
+      <c r="AY30" s="82">
         <f>GHG!G117</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -10740,7 +10746,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:75">
+    <row r="31" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -10918,27 +10924,27 @@
         <f>GHG!AJ54</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT31" s="94">
+      <c r="AT31" s="82">
         <f>GHG!B118</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU31" s="94">
+      <c r="AU31" s="82">
         <f>GHG!C118</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV31" s="94">
+      <c r="AV31" s="82">
         <f>GHG!D118</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW31" s="94">
+      <c r="AW31" s="82">
         <f>GHG!E118</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX31" s="94">
+      <c r="AX31" s="82">
         <f>GHG!F118</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY31" s="94">
+      <c r="AY31" s="82">
         <f>GHG!G118</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -11039,7 +11045,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:75">
+    <row r="32" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -11217,27 +11223,27 @@
         <f>GHG!AJ55</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT32" s="94">
+      <c r="AT32" s="82">
         <f>GHG!B119</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU32" s="94">
+      <c r="AU32" s="82">
         <f>GHG!C119</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV32" s="94">
+      <c r="AV32" s="82">
         <f>GHG!D119</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW32" s="94">
+      <c r="AW32" s="82">
         <f>GHG!E119</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX32" s="94">
+      <c r="AX32" s="82">
         <f>GHG!F119</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY32" s="94">
+      <c r="AY32" s="82">
         <f>GHG!G119</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -11338,7 +11344,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:75">
+    <row r="33" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -11516,27 +11522,27 @@
         <f>GHG!AJ56</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT33" s="94">
+      <c r="AT33" s="82">
         <f>GHG!B120</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU33" s="94">
+      <c r="AU33" s="82">
         <f>GHG!C120</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV33" s="94">
+      <c r="AV33" s="82">
         <f>GHG!D120</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW33" s="94">
+      <c r="AW33" s="82">
         <f>GHG!E120</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX33" s="94">
+      <c r="AX33" s="82">
         <f>GHG!F120</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY33" s="94">
+      <c r="AY33" s="82">
         <f>GHG!G120</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -11637,7 +11643,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:75">
+    <row r="34" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -11815,27 +11821,27 @@
         <f>GHG!AJ57</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT34" s="94">
+      <c r="AT34" s="82">
         <f>GHG!B121</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU34" s="94">
+      <c r="AU34" s="82">
         <f>GHG!C121</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV34" s="94">
+      <c r="AV34" s="82">
         <f>GHG!D121</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW34" s="94">
+      <c r="AW34" s="82">
         <f>GHG!E121</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX34" s="94">
+      <c r="AX34" s="82">
         <f>GHG!F121</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY34" s="94">
+      <c r="AY34" s="82">
         <f>GHG!G121</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -11936,7 +11942,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:75">
+    <row r="35" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -12114,27 +12120,27 @@
         <f>GHG!AJ58</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT35" s="94">
+      <c r="AT35" s="82">
         <f>GHG!B122</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU35" s="94">
+      <c r="AU35" s="82">
         <f>GHG!C122</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV35" s="94">
+      <c r="AV35" s="82">
         <f>GHG!D122</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW35" s="94">
+      <c r="AW35" s="82">
         <f>GHG!E122</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX35" s="94">
+      <c r="AX35" s="82">
         <f>GHG!F122</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY35" s="94">
+      <c r="AY35" s="82">
         <f>GHG!G122</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -12235,7 +12241,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:75">
+    <row r="36" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -12413,27 +12419,27 @@
         <f>GHG!AJ59</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT36" s="94">
+      <c r="AT36" s="82">
         <f>GHG!B123</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU36" s="94">
+      <c r="AU36" s="82">
         <f>GHG!C123</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV36" s="94">
+      <c r="AV36" s="82">
         <f>GHG!D123</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW36" s="94">
+      <c r="AW36" s="82">
         <f>GHG!E123</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX36" s="94">
+      <c r="AX36" s="82">
         <f>GHG!F123</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY36" s="94">
+      <c r="AY36" s="82">
         <f>GHG!G123</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -12534,7 +12540,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:75">
+    <row r="37" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -12712,27 +12718,27 @@
         <f>GHG!AJ60</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT37" s="94">
+      <c r="AT37" s="82">
         <f>GHG!B124</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU37" s="94">
+      <c r="AU37" s="82">
         <f>GHG!C124</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV37" s="94">
+      <c r="AV37" s="82">
         <f>GHG!D124</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW37" s="94">
+      <c r="AW37" s="82">
         <f>GHG!E124</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX37" s="94">
+      <c r="AX37" s="82">
         <f>GHG!F124</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY37" s="94">
+      <c r="AY37" s="82">
         <f>GHG!G124</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -12833,7 +12839,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:75">
+    <row r="38" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -13011,27 +13017,27 @@
         <f>GHG!AJ61</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT38" s="94">
+      <c r="AT38" s="82">
         <f>GHG!B125</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU38" s="94">
+      <c r="AU38" s="82">
         <f>GHG!C125</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV38" s="94">
+      <c r="AV38" s="82">
         <f>GHG!D125</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW38" s="94">
+      <c r="AW38" s="82">
         <f>GHG!E125</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX38" s="94">
+      <c r="AX38" s="82">
         <f>GHG!F125</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY38" s="94">
+      <c r="AY38" s="82">
         <f>GHG!G125</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -13132,7 +13138,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:75">
+    <row r="39" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -13310,27 +13316,27 @@
         <f>GHG!AJ62</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT39" s="94">
+      <c r="AT39" s="82">
         <f>GHG!B126</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU39" s="94">
+      <c r="AU39" s="82">
         <f>GHG!C126</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV39" s="94">
+      <c r="AV39" s="82">
         <f>GHG!D126</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW39" s="94">
+      <c r="AW39" s="82">
         <f>GHG!E126</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX39" s="94">
+      <c r="AX39" s="82">
         <f>GHG!F126</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY39" s="94">
+      <c r="AY39" s="82">
         <f>GHG!G126</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -13431,7 +13437,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:75">
+    <row r="40" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -13609,27 +13615,27 @@
         <f>GHG!AJ63</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT40" s="94">
+      <c r="AT40" s="82">
         <f>GHG!B127</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU40" s="94">
+      <c r="AU40" s="82">
         <f>GHG!C127</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV40" s="94">
+      <c r="AV40" s="82">
         <f>GHG!D127</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW40" s="94">
+      <c r="AW40" s="82">
         <f>GHG!E127</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX40" s="94">
+      <c r="AX40" s="82">
         <f>GHG!F127</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY40" s="94">
+      <c r="AY40" s="82">
         <f>GHG!G127</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -13730,7 +13736,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:75">
+    <row r="41" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -13908,27 +13914,27 @@
         <f>GHG!AJ64</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT41" s="94">
+      <c r="AT41" s="82">
         <f>GHG!B128</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU41" s="94">
+      <c r="AU41" s="82">
         <f>GHG!C128</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV41" s="94">
+      <c r="AV41" s="82">
         <f>GHG!D128</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW41" s="94">
+      <c r="AW41" s="82">
         <f>GHG!E128</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX41" s="94">
+      <c r="AX41" s="82">
         <f>GHG!F128</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY41" s="94">
+      <c r="AY41" s="82">
         <f>GHG!G128</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -14029,7 +14035,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:75">
+    <row r="42" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -14207,27 +14213,27 @@
         <f>GHG!AJ65</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT42" s="94">
+      <c r="AT42" s="82">
         <f>GHG!B129</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU42" s="94">
+      <c r="AU42" s="82">
         <f>GHG!C129</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV42" s="94">
+      <c r="AV42" s="82">
         <f>GHG!D129</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW42" s="94">
+      <c r="AW42" s="82">
         <f>GHG!E129</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX42" s="94">
+      <c r="AX42" s="82">
         <f>GHG!F129</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY42" s="94">
+      <c r="AY42" s="82">
         <f>GHG!G129</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -14328,7 +14334,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:75">
+    <row r="43" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -14506,27 +14512,27 @@
         <f>GHG!AJ66</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT43" s="94">
+      <c r="AT43" s="82">
         <f>GHG!B130</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU43" s="94">
+      <c r="AU43" s="82">
         <f>GHG!C130</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV43" s="94">
+      <c r="AV43" s="82">
         <f>GHG!D130</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW43" s="94">
+      <c r="AW43" s="82">
         <f>GHG!E130</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX43" s="94">
+      <c r="AX43" s="82">
         <f>GHG!F130</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY43" s="94">
+      <c r="AY43" s="82">
         <f>GHG!G130</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -14627,7 +14633,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:75">
+    <row r="44" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -14805,27 +14811,27 @@
         <f>GHG!AJ67</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT44" s="94">
+      <c r="AT44" s="82">
         <f>GHG!B131</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU44" s="94">
+      <c r="AU44" s="82">
         <f>GHG!C131</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV44" s="94">
+      <c r="AV44" s="82">
         <f>GHG!D131</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW44" s="94">
+      <c r="AW44" s="82">
         <f>GHG!E131</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX44" s="94">
+      <c r="AX44" s="82">
         <f>GHG!F131</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY44" s="94">
+      <c r="AY44" s="82">
         <f>GHG!G131</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -14926,7 +14932,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:75">
+    <row r="45" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
@@ -15104,27 +15110,27 @@
         <f>GHG!AJ68</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT45" s="94">
+      <c r="AT45" s="82">
         <f>GHG!B132</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU45" s="94">
+      <c r="AU45" s="82">
         <f>GHG!C132</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV45" s="94">
+      <c r="AV45" s="82">
         <f>GHG!D132</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW45" s="94">
+      <c r="AW45" s="82">
         <f>GHG!E132</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX45" s="94">
+      <c r="AX45" s="82">
         <f>GHG!F132</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY45" s="94">
+      <c r="AY45" s="82">
         <f>GHG!G132</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -15225,7 +15231,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:75">
+    <row r="46" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
@@ -15403,27 +15409,27 @@
         <f>GHG!AJ69</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT46" s="94">
+      <c r="AT46" s="82">
         <f>GHG!B133</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU46" s="94">
+      <c r="AU46" s="82">
         <f>GHG!C133</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV46" s="94">
+      <c r="AV46" s="82">
         <f>GHG!D133</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW46" s="94">
+      <c r="AW46" s="82">
         <f>GHG!E133</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX46" s="94">
+      <c r="AX46" s="82">
         <f>GHG!F133</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY46" s="94">
+      <c r="AY46" s="82">
         <f>GHG!G133</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -15524,7 +15530,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:75">
+    <row r="47" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
@@ -15702,27 +15708,27 @@
         <f>GHG!AJ70</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT47" s="94">
+      <c r="AT47" s="82">
         <f>GHG!B134</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU47" s="94">
+      <c r="AU47" s="82">
         <f>GHG!C134</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV47" s="94">
+      <c r="AV47" s="82">
         <f>GHG!D134</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW47" s="94">
+      <c r="AW47" s="82">
         <f>GHG!E134</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX47" s="94">
+      <c r="AX47" s="82">
         <f>GHG!F134</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY47" s="94">
+      <c r="AY47" s="82">
         <f>GHG!G134</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -15823,7 +15829,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:75">
+    <row r="48" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
@@ -16001,27 +16007,27 @@
         <f>GHG!AJ71</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT48" s="94">
+      <c r="AT48" s="82">
         <f>GHG!B135</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU48" s="94">
+      <c r="AU48" s="82">
         <f>GHG!C135</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV48" s="94">
+      <c r="AV48" s="82">
         <f>GHG!D135</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW48" s="94">
+      <c r="AW48" s="82">
         <f>GHG!E135</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX48" s="94">
+      <c r="AX48" s="82">
         <f>GHG!F135</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY48" s="94">
+      <c r="AY48" s="82">
         <f>GHG!G135</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -16122,7 +16128,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:75">
+    <row r="49" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
@@ -16300,27 +16306,27 @@
         <f>GHG!AJ72</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT49" s="94">
+      <c r="AT49" s="82">
         <f>GHG!B136</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU49" s="94">
+      <c r="AU49" s="82">
         <f>GHG!C136</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV49" s="94">
+      <c r="AV49" s="82">
         <f>GHG!D136</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW49" s="94">
+      <c r="AW49" s="82">
         <f>GHG!E136</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX49" s="94">
+      <c r="AX49" s="82">
         <f>GHG!F136</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY49" s="94">
+      <c r="AY49" s="82">
         <f>GHG!G136</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -16421,7 +16427,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:75">
+    <row r="50" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
@@ -16599,27 +16605,27 @@
         <f>GHG!AJ73</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT50" s="94">
+      <c r="AT50" s="82">
         <f>GHG!B137</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU50" s="94">
+      <c r="AU50" s="82">
         <f>GHG!C137</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV50" s="94">
+      <c r="AV50" s="82">
         <f>GHG!D137</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW50" s="94">
+      <c r="AW50" s="82">
         <f>GHG!E137</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX50" s="94">
+      <c r="AX50" s="82">
         <f>GHG!F137</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY50" s="94">
+      <c r="AY50" s="82">
         <f>GHG!G137</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -16720,7 +16726,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:75">
+    <row r="51" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
@@ -16898,27 +16904,27 @@
         <f>GHG!AJ74</f>
         <v>28.77813093</v>
       </c>
-      <c r="AT51" s="94">
+      <c r="AT51" s="82">
         <f>GHG!B138</f>
         <v>1.8117900000000001E-5</v>
       </c>
-      <c r="AU51" s="94">
+      <c r="AU51" s="82">
         <f>GHG!C138</f>
         <v>1.7504599999999998E-5</v>
       </c>
-      <c r="AV51" s="94">
+      <c r="AV51" s="82">
         <f>GHG!D138</f>
         <v>2.31529E-5</v>
       </c>
-      <c r="AW51" s="94">
+      <c r="AW51" s="82">
         <f>GHG!E138</f>
         <v>2.0860899999999999E-5</v>
       </c>
-      <c r="AX51" s="94">
+      <c r="AX51" s="82">
         <f>GHG!F138</f>
         <v>9.2101800000000006E-6</v>
       </c>
-      <c r="AY51" s="94">
+      <c r="AY51" s="82">
         <f>GHG!G138</f>
         <v>9.2101800000000006E-6</v>
       </c>
@@ -17028,14 +17034,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9064C83-FBE2-4371-949A-1A7D90AF74E5}">
   <dimension ref="A1:BR58"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="27" max="27" width="42.5703125" customWidth="1"/>
     <col min="50" max="50" width="20" customWidth="1"/>
     <col min="69" max="69" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="S1" t="s">
         <v>75</v>
       </c>
@@ -17064,7 +17070,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:70">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" s="43"/>
       <c r="B2" s="43"/>
       <c r="C2" s="43"/>
@@ -17153,7 +17159,7 @@
       <c r="BP2" s="43"/>
       <c r="BQ2" s="43"/>
     </row>
-    <row r="3" spans="1:70" s="42" customFormat="1" ht="43.5">
+    <row r="3" spans="1:70" s="42" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
         <v>79</v>
       </c>
@@ -17372,7 +17378,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:70">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" s="43" t="s">
         <v>96</v>
       </c>
@@ -17610,7 +17616,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="5" spans="1:70">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A5" s="43" t="s">
         <v>101</v>
       </c>
@@ -17819,7 +17825,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:70">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A6" s="43" t="s">
         <v>106</v>
       </c>
@@ -18028,14 +18034,14 @@
         <v>171</v>
       </c>
     </row>
-    <row r="7" spans="1:70">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A7" s="43"/>
       <c r="B7" s="43" t="str">
         <f>_xlfn.CONCAT(LOWER(B3),"_",B5)</f>
         <v>summer_on-peak_usdperkWh</v>
       </c>
       <c r="C7" s="43" t="str">
-        <f t="shared" ref="C7:AA7" si="0">_xlfn.CONCAT(LOWER(C3),"_",C5)</f>
+        <f t="shared" ref="C7:R7" si="0">_xlfn.CONCAT(LOWER(C3),"_",C5)</f>
         <v>summer_off-peak_usdperkWh</v>
       </c>
       <c r="D7" s="43" t="str">
@@ -18303,7 +18309,7 @@
         <v>gasoline_transportation_usdperMMBtu_ch4</v>
       </c>
     </row>
-    <row r="8" spans="1:70">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A8" s="43"/>
       <c r="B8" s="43" t="s">
         <v>1</v>
@@ -18519,7 +18525,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:70">
+    <row r="9" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1</v>
       </c>
@@ -18796,7 +18802,7 @@
         <v>8.0634279999999992E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:70">
+    <row r="10" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2</v>
       </c>
@@ -19073,7 +19079,7 @@
         <v>8.3512699999999992E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:70">
+    <row r="11" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
@@ -19350,7 +19356,7 @@
         <v>8.6429509999999994E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:70">
+    <row r="12" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>4</v>
       </c>
@@ -19627,7 +19633,7 @@
         <v>8.9307929999999994E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:70">
+    <row r="13" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>5</v>
       </c>
@@ -19904,7 +19910,7 @@
         <v>9.2224739999999996E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:70">
+    <row r="14" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>6</v>
       </c>
@@ -20181,7 +20187,7 @@
         <v>9.5563709999999993E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:70">
+    <row r="15" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>7</v>
       </c>
@@ -20458,7 +20464,7 @@
         <v>9.8941059999999997E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:70">
+    <row r="16" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>8</v>
       </c>
@@ -20735,7 +20741,7 @@
         <v>1.0231841E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:69">
+    <row r="17" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9</v>
       </c>
@@ -21012,7 +21018,7 @@
         <v>1.0569577E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:69">
+    <row r="18" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>10</v>
       </c>
@@ -21289,7 +21295,7 @@
         <v>1.0907312000000001E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:69">
+    <row r="19" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>11</v>
       </c>
@@ -21566,7 +21572,7 @@
         <v>1.1241209E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:69">
+    <row r="20" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>12</v>
       </c>
@@ -21843,7 +21849,7 @@
         <v>1.1578944000000001E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:69">
+    <row r="21" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>13</v>
       </c>
@@ -22120,7 +22126,7 @@
         <v>1.1916680000000001E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:69">
+    <row r="22" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>14</v>
       </c>
@@ -22397,7 +22403,7 @@
         <v>1.2254414999999999E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:69">
+    <row r="23" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>15</v>
       </c>
@@ -22674,7 +22680,7 @@
         <v>1.2588312000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:69">
+    <row r="24" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>16</v>
       </c>
@@ -22951,7 +22957,7 @@
         <v>1.2952913E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:69">
+    <row r="25" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>17</v>
       </c>
@@ -23228,7 +23234,7 @@
         <v>1.3321351E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:69">
+    <row r="26" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>18</v>
       </c>
@@ -23505,7 +23511,7 @@
         <v>1.3685951E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:69">
+    <row r="27" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>19</v>
       </c>
@@ -23782,7 +23788,7 @@
         <v>1.4050551999999999E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:69">
+    <row r="28" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>20</v>
       </c>
@@ -24059,7 +24065,7 @@
         <v>1.4415152000000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:69">
+    <row r="29" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>21</v>
       </c>
@@ -24336,7 +24342,7 @@
         <v>1.4779753E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:69">
+    <row r="30" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>22</v>
       </c>
@@ -24613,7 +24619,7 @@
         <v>1.5144352999999999E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:69">
+    <row r="31" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>23</v>
       </c>
@@ -24890,7 +24896,7 @@
         <v>1.5508954E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:69">
+    <row r="32" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>24</v>
       </c>
@@ -25167,7 +25173,7 @@
         <v>1.5873554000000002E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:69">
+    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>25</v>
       </c>
@@ -25444,7 +25450,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:69">
+    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26</v>
       </c>
@@ -25721,7 +25727,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:69">
+    <row r="35" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>27</v>
       </c>
@@ -25998,7 +26004,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:69">
+    <row r="36" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>28</v>
       </c>
@@ -26275,7 +26281,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:69">
+    <row r="37" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>29</v>
       </c>
@@ -26552,7 +26558,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:69">
+    <row r="38" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>30</v>
       </c>
@@ -26829,7 +26835,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:69">
+    <row r="39" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>31</v>
       </c>
@@ -27106,7 +27112,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:69">
+    <row r="40" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>32</v>
       </c>
@@ -27383,7 +27389,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:69">
+    <row r="41" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>33</v>
       </c>
@@ -27660,7 +27666,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:69">
+    <row r="42" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>34</v>
       </c>
@@ -27937,7 +27943,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:69">
+    <row r="43" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>35</v>
       </c>
@@ -28214,7 +28220,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:69">
+    <row r="44" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>36</v>
       </c>
@@ -28491,7 +28497,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:69">
+    <row r="45" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>37</v>
       </c>
@@ -28768,7 +28774,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:69">
+    <row r="46" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>38</v>
       </c>
@@ -29045,7 +29051,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:69">
+    <row r="47" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>39</v>
       </c>
@@ -29322,7 +29328,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:69">
+    <row r="48" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>40</v>
       </c>
@@ -29599,7 +29605,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:69">
+    <row r="49" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>41</v>
       </c>
@@ -29876,7 +29882,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:69">
+    <row r="50" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>42</v>
       </c>
@@ -30153,7 +30159,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:69">
+    <row r="51" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>43</v>
       </c>
@@ -30430,7 +30436,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:69">
+    <row r="52" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>44</v>
       </c>
@@ -30707,7 +30713,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:69">
+    <row r="53" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>45</v>
       </c>
@@ -30984,7 +30990,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:69">
+    <row r="54" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>46</v>
       </c>
@@ -31261,7 +31267,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:69">
+    <row r="55" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>47</v>
       </c>
@@ -31538,7 +31544,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:69">
+    <row r="56" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>48</v>
       </c>
@@ -31815,7 +31821,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:69">
+    <row r="57" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>49</v>
       </c>
@@ -32092,7 +32098,7 @@
         <v>1.6238155000000001E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:69">
+    <row r="58" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>50</v>
       </c>
@@ -32378,23 +32384,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:EG71"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:137" ht="15" customHeight="1">
+    <row r="1" spans="1:137" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
-      <c r="E1" s="95" t="s">
+      <c r="E1" s="103" t="s">
         <v>173</v>
       </c>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="4" t="s">
@@ -32415,19 +32421,19 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
       <c r="AB1" s="3"/>
-      <c r="AC1" s="97"/>
-      <c r="AD1" s="97"/>
+      <c r="AC1" s="83"/>
+      <c r="AD1" s="83"/>
       <c r="AE1" s="3"/>
-      <c r="AF1" s="97"/>
-      <c r="AG1" s="97"/>
+      <c r="AF1" s="83"/>
+      <c r="AG1" s="83"/>
       <c r="AH1" s="3"/>
       <c r="AI1" s="5"/>
       <c r="AJ1" s="5"/>
       <c r="AK1" s="5"/>
       <c r="AL1" s="5"/>
       <c r="AM1" s="3"/>
-      <c r="AN1" s="97"/>
-      <c r="AO1" s="97"/>
+      <c r="AN1" s="83"/>
+      <c r="AO1" s="83"/>
       <c r="AP1" s="3"/>
       <c r="AQ1" s="3"/>
       <c r="AR1" s="3"/>
@@ -32442,8 +32448,8 @@
       <c r="BA1" s="3"/>
       <c r="BB1" s="3"/>
       <c r="BC1" s="3"/>
-      <c r="BD1" s="97"/>
-      <c r="BE1" s="97"/>
+      <c r="BD1" s="83"/>
+      <c r="BE1" s="83"/>
       <c r="BF1" s="3"/>
       <c r="BG1" s="3"/>
       <c r="BH1" s="3"/>
@@ -32525,7 +32531,7 @@
       <c r="EF1" s="3"/>
       <c r="EG1" s="3"/>
     </row>
-    <row r="2" spans="1:137">
+    <row r="2" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -32537,8 +32543,8 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="97"/>
-      <c r="M2" s="97"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -32554,19 +32560,19 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
-      <c r="AC2" s="97"/>
-      <c r="AD2" s="97"/>
+      <c r="AC2" s="83"/>
+      <c r="AD2" s="83"/>
       <c r="AE2" s="3"/>
-      <c r="AF2" s="97"/>
-      <c r="AG2" s="97"/>
+      <c r="AF2" s="83"/>
+      <c r="AG2" s="83"/>
       <c r="AH2" s="3"/>
       <c r="AI2" s="3"/>
       <c r="AJ2" s="3"/>
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
-      <c r="AN2" s="97"/>
-      <c r="AO2" s="97"/>
+      <c r="AN2" s="83"/>
+      <c r="AO2" s="83"/>
       <c r="AP2" s="3"/>
       <c r="AQ2" s="3"/>
       <c r="AR2" s="3"/>
@@ -32581,8 +32587,8 @@
       <c r="BA2" s="3"/>
       <c r="BB2" s="3"/>
       <c r="BC2" s="3"/>
-      <c r="BD2" s="97"/>
-      <c r="BE2" s="97"/>
+      <c r="BD2" s="83"/>
+      <c r="BE2" s="83"/>
       <c r="BF2" s="3"/>
       <c r="BG2" s="3"/>
       <c r="BH2" s="3"/>
@@ -32664,7 +32670,7 @@
       <c r="EF2" s="3"/>
       <c r="EG2" s="3"/>
     </row>
-    <row r="3" spans="1:137">
+    <row r="3" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="6" t="s">
         <v>175</v>
@@ -32733,13 +32739,13 @@
       <c r="AB3" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="AC3" s="98" t="s">
-        <v>176</v>
-      </c>
-      <c r="AD3" s="98"/>
+      <c r="AC3" s="95" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD3" s="95"/>
       <c r="AE3" s="3"/>
-      <c r="AF3" s="97"/>
-      <c r="AG3" s="97"/>
+      <c r="AF3" s="83"/>
+      <c r="AG3" s="83"/>
       <c r="AH3" s="3"/>
       <c r="AI3" s="6" t="s">
         <v>178</v>
@@ -32752,8 +32758,8 @@
       <c r="AM3" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="AN3" s="97"/>
-      <c r="AO3" s="97"/>
+      <c r="AN3" s="83"/>
+      <c r="AO3" s="83"/>
       <c r="AP3" s="3"/>
       <c r="AQ3" s="3"/>
       <c r="AR3" s="3"/>
@@ -32768,8 +32774,8 @@
       <c r="BA3" s="3"/>
       <c r="BB3" s="3"/>
       <c r="BC3" s="3"/>
-      <c r="BD3" s="97"/>
-      <c r="BE3" s="97"/>
+      <c r="BD3" s="83"/>
+      <c r="BE3" s="83"/>
       <c r="BF3" s="3"/>
       <c r="BG3" s="3"/>
       <c r="BH3" s="3"/>
@@ -32851,7 +32857,7 @@
       <c r="EF3" s="3"/>
       <c r="EG3" s="3"/>
     </row>
-    <row r="4" spans="1:137" ht="15" customHeight="1">
+    <row r="4" spans="1:137" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>180</v>
       </c>
@@ -32937,12 +32943,12 @@
       <c r="AC4" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="AD4" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE4" s="97"/>
-      <c r="AF4" s="97"/>
-      <c r="AG4" s="97"/>
+      <c r="AD4" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE4" s="83"/>
+      <c r="AF4" s="83"/>
+      <c r="AG4" s="83"/>
       <c r="AH4" s="3"/>
       <c r="AI4" s="12" t="s">
         <v>189</v>
@@ -32953,12 +32959,12 @@
       <c r="AK4" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="AL4" s="82" t="s">
+      <c r="AL4" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="AM4" s="83"/>
-      <c r="AN4" s="97"/>
-      <c r="AO4" s="97"/>
+      <c r="AM4" s="102"/>
+      <c r="AN4" s="83"/>
+      <c r="AO4" s="83"/>
       <c r="AP4" s="14"/>
       <c r="AQ4" s="14"/>
       <c r="AR4" s="3"/>
@@ -32973,8 +32979,8 @@
       <c r="BA4" s="14"/>
       <c r="BB4" s="3"/>
       <c r="BC4" s="3"/>
-      <c r="BD4" s="97"/>
-      <c r="BE4" s="97"/>
+      <c r="BD4" s="83"/>
+      <c r="BE4" s="83"/>
       <c r="BF4" s="3"/>
       <c r="BG4" s="3"/>
       <c r="BH4" s="3"/>
@@ -33056,7 +33062,7 @@
       <c r="EF4" s="3"/>
       <c r="EG4" s="3"/>
     </row>
-    <row r="5" spans="1:137">
+    <row r="5" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>192</v>
       </c>
@@ -33142,12 +33148,12 @@
       <c r="AC5" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="AD5" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE5" s="97"/>
-      <c r="AF5" s="97"/>
-      <c r="AG5" s="97"/>
+      <c r="AD5" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE5" s="83"/>
+      <c r="AF5" s="83"/>
+      <c r="AG5" s="83"/>
       <c r="AH5" s="3" t="s">
         <v>193</v>
       </c>
@@ -33184,8 +33190,8 @@
       <c r="BA5" s="3"/>
       <c r="BB5" s="3"/>
       <c r="BC5" s="3"/>
-      <c r="BD5" s="97"/>
-      <c r="BE5" s="97"/>
+      <c r="BD5" s="83"/>
+      <c r="BE5" s="83"/>
       <c r="BF5" s="3"/>
       <c r="BG5" s="3"/>
       <c r="BH5" s="3"/>
@@ -33267,7 +33273,7 @@
       <c r="EF5" s="3"/>
       <c r="EG5" s="3"/>
     </row>
-    <row r="6" spans="1:137">
+    <row r="6" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>197</v>
       </c>
@@ -33353,12 +33359,12 @@
       <c r="AC6" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="AD6" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE6" s="97"/>
-      <c r="AF6" s="97"/>
-      <c r="AG6" s="97"/>
+      <c r="AD6" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE6" s="83"/>
+      <c r="AF6" s="83"/>
+      <c r="AG6" s="83"/>
       <c r="AH6" s="3" t="s">
         <v>198</v>
       </c>
@@ -33395,8 +33401,8 @@
       <c r="BA6" s="3"/>
       <c r="BB6" s="3"/>
       <c r="BC6" s="3"/>
-      <c r="BD6" s="97"/>
-      <c r="BE6" s="97"/>
+      <c r="BD6" s="83"/>
+      <c r="BE6" s="83"/>
       <c r="BF6" s="3"/>
       <c r="BG6" s="3"/>
       <c r="BH6" s="3"/>
@@ -33478,7 +33484,7 @@
       <c r="EF6" s="3"/>
       <c r="EG6" s="23"/>
     </row>
-    <row r="7" spans="1:137">
+    <row r="7" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>201</v>
       </c>
@@ -33564,12 +33570,12 @@
       <c r="AC7" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="AD7" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE7" s="97"/>
-      <c r="AF7" s="97"/>
-      <c r="AG7" s="97"/>
+      <c r="AD7" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE7" s="83"/>
+      <c r="AF7" s="83"/>
+      <c r="AG7" s="83"/>
       <c r="AH7" s="3" t="s">
         <v>202</v>
       </c>
@@ -33608,8 +33614,8 @@
       <c r="BA7" s="3"/>
       <c r="BB7" s="3"/>
       <c r="BC7" s="3"/>
-      <c r="BD7" s="97"/>
-      <c r="BE7" s="97"/>
+      <c r="BD7" s="83"/>
+      <c r="BE7" s="83"/>
       <c r="BF7" s="3"/>
       <c r="BG7" s="3"/>
       <c r="BH7" s="3"/>
@@ -33691,7 +33697,7 @@
       <c r="EF7" s="3"/>
       <c r="EG7" s="3"/>
     </row>
-    <row r="8" spans="1:137">
+    <row r="8" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>176</v>
       </c>
@@ -33777,12 +33783,12 @@
       <c r="AC8" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="AD8" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE8" s="97"/>
-      <c r="AF8" s="97"/>
-      <c r="AG8" s="97"/>
+      <c r="AD8" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE8" s="83"/>
+      <c r="AF8" s="83"/>
+      <c r="AG8" s="83"/>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
@@ -33811,8 +33817,8 @@
       <c r="BA8" s="3"/>
       <c r="BB8" s="3"/>
       <c r="BC8" s="3"/>
-      <c r="BD8" s="97"/>
-      <c r="BE8" s="97"/>
+      <c r="BD8" s="83"/>
+      <c r="BE8" s="83"/>
       <c r="BF8" s="3"/>
       <c r="BG8" s="3"/>
       <c r="BH8" s="3"/>
@@ -33894,7 +33900,7 @@
       <c r="EF8" s="3"/>
       <c r="EG8" s="3"/>
     </row>
-    <row r="9" spans="1:137">
+    <row r="9" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>176</v>
       </c>
@@ -33980,12 +33986,12 @@
       <c r="AC9" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="AD9" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE9" s="97"/>
-      <c r="AF9" s="97"/>
-      <c r="AG9" s="97"/>
+      <c r="AD9" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE9" s="83"/>
+      <c r="AF9" s="83"/>
+      <c r="AG9" s="83"/>
       <c r="AH9" s="3"/>
       <c r="AI9" s="25"/>
       <c r="AJ9" s="25"/>
@@ -33996,8 +34002,8 @@
       <c r="AM9" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="AN9" s="97"/>
-      <c r="AO9" s="97"/>
+      <c r="AN9" s="83"/>
+      <c r="AO9" s="83"/>
       <c r="AP9" s="3"/>
       <c r="AQ9" s="3"/>
       <c r="AR9" s="3"/>
@@ -34012,8 +34018,8 @@
       <c r="BA9" s="3"/>
       <c r="BB9" s="3"/>
       <c r="BC9" s="3"/>
-      <c r="BD9" s="97"/>
-      <c r="BE9" s="97"/>
+      <c r="BD9" s="83"/>
+      <c r="BE9" s="83"/>
       <c r="BF9" s="3"/>
       <c r="BG9" s="3"/>
       <c r="BH9" s="3"/>
@@ -34095,7 +34101,7 @@
       <c r="EF9" s="3"/>
       <c r="EG9" s="3"/>
     </row>
-    <row r="10" spans="1:137">
+    <row r="10" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -34107,8 +34113,8 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="97"/>
-      <c r="M10" s="97"/>
+      <c r="L10" s="83"/>
+      <c r="M10" s="83"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -34124,19 +34130,19 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
-      <c r="AC10" s="97"/>
-      <c r="AD10" s="97"/>
+      <c r="AC10" s="83"/>
+      <c r="AD10" s="83"/>
       <c r="AE10" s="3"/>
-      <c r="AF10" s="97"/>
-      <c r="AG10" s="97"/>
+      <c r="AF10" s="83"/>
+      <c r="AG10" s="83"/>
       <c r="AH10" s="3"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
-      <c r="AN10" s="97"/>
-      <c r="AO10" s="97"/>
+      <c r="AN10" s="83"/>
+      <c r="AO10" s="83"/>
       <c r="AP10" s="3"/>
       <c r="AQ10" s="3"/>
       <c r="AR10" s="3"/>
@@ -34151,8 +34157,8 @@
       <c r="BA10" s="3"/>
       <c r="BB10" s="3"/>
       <c r="BC10" s="3"/>
-      <c r="BD10" s="97"/>
-      <c r="BE10" s="97"/>
+      <c r="BD10" s="83"/>
+      <c r="BE10" s="83"/>
       <c r="BF10" s="4"/>
       <c r="BG10" s="3"/>
       <c r="BH10" s="3"/>
@@ -34234,7 +34240,7 @@
       <c r="EF10" s="3"/>
       <c r="EG10" s="3"/>
     </row>
-    <row r="11" spans="1:137">
+    <row r="11" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -34246,8 +34252,8 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="97"/>
-      <c r="M11" s="97"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
       <c r="N11" s="6" t="s">
         <v>207</v>
       </c>
@@ -34285,21 +34291,21 @@
       <c r="AB11" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="AC11" s="98" t="s">
-        <v>176</v>
-      </c>
-      <c r="AD11" s="98"/>
+      <c r="AC11" s="95" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD11" s="95"/>
       <c r="AE11" s="3"/>
-      <c r="AF11" s="97"/>
-      <c r="AG11" s="97"/>
+      <c r="AF11" s="83"/>
+      <c r="AG11" s="83"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
-      <c r="AN11" s="97"/>
-      <c r="AO11" s="97"/>
+      <c r="AN11" s="83"/>
+      <c r="AO11" s="83"/>
       <c r="AP11" s="3"/>
       <c r="AQ11" s="3"/>
       <c r="AR11" s="3"/>
@@ -34314,8 +34320,8 @@
       <c r="BA11" s="3"/>
       <c r="BB11" s="3"/>
       <c r="BC11" s="3"/>
-      <c r="BD11" s="97"/>
-      <c r="BE11" s="97"/>
+      <c r="BD11" s="83"/>
+      <c r="BE11" s="83"/>
       <c r="BF11" s="3"/>
       <c r="BG11" s="3"/>
       <c r="BH11" s="3"/>
@@ -34397,7 +34403,7 @@
       <c r="EF11" s="3"/>
       <c r="EG11" s="3"/>
     </row>
-    <row r="12" spans="1:137">
+    <row r="12" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -34409,8 +34415,8 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="97"/>
-      <c r="M12" s="99"/>
+      <c r="L12" s="83"/>
+      <c r="M12" s="100"/>
       <c r="N12" s="16">
         <v>0</v>
       </c>
@@ -34459,20 +34465,20 @@
       <c r="AC12" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="AD12" s="97" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE12" s="97"/>
-      <c r="AF12" s="97"/>
-      <c r="AG12" s="97"/>
+      <c r="AD12" s="83" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE12" s="83"/>
+      <c r="AF12" s="83"/>
+      <c r="AG12" s="83"/>
       <c r="AH12" s="3"/>
       <c r="AI12" s="3"/>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
-      <c r="AN12" s="97"/>
-      <c r="AO12" s="97"/>
+      <c r="AN12" s="83"/>
+      <c r="AO12" s="83"/>
       <c r="AP12" s="3"/>
       <c r="AQ12" s="3"/>
       <c r="AR12" s="3"/>
@@ -34487,8 +34493,8 @@
       <c r="BA12" s="3"/>
       <c r="BB12" s="3"/>
       <c r="BC12" s="3"/>
-      <c r="BD12" s="97"/>
-      <c r="BE12" s="97"/>
+      <c r="BD12" s="83"/>
+      <c r="BE12" s="83"/>
       <c r="BF12" s="3"/>
       <c r="BG12" s="3"/>
       <c r="BH12" s="3"/>
@@ -34570,7 +34576,7 @@
       <c r="EF12" s="3"/>
       <c r="EG12" s="3"/>
     </row>
-    <row r="13" spans="1:137">
+    <row r="13" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -34582,8 +34588,8 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="97"/>
-      <c r="M13" s="97"/>
+      <c r="L13" s="83"/>
+      <c r="M13" s="83"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
@@ -34599,19 +34605,19 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
-      <c r="AC13" s="97"/>
-      <c r="AD13" s="97"/>
+      <c r="AC13" s="83"/>
+      <c r="AD13" s="83"/>
       <c r="AE13" s="3"/>
-      <c r="AF13" s="97"/>
-      <c r="AG13" s="97"/>
+      <c r="AF13" s="83"/>
+      <c r="AG13" s="83"/>
       <c r="AH13" s="3"/>
       <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
-      <c r="AN13" s="97"/>
-      <c r="AO13" s="97"/>
+      <c r="AN13" s="83"/>
+      <c r="AO13" s="83"/>
       <c r="AP13" s="3"/>
       <c r="AQ13" s="3"/>
       <c r="AR13" s="3"/>
@@ -34626,8 +34632,8 @@
       <c r="BA13" s="3"/>
       <c r="BB13" s="3"/>
       <c r="BC13" s="3"/>
-      <c r="BD13" s="97"/>
-      <c r="BE13" s="97"/>
+      <c r="BD13" s="83"/>
+      <c r="BE13" s="83"/>
       <c r="BF13" s="3"/>
       <c r="BG13" s="3"/>
       <c r="BH13" s="3"/>
@@ -34709,7 +34715,7 @@
       <c r="EF13" s="3"/>
       <c r="EG13" s="3"/>
     </row>
-    <row r="14" spans="1:137">
+    <row r="14" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="3" t="s">
         <v>208</v>
@@ -34727,8 +34733,8 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="97"/>
-      <c r="M14" s="99"/>
+      <c r="L14" s="83"/>
+      <c r="M14" s="100"/>
       <c r="N14" s="19">
         <v>1</v>
       </c>
@@ -34748,13 +34754,13 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
-      <c r="AC14" s="97"/>
-      <c r="AD14" s="97"/>
+      <c r="AC14" s="83"/>
+      <c r="AD14" s="83"/>
       <c r="AE14" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="AF14" s="97"/>
-      <c r="AG14" s="97"/>
+      <c r="AF14" s="83"/>
+      <c r="AG14" s="83"/>
       <c r="AH14" s="3" t="s">
         <v>212</v>
       </c>
@@ -34874,7 +34880,7 @@
       <c r="EF14" s="3"/>
       <c r="EG14" s="3"/>
     </row>
-    <row r="15" spans="1:137">
+    <row r="15" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="27" t="s">
         <v>215</v>
@@ -34906,8 +34912,8 @@
       <c r="K15" s="27" t="s">
         <v>224</v>
       </c>
-      <c r="L15" s="97"/>
-      <c r="M15" s="97"/>
+      <c r="L15" s="83"/>
+      <c r="M15" s="83"/>
       <c r="N15" s="28">
         <v>1</v>
       </c>
@@ -34953,17 +34959,17 @@
       <c r="AB15" s="28">
         <v>15</v>
       </c>
-      <c r="AC15" s="100">
+      <c r="AC15" s="94">
         <v>16</v>
       </c>
-      <c r="AD15" s="100"/>
+      <c r="AD15" s="94"/>
       <c r="AE15" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="AF15" s="98" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG15" s="98"/>
+      <c r="AF15" s="95" t="s">
+        <v>176</v>
+      </c>
+      <c r="AG15" s="95"/>
       <c r="AH15" s="6" t="s">
         <v>226</v>
       </c>
@@ -35017,10 +35023,10 @@
         <v>176</v>
       </c>
       <c r="BD15" s="3"/>
-      <c r="BE15" s="101" t="s">
+      <c r="BE15" s="96" t="s">
         <v>230</v>
       </c>
-      <c r="BF15" s="102"/>
+      <c r="BF15" s="97"/>
       <c r="BG15" s="3"/>
       <c r="BH15" s="3"/>
       <c r="BI15" s="3"/>
@@ -35101,403 +35107,403 @@
       <c r="EF15" s="3"/>
       <c r="EG15" s="3"/>
     </row>
-    <row r="16" spans="1:137">
+    <row r="16" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="98" t="s">
         <v>181</v>
       </c>
-      <c r="C16" s="84" t="s">
+      <c r="C16" s="98" t="s">
         <v>182</v>
       </c>
-      <c r="D16" s="84" t="s">
+      <c r="D16" s="98" t="s">
         <v>183</v>
       </c>
-      <c r="E16" s="84" t="s">
+      <c r="E16" s="98" t="s">
         <v>184</v>
       </c>
-      <c r="F16" s="84" t="s">
+      <c r="F16" s="98" t="s">
         <v>185</v>
       </c>
-      <c r="G16" s="84" t="s">
-        <v>176</v>
-      </c>
-      <c r="H16" s="84" t="s">
+      <c r="G16" s="98" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="98" t="s">
         <v>186</v>
       </c>
-      <c r="I16" s="84" t="s">
+      <c r="I16" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="J16" s="84" t="s">
+      <c r="J16" s="98" t="s">
         <v>187</v>
       </c>
-      <c r="K16" s="84" t="s">
+      <c r="K16" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="L16" s="103" t="s">
-        <v>176</v>
-      </c>
-      <c r="M16" s="99"/>
-      <c r="N16" s="86" t="s">
+      <c r="L16" s="99" t="s">
+        <v>176</v>
+      </c>
+      <c r="M16" s="100"/>
+      <c r="N16" s="90" t="s">
         <v>188</v>
       </c>
-      <c r="O16" s="86" t="s">
+      <c r="O16" s="90" t="s">
         <v>232</v>
       </c>
-      <c r="P16" s="86" t="s">
+      <c r="P16" s="90" t="s">
         <v>233</v>
       </c>
-      <c r="Q16" s="86" t="s">
+      <c r="Q16" s="90" t="s">
         <v>234</v>
       </c>
-      <c r="R16" s="86" t="s">
+      <c r="R16" s="90" t="s">
         <v>235</v>
       </c>
-      <c r="S16" s="86" t="s">
+      <c r="S16" s="90" t="s">
         <v>236</v>
       </c>
-      <c r="T16" s="86" t="s">
+      <c r="T16" s="90" t="s">
         <v>237</v>
       </c>
-      <c r="U16" s="86" t="s">
+      <c r="U16" s="90" t="s">
         <v>238</v>
       </c>
-      <c r="V16" s="86" t="s">
+      <c r="V16" s="90" t="s">
         <v>239</v>
       </c>
-      <c r="W16" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="X16" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y16" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z16" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA16" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB16" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="AC16" s="86" t="s">
-        <v>176</v>
-      </c>
-      <c r="AD16" s="87" t="s">
-        <v>176</v>
-      </c>
-      <c r="AE16" s="88" t="s">
+      <c r="W16" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="X16" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="Y16" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z16" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA16" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB16" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="AC16" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD16" s="92" t="s">
+        <v>176</v>
+      </c>
+      <c r="AE16" s="85" t="s">
         <v>240</v>
       </c>
-      <c r="AF16" s="89" t="s">
-        <v>176</v>
-      </c>
-      <c r="AG16" s="104" t="s">
-        <v>176</v>
-      </c>
-      <c r="AH16" s="88" t="s">
+      <c r="AF16" s="93" t="s">
+        <v>176</v>
+      </c>
+      <c r="AG16" s="89" t="s">
+        <v>176</v>
+      </c>
+      <c r="AH16" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="AI16" s="91" t="s">
+      <c r="AI16" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="AJ16" s="91" t="s">
+      <c r="AJ16" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="AK16" s="91" t="s">
+      <c r="AK16" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="AL16" s="91" t="s">
+      <c r="AL16" s="84" t="s">
         <v>241</v>
       </c>
-      <c r="AM16" s="90" t="s">
+      <c r="AM16" s="86" t="s">
         <v>242</v>
       </c>
-      <c r="AN16" s="104" t="s">
-        <v>176</v>
-      </c>
-      <c r="AO16" s="88" t="s">
+      <c r="AN16" s="89" t="s">
+        <v>176</v>
+      </c>
+      <c r="AO16" s="85" t="s">
         <v>192</v>
       </c>
-      <c r="AP16" s="91" t="s">
+      <c r="AP16" s="84" t="s">
         <v>243</v>
       </c>
-      <c r="AQ16" s="91" t="s">
+      <c r="AQ16" s="84" t="s">
         <v>244</v>
       </c>
-      <c r="AR16" s="92">
+      <c r="AR16" s="87">
         <v>0</v>
       </c>
-      <c r="AS16" s="93">
+      <c r="AS16" s="88">
         <v>0</v>
       </c>
-      <c r="AT16" s="88" t="s">
+      <c r="AT16" s="85" t="s">
         <v>192</v>
       </c>
-      <c r="AU16" s="91" t="s">
+      <c r="AU16" s="84" t="s">
         <v>243</v>
       </c>
-      <c r="AV16" s="91" t="s">
+      <c r="AV16" s="84" t="s">
         <v>244</v>
       </c>
-      <c r="AW16" s="92">
+      <c r="AW16" s="87">
         <v>0</v>
       </c>
-      <c r="AX16" s="93">
+      <c r="AX16" s="88">
         <v>0</v>
       </c>
-      <c r="AY16" s="88" t="s">
+      <c r="AY16" s="85" t="s">
         <v>192</v>
       </c>
-      <c r="AZ16" s="91" t="s">
+      <c r="AZ16" s="84" t="s">
         <v>243</v>
       </c>
-      <c r="BA16" s="91" t="s">
+      <c r="BA16" s="84" t="s">
         <v>244</v>
       </c>
-      <c r="BB16" s="92">
+      <c r="BB16" s="87">
         <v>0</v>
       </c>
-      <c r="BC16" s="93">
+      <c r="BC16" s="88">
         <v>0</v>
       </c>
-      <c r="BD16" s="104" t="s">
-        <v>176</v>
-      </c>
-      <c r="BE16" s="88" t="s">
+      <c r="BD16" s="89" t="s">
+        <v>176</v>
+      </c>
+      <c r="BE16" s="85" t="s">
         <v>245</v>
       </c>
-      <c r="BF16" s="90" t="s">
+      <c r="BF16" s="86" t="s">
         <v>246</v>
       </c>
-      <c r="BG16" s="88" t="s">
-        <v>176</v>
-      </c>
-      <c r="BH16" s="91"/>
-      <c r="BI16" s="91"/>
-      <c r="BJ16" s="91"/>
-      <c r="BK16" s="91"/>
-      <c r="BL16" s="91"/>
-      <c r="BM16" s="91"/>
-      <c r="BN16" s="91"/>
-      <c r="BO16" s="91"/>
-      <c r="BP16" s="91"/>
-      <c r="BQ16" s="97"/>
-      <c r="BR16" s="91"/>
-      <c r="BS16" s="91"/>
-      <c r="BT16" s="91"/>
-      <c r="BU16" s="91"/>
-      <c r="BV16" s="91"/>
-      <c r="BW16" s="91"/>
-      <c r="BX16" s="97"/>
-      <c r="BY16" s="91"/>
-      <c r="BZ16" s="91"/>
-      <c r="CA16" s="91"/>
-      <c r="CB16" s="91"/>
-      <c r="CC16" s="91"/>
-      <c r="CD16" s="91"/>
-      <c r="CE16" s="97"/>
-      <c r="CF16" s="91"/>
-      <c r="CG16" s="91"/>
-      <c r="CH16" s="91"/>
-      <c r="CI16" s="91"/>
-      <c r="CJ16" s="91"/>
-      <c r="CK16" s="91"/>
-      <c r="CL16" s="97"/>
-      <c r="CM16" s="91"/>
-      <c r="CN16" s="91"/>
-      <c r="CO16" s="91"/>
-      <c r="CP16" s="91"/>
-      <c r="CQ16" s="91"/>
-      <c r="CR16" s="91"/>
-      <c r="CS16" s="97"/>
-      <c r="CT16" s="91"/>
-      <c r="CU16" s="91"/>
-      <c r="CV16" s="91"/>
-      <c r="CW16" s="91"/>
-      <c r="CX16" s="91"/>
-      <c r="CY16" s="91"/>
-      <c r="CZ16" s="97"/>
-      <c r="DA16" s="91"/>
-      <c r="DB16" s="91"/>
-      <c r="DC16" s="91"/>
-      <c r="DD16" s="91"/>
-      <c r="DE16" s="91"/>
-      <c r="DF16" s="91"/>
-      <c r="DG16" s="97"/>
-      <c r="DH16" s="91"/>
-      <c r="DI16" s="91"/>
-      <c r="DJ16" s="91"/>
-      <c r="DK16" s="91"/>
-      <c r="DL16" s="91"/>
-      <c r="DM16" s="91"/>
-      <c r="DN16" s="97"/>
-      <c r="DO16" s="91"/>
-      <c r="DP16" s="91"/>
-      <c r="DQ16" s="91"/>
-      <c r="DR16" s="91"/>
-      <c r="DS16" s="91"/>
-      <c r="DT16" s="91"/>
-      <c r="DU16" s="97"/>
-      <c r="DV16" s="91"/>
-      <c r="DW16" s="91"/>
-      <c r="DX16" s="91"/>
-      <c r="DY16" s="91"/>
-      <c r="DZ16" s="91"/>
-      <c r="EA16" s="91"/>
-      <c r="EB16" s="97"/>
-      <c r="EC16" s="97"/>
-      <c r="ED16" s="97"/>
-      <c r="EE16" s="97"/>
-      <c r="EF16" s="97"/>
-      <c r="EG16" s="97"/>
+      <c r="BG16" s="85" t="s">
+        <v>176</v>
+      </c>
+      <c r="BH16" s="84"/>
+      <c r="BI16" s="84"/>
+      <c r="BJ16" s="84"/>
+      <c r="BK16" s="84"/>
+      <c r="BL16" s="84"/>
+      <c r="BM16" s="84"/>
+      <c r="BN16" s="84"/>
+      <c r="BO16" s="84"/>
+      <c r="BP16" s="84"/>
+      <c r="BQ16" s="83"/>
+      <c r="BR16" s="84"/>
+      <c r="BS16" s="84"/>
+      <c r="BT16" s="84"/>
+      <c r="BU16" s="84"/>
+      <c r="BV16" s="84"/>
+      <c r="BW16" s="84"/>
+      <c r="BX16" s="83"/>
+      <c r="BY16" s="84"/>
+      <c r="BZ16" s="84"/>
+      <c r="CA16" s="84"/>
+      <c r="CB16" s="84"/>
+      <c r="CC16" s="84"/>
+      <c r="CD16" s="84"/>
+      <c r="CE16" s="83"/>
+      <c r="CF16" s="84"/>
+      <c r="CG16" s="84"/>
+      <c r="CH16" s="84"/>
+      <c r="CI16" s="84"/>
+      <c r="CJ16" s="84"/>
+      <c r="CK16" s="84"/>
+      <c r="CL16" s="83"/>
+      <c r="CM16" s="84"/>
+      <c r="CN16" s="84"/>
+      <c r="CO16" s="84"/>
+      <c r="CP16" s="84"/>
+      <c r="CQ16" s="84"/>
+      <c r="CR16" s="84"/>
+      <c r="CS16" s="83"/>
+      <c r="CT16" s="84"/>
+      <c r="CU16" s="84"/>
+      <c r="CV16" s="84"/>
+      <c r="CW16" s="84"/>
+      <c r="CX16" s="84"/>
+      <c r="CY16" s="84"/>
+      <c r="CZ16" s="83"/>
+      <c r="DA16" s="84"/>
+      <c r="DB16" s="84"/>
+      <c r="DC16" s="84"/>
+      <c r="DD16" s="84"/>
+      <c r="DE16" s="84"/>
+      <c r="DF16" s="84"/>
+      <c r="DG16" s="83"/>
+      <c r="DH16" s="84"/>
+      <c r="DI16" s="84"/>
+      <c r="DJ16" s="84"/>
+      <c r="DK16" s="84"/>
+      <c r="DL16" s="84"/>
+      <c r="DM16" s="84"/>
+      <c r="DN16" s="83"/>
+      <c r="DO16" s="84"/>
+      <c r="DP16" s="84"/>
+      <c r="DQ16" s="84"/>
+      <c r="DR16" s="84"/>
+      <c r="DS16" s="84"/>
+      <c r="DT16" s="84"/>
+      <c r="DU16" s="83"/>
+      <c r="DV16" s="84"/>
+      <c r="DW16" s="84"/>
+      <c r="DX16" s="84"/>
+      <c r="DY16" s="84"/>
+      <c r="DZ16" s="84"/>
+      <c r="EA16" s="84"/>
+      <c r="EB16" s="83"/>
+      <c r="EC16" s="83"/>
+      <c r="ED16" s="83"/>
+      <c r="EE16" s="83"/>
+      <c r="EF16" s="83"/>
+      <c r="EG16" s="83"/>
     </row>
-    <row r="17" spans="1:137">
+    <row r="17" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
         <v>247</v>
       </c>
-      <c r="B17" s="85"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="85"/>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="103"/>
-      <c r="M17" s="99"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="85"/>
-      <c r="R17" s="85"/>
-      <c r="S17" s="85"/>
-      <c r="T17" s="85"/>
-      <c r="U17" s="85"/>
-      <c r="V17" s="85"/>
-      <c r="W17" s="85"/>
-      <c r="X17" s="85"/>
-      <c r="Y17" s="85"/>
-      <c r="Z17" s="85"/>
-      <c r="AA17" s="85"/>
-      <c r="AB17" s="85"/>
-      <c r="AC17" s="85"/>
-      <c r="AD17" s="87"/>
-      <c r="AE17" s="88"/>
-      <c r="AF17" s="89"/>
-      <c r="AG17" s="104"/>
-      <c r="AH17" s="88"/>
-      <c r="AI17" s="91"/>
-      <c r="AJ17" s="91"/>
-      <c r="AK17" s="91"/>
-      <c r="AL17" s="91"/>
-      <c r="AM17" s="90"/>
-      <c r="AN17" s="104"/>
-      <c r="AO17" s="88"/>
-      <c r="AP17" s="91"/>
-      <c r="AQ17" s="91"/>
-      <c r="AR17" s="92"/>
-      <c r="AS17" s="93"/>
-      <c r="AT17" s="88"/>
-      <c r="AU17" s="91"/>
-      <c r="AV17" s="91"/>
-      <c r="AW17" s="92"/>
-      <c r="AX17" s="93"/>
-      <c r="AY17" s="88"/>
-      <c r="AZ17" s="91"/>
-      <c r="BA17" s="91"/>
-      <c r="BB17" s="92"/>
-      <c r="BC17" s="93"/>
-      <c r="BD17" s="104"/>
-      <c r="BE17" s="88"/>
-      <c r="BF17" s="90"/>
-      <c r="BG17" s="88"/>
-      <c r="BH17" s="91"/>
-      <c r="BI17" s="91"/>
-      <c r="BJ17" s="91"/>
-      <c r="BK17" s="91"/>
-      <c r="BL17" s="91"/>
-      <c r="BM17" s="91"/>
-      <c r="BN17" s="91"/>
-      <c r="BO17" s="91"/>
-      <c r="BP17" s="91"/>
-      <c r="BQ17" s="97"/>
-      <c r="BR17" s="91"/>
-      <c r="BS17" s="91"/>
-      <c r="BT17" s="91"/>
-      <c r="BU17" s="91"/>
-      <c r="BV17" s="91"/>
-      <c r="BW17" s="91"/>
-      <c r="BX17" s="97"/>
-      <c r="BY17" s="91"/>
-      <c r="BZ17" s="91"/>
-      <c r="CA17" s="91"/>
-      <c r="CB17" s="91"/>
-      <c r="CC17" s="91"/>
-      <c r="CD17" s="91"/>
-      <c r="CE17" s="97"/>
-      <c r="CF17" s="91"/>
-      <c r="CG17" s="91"/>
-      <c r="CH17" s="91"/>
-      <c r="CI17" s="91"/>
-      <c r="CJ17" s="91"/>
-      <c r="CK17" s="91"/>
-      <c r="CL17" s="97"/>
-      <c r="CM17" s="91"/>
-      <c r="CN17" s="91"/>
-      <c r="CO17" s="91"/>
-      <c r="CP17" s="91"/>
-      <c r="CQ17" s="91"/>
-      <c r="CR17" s="91"/>
-      <c r="CS17" s="97"/>
-      <c r="CT17" s="91"/>
-      <c r="CU17" s="91"/>
-      <c r="CV17" s="91"/>
-      <c r="CW17" s="91"/>
-      <c r="CX17" s="91"/>
-      <c r="CY17" s="91"/>
-      <c r="CZ17" s="97"/>
-      <c r="DA17" s="91"/>
-      <c r="DB17" s="91"/>
-      <c r="DC17" s="91"/>
-      <c r="DD17" s="91"/>
-      <c r="DE17" s="91"/>
-      <c r="DF17" s="91"/>
-      <c r="DG17" s="97"/>
-      <c r="DH17" s="91"/>
-      <c r="DI17" s="91"/>
-      <c r="DJ17" s="91"/>
-      <c r="DK17" s="91"/>
-      <c r="DL17" s="91"/>
-      <c r="DM17" s="91"/>
-      <c r="DN17" s="97"/>
-      <c r="DO17" s="91"/>
-      <c r="DP17" s="91"/>
-      <c r="DQ17" s="91"/>
-      <c r="DR17" s="91"/>
-      <c r="DS17" s="91"/>
-      <c r="DT17" s="91"/>
-      <c r="DU17" s="97"/>
-      <c r="DV17" s="91"/>
-      <c r="DW17" s="91"/>
-      <c r="DX17" s="91"/>
-      <c r="DY17" s="91"/>
-      <c r="DZ17" s="91"/>
-      <c r="EA17" s="91"/>
-      <c r="EB17" s="97"/>
-      <c r="EC17" s="97"/>
-      <c r="ED17" s="97"/>
-      <c r="EE17" s="97"/>
-      <c r="EF17" s="97"/>
-      <c r="EG17" s="97"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="91"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="91"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="91"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="91"/>
+      <c r="O17" s="91"/>
+      <c r="P17" s="91"/>
+      <c r="Q17" s="91"/>
+      <c r="R17" s="91"/>
+      <c r="S17" s="91"/>
+      <c r="T17" s="91"/>
+      <c r="U17" s="91"/>
+      <c r="V17" s="91"/>
+      <c r="W17" s="91"/>
+      <c r="X17" s="91"/>
+      <c r="Y17" s="91"/>
+      <c r="Z17" s="91"/>
+      <c r="AA17" s="91"/>
+      <c r="AB17" s="91"/>
+      <c r="AC17" s="91"/>
+      <c r="AD17" s="92"/>
+      <c r="AE17" s="85"/>
+      <c r="AF17" s="93"/>
+      <c r="AG17" s="89"/>
+      <c r="AH17" s="85"/>
+      <c r="AI17" s="84"/>
+      <c r="AJ17" s="84"/>
+      <c r="AK17" s="84"/>
+      <c r="AL17" s="84"/>
+      <c r="AM17" s="86"/>
+      <c r="AN17" s="89"/>
+      <c r="AO17" s="85"/>
+      <c r="AP17" s="84"/>
+      <c r="AQ17" s="84"/>
+      <c r="AR17" s="87"/>
+      <c r="AS17" s="88"/>
+      <c r="AT17" s="85"/>
+      <c r="AU17" s="84"/>
+      <c r="AV17" s="84"/>
+      <c r="AW17" s="87"/>
+      <c r="AX17" s="88"/>
+      <c r="AY17" s="85"/>
+      <c r="AZ17" s="84"/>
+      <c r="BA17" s="84"/>
+      <c r="BB17" s="87"/>
+      <c r="BC17" s="88"/>
+      <c r="BD17" s="89"/>
+      <c r="BE17" s="85"/>
+      <c r="BF17" s="86"/>
+      <c r="BG17" s="85"/>
+      <c r="BH17" s="84"/>
+      <c r="BI17" s="84"/>
+      <c r="BJ17" s="84"/>
+      <c r="BK17" s="84"/>
+      <c r="BL17" s="84"/>
+      <c r="BM17" s="84"/>
+      <c r="BN17" s="84"/>
+      <c r="BO17" s="84"/>
+      <c r="BP17" s="84"/>
+      <c r="BQ17" s="83"/>
+      <c r="BR17" s="84"/>
+      <c r="BS17" s="84"/>
+      <c r="BT17" s="84"/>
+      <c r="BU17" s="84"/>
+      <c r="BV17" s="84"/>
+      <c r="BW17" s="84"/>
+      <c r="BX17" s="83"/>
+      <c r="BY17" s="84"/>
+      <c r="BZ17" s="84"/>
+      <c r="CA17" s="84"/>
+      <c r="CB17" s="84"/>
+      <c r="CC17" s="84"/>
+      <c r="CD17" s="84"/>
+      <c r="CE17" s="83"/>
+      <c r="CF17" s="84"/>
+      <c r="CG17" s="84"/>
+      <c r="CH17" s="84"/>
+      <c r="CI17" s="84"/>
+      <c r="CJ17" s="84"/>
+      <c r="CK17" s="84"/>
+      <c r="CL17" s="83"/>
+      <c r="CM17" s="84"/>
+      <c r="CN17" s="84"/>
+      <c r="CO17" s="84"/>
+      <c r="CP17" s="84"/>
+      <c r="CQ17" s="84"/>
+      <c r="CR17" s="84"/>
+      <c r="CS17" s="83"/>
+      <c r="CT17" s="84"/>
+      <c r="CU17" s="84"/>
+      <c r="CV17" s="84"/>
+      <c r="CW17" s="84"/>
+      <c r="CX17" s="84"/>
+      <c r="CY17" s="84"/>
+      <c r="CZ17" s="83"/>
+      <c r="DA17" s="84"/>
+      <c r="DB17" s="84"/>
+      <c r="DC17" s="84"/>
+      <c r="DD17" s="84"/>
+      <c r="DE17" s="84"/>
+      <c r="DF17" s="84"/>
+      <c r="DG17" s="83"/>
+      <c r="DH17" s="84"/>
+      <c r="DI17" s="84"/>
+      <c r="DJ17" s="84"/>
+      <c r="DK17" s="84"/>
+      <c r="DL17" s="84"/>
+      <c r="DM17" s="84"/>
+      <c r="DN17" s="83"/>
+      <c r="DO17" s="84"/>
+      <c r="DP17" s="84"/>
+      <c r="DQ17" s="84"/>
+      <c r="DR17" s="84"/>
+      <c r="DS17" s="84"/>
+      <c r="DT17" s="84"/>
+      <c r="DU17" s="83"/>
+      <c r="DV17" s="84"/>
+      <c r="DW17" s="84"/>
+      <c r="DX17" s="84"/>
+      <c r="DY17" s="84"/>
+      <c r="DZ17" s="84"/>
+      <c r="EA17" s="84"/>
+      <c r="EB17" s="83"/>
+      <c r="EC17" s="83"/>
+      <c r="ED17" s="83"/>
+      <c r="EE17" s="83"/>
+      <c r="EF17" s="83"/>
+      <c r="EG17" s="83"/>
     </row>
-    <row r="18" spans="1:137">
+    <row r="18" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -35694,7 +35700,7 @@
       <c r="EF18" s="3"/>
       <c r="EG18" s="3"/>
     </row>
-    <row r="19" spans="1:137">
+    <row r="19" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>195</v>
@@ -35935,7 +35941,7 @@
       <c r="EF19" s="3"/>
       <c r="EG19" s="3"/>
     </row>
-    <row r="20" spans="1:137">
+    <row r="20" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2026</v>
       </c>
@@ -36091,8 +36097,8 @@
       <c r="BC20" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD20" s="97"/>
-      <c r="BE20" s="97"/>
+      <c r="BD20" s="83"/>
+      <c r="BE20" s="83"/>
       <c r="BF20" s="38" t="s">
         <v>176</v>
       </c>
@@ -36176,7 +36182,7 @@
       <c r="EF20" s="3"/>
       <c r="EG20" s="3"/>
     </row>
-    <row r="21" spans="1:137">
+    <row r="21" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>2027</v>
       </c>
@@ -36332,8 +36338,8 @@
       <c r="BC21" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD21" s="97"/>
-      <c r="BE21" s="97"/>
+      <c r="BD21" s="83"/>
+      <c r="BE21" s="83"/>
       <c r="BF21" s="38" t="s">
         <v>176</v>
       </c>
@@ -36417,7 +36423,7 @@
       <c r="EF21" s="3"/>
       <c r="EG21" s="3"/>
     </row>
-    <row r="22" spans="1:137">
+    <row r="22" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>2028</v>
       </c>
@@ -36573,8 +36579,8 @@
       <c r="BC22" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD22" s="97"/>
-      <c r="BE22" s="97"/>
+      <c r="BD22" s="83"/>
+      <c r="BE22" s="83"/>
       <c r="BF22" s="38" t="s">
         <v>176</v>
       </c>
@@ -36658,7 +36664,7 @@
       <c r="EF22" s="3"/>
       <c r="EG22" s="3"/>
     </row>
-    <row r="23" spans="1:137">
+    <row r="23" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>2029</v>
       </c>
@@ -36814,8 +36820,8 @@
       <c r="BC23" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD23" s="97"/>
-      <c r="BE23" s="97"/>
+      <c r="BD23" s="83"/>
+      <c r="BE23" s="83"/>
       <c r="BF23" s="38" t="s">
         <v>176</v>
       </c>
@@ -36899,7 +36905,7 @@
       <c r="EF23" s="3"/>
       <c r="EG23" s="3"/>
     </row>
-    <row r="24" spans="1:137">
+    <row r="24" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>2030</v>
       </c>
@@ -37055,8 +37061,8 @@
       <c r="BC24" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD24" s="97"/>
-      <c r="BE24" s="97"/>
+      <c r="BD24" s="83"/>
+      <c r="BE24" s="83"/>
       <c r="BF24" s="38" t="s">
         <v>176</v>
       </c>
@@ -37140,7 +37146,7 @@
       <c r="EF24" s="3"/>
       <c r="EG24" s="3"/>
     </row>
-    <row r="25" spans="1:137">
+    <row r="25" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>2031</v>
       </c>
@@ -37296,8 +37302,8 @@
       <c r="BC25" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD25" s="97"/>
-      <c r="BE25" s="97"/>
+      <c r="BD25" s="83"/>
+      <c r="BE25" s="83"/>
       <c r="BF25" s="38" t="s">
         <v>176</v>
       </c>
@@ -37381,7 +37387,7 @@
       <c r="EF25" s="3"/>
       <c r="EG25" s="3"/>
     </row>
-    <row r="26" spans="1:137">
+    <row r="26" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>2032</v>
       </c>
@@ -37537,8 +37543,8 @@
       <c r="BC26" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD26" s="97"/>
-      <c r="BE26" s="97"/>
+      <c r="BD26" s="83"/>
+      <c r="BE26" s="83"/>
       <c r="BF26" s="38" t="s">
         <v>176</v>
       </c>
@@ -37622,7 +37628,7 @@
       <c r="EF26" s="3"/>
       <c r="EG26" s="3"/>
     </row>
-    <row r="27" spans="1:137">
+    <row r="27" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>2033</v>
       </c>
@@ -37778,8 +37784,8 @@
       <c r="BC27" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD27" s="97"/>
-      <c r="BE27" s="97"/>
+      <c r="BD27" s="83"/>
+      <c r="BE27" s="83"/>
       <c r="BF27" s="38" t="s">
         <v>176</v>
       </c>
@@ -37863,7 +37869,7 @@
       <c r="EF27" s="3"/>
       <c r="EG27" s="3"/>
     </row>
-    <row r="28" spans="1:137">
+    <row r="28" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>2034</v>
       </c>
@@ -38019,8 +38025,8 @@
       <c r="BC28" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD28" s="97"/>
-      <c r="BE28" s="97"/>
+      <c r="BD28" s="83"/>
+      <c r="BE28" s="83"/>
       <c r="BF28" s="38" t="s">
         <v>176</v>
       </c>
@@ -38104,7 +38110,7 @@
       <c r="EF28" s="3"/>
       <c r="EG28" s="3"/>
     </row>
-    <row r="29" spans="1:137">
+    <row r="29" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>2035</v>
       </c>
@@ -38260,8 +38266,8 @@
       <c r="BC29" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD29" s="97"/>
-      <c r="BE29" s="97"/>
+      <c r="BD29" s="83"/>
+      <c r="BE29" s="83"/>
       <c r="BF29" s="38" t="s">
         <v>176</v>
       </c>
@@ -38345,7 +38351,7 @@
       <c r="EF29" s="3"/>
       <c r="EG29" s="3"/>
     </row>
-    <row r="30" spans="1:137">
+    <row r="30" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>2036</v>
       </c>
@@ -38501,8 +38507,8 @@
       <c r="BC30" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD30" s="97"/>
-      <c r="BE30" s="97"/>
+      <c r="BD30" s="83"/>
+      <c r="BE30" s="83"/>
       <c r="BF30" s="38" t="s">
         <v>176</v>
       </c>
@@ -38586,7 +38592,7 @@
       <c r="EF30" s="3"/>
       <c r="EG30" s="3"/>
     </row>
-    <row r="31" spans="1:137">
+    <row r="31" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>2037</v>
       </c>
@@ -38742,8 +38748,8 @@
       <c r="BC31" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD31" s="97"/>
-      <c r="BE31" s="97"/>
+      <c r="BD31" s="83"/>
+      <c r="BE31" s="83"/>
       <c r="BF31" s="38" t="s">
         <v>176</v>
       </c>
@@ -38827,7 +38833,7 @@
       <c r="EF31" s="3"/>
       <c r="EG31" s="3"/>
     </row>
-    <row r="32" spans="1:137">
+    <row r="32" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>2038</v>
       </c>
@@ -38983,8 +38989,8 @@
       <c r="BC32" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD32" s="97"/>
-      <c r="BE32" s="97"/>
+      <c r="BD32" s="83"/>
+      <c r="BE32" s="83"/>
       <c r="BF32" s="38" t="s">
         <v>176</v>
       </c>
@@ -39068,7 +39074,7 @@
       <c r="EF32" s="3"/>
       <c r="EG32" s="3"/>
     </row>
-    <row r="33" spans="1:137">
+    <row r="33" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>2039</v>
       </c>
@@ -39224,8 +39230,8 @@
       <c r="BC33" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD33" s="97"/>
-      <c r="BE33" s="97"/>
+      <c r="BD33" s="83"/>
+      <c r="BE33" s="83"/>
       <c r="BF33" s="38" t="s">
         <v>176</v>
       </c>
@@ -39309,7 +39315,7 @@
       <c r="EF33" s="3"/>
       <c r="EG33" s="3"/>
     </row>
-    <row r="34" spans="1:137">
+    <row r="34" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>2040</v>
       </c>
@@ -39465,8 +39471,8 @@
       <c r="BC34" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD34" s="97"/>
-      <c r="BE34" s="97"/>
+      <c r="BD34" s="83"/>
+      <c r="BE34" s="83"/>
       <c r="BF34" s="38" t="s">
         <v>176</v>
       </c>
@@ -39550,7 +39556,7 @@
       <c r="EF34" s="3"/>
       <c r="EG34" s="3"/>
     </row>
-    <row r="35" spans="1:137">
+    <row r="35" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>2041</v>
       </c>
@@ -39706,8 +39712,8 @@
       <c r="BC35" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD35" s="97"/>
-      <c r="BE35" s="97"/>
+      <c r="BD35" s="83"/>
+      <c r="BE35" s="83"/>
       <c r="BF35" s="38" t="s">
         <v>176</v>
       </c>
@@ -39791,7 +39797,7 @@
       <c r="EF35" s="3"/>
       <c r="EG35" s="3"/>
     </row>
-    <row r="36" spans="1:137">
+    <row r="36" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>2042</v>
       </c>
@@ -39947,8 +39953,8 @@
       <c r="BC36" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD36" s="97"/>
-      <c r="BE36" s="97"/>
+      <c r="BD36" s="83"/>
+      <c r="BE36" s="83"/>
       <c r="BF36" s="38" t="s">
         <v>176</v>
       </c>
@@ -40032,7 +40038,7 @@
       <c r="EF36" s="3"/>
       <c r="EG36" s="3"/>
     </row>
-    <row r="37" spans="1:137">
+    <row r="37" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>2043</v>
       </c>
@@ -40188,8 +40194,8 @@
       <c r="BC37" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD37" s="97"/>
-      <c r="BE37" s="97"/>
+      <c r="BD37" s="83"/>
+      <c r="BE37" s="83"/>
       <c r="BF37" s="38" t="s">
         <v>176</v>
       </c>
@@ -40273,7 +40279,7 @@
       <c r="EF37" s="3"/>
       <c r="EG37" s="3"/>
     </row>
-    <row r="38" spans="1:137">
+    <row r="38" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>2044</v>
       </c>
@@ -40429,8 +40435,8 @@
       <c r="BC38" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD38" s="97"/>
-      <c r="BE38" s="97"/>
+      <c r="BD38" s="83"/>
+      <c r="BE38" s="83"/>
       <c r="BF38" s="38" t="s">
         <v>176</v>
       </c>
@@ -40514,7 +40520,7 @@
       <c r="EF38" s="3"/>
       <c r="EG38" s="3"/>
     </row>
-    <row r="39" spans="1:137">
+    <row r="39" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>2045</v>
       </c>
@@ -40670,8 +40676,8 @@
       <c r="BC39" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD39" s="97"/>
-      <c r="BE39" s="97"/>
+      <c r="BD39" s="83"/>
+      <c r="BE39" s="83"/>
       <c r="BF39" s="38" t="s">
         <v>176</v>
       </c>
@@ -40755,7 +40761,7 @@
       <c r="EF39" s="3"/>
       <c r="EG39" s="3"/>
     </row>
-    <row r="40" spans="1:137">
+    <row r="40" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>2046</v>
       </c>
@@ -40911,8 +40917,8 @@
       <c r="BC40" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD40" s="97"/>
-      <c r="BE40" s="97"/>
+      <c r="BD40" s="83"/>
+      <c r="BE40" s="83"/>
       <c r="BF40" s="38" t="s">
         <v>176</v>
       </c>
@@ -40996,7 +41002,7 @@
       <c r="EF40" s="3"/>
       <c r="EG40" s="3"/>
     </row>
-    <row r="41" spans="1:137">
+    <row r="41" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>2047</v>
       </c>
@@ -41152,8 +41158,8 @@
       <c r="BC41" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD41" s="97"/>
-      <c r="BE41" s="97"/>
+      <c r="BD41" s="83"/>
+      <c r="BE41" s="83"/>
       <c r="BF41" s="38" t="s">
         <v>176</v>
       </c>
@@ -41237,7 +41243,7 @@
       <c r="EF41" s="3"/>
       <c r="EG41" s="3"/>
     </row>
-    <row r="42" spans="1:137">
+    <row r="42" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>2048</v>
       </c>
@@ -41393,8 +41399,8 @@
       <c r="BC42" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD42" s="97"/>
-      <c r="BE42" s="97"/>
+      <c r="BD42" s="83"/>
+      <c r="BE42" s="83"/>
       <c r="BF42" s="38" t="s">
         <v>176</v>
       </c>
@@ -41478,7 +41484,7 @@
       <c r="EF42" s="3"/>
       <c r="EG42" s="3"/>
     </row>
-    <row r="43" spans="1:137">
+    <row r="43" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>2049</v>
       </c>
@@ -41634,8 +41640,8 @@
       <c r="BC43" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD43" s="97"/>
-      <c r="BE43" s="97"/>
+      <c r="BD43" s="83"/>
+      <c r="BE43" s="83"/>
       <c r="BF43" s="38" t="s">
         <v>176</v>
       </c>
@@ -41719,7 +41725,7 @@
       <c r="EF43" s="3"/>
       <c r="EG43" s="3"/>
     </row>
-    <row r="44" spans="1:137">
+    <row r="44" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>2050</v>
       </c>
@@ -41875,8 +41881,8 @@
       <c r="BC44" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD44" s="97"/>
-      <c r="BE44" s="97"/>
+      <c r="BD44" s="83"/>
+      <c r="BE44" s="83"/>
       <c r="BF44" s="38" t="s">
         <v>176</v>
       </c>
@@ -41960,7 +41966,7 @@
       <c r="EF44" s="3"/>
       <c r="EG44" s="3"/>
     </row>
-    <row r="45" spans="1:137">
+    <row r="45" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>2051</v>
       </c>
@@ -42116,8 +42122,8 @@
       <c r="BC45" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD45" s="97"/>
-      <c r="BE45" s="97"/>
+      <c r="BD45" s="83"/>
+      <c r="BE45" s="83"/>
       <c r="BF45" s="38" t="s">
         <v>176</v>
       </c>
@@ -42201,7 +42207,7 @@
       <c r="EF45" s="3"/>
       <c r="EG45" s="3"/>
     </row>
-    <row r="46" spans="1:137">
+    <row r="46" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>2052</v>
       </c>
@@ -42357,8 +42363,8 @@
       <c r="BC46" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD46" s="97"/>
-      <c r="BE46" s="97"/>
+      <c r="BD46" s="83"/>
+      <c r="BE46" s="83"/>
       <c r="BF46" s="38" t="s">
         <v>176</v>
       </c>
@@ -42442,7 +42448,7 @@
       <c r="EF46" s="3"/>
       <c r="EG46" s="3"/>
     </row>
-    <row r="47" spans="1:137">
+    <row r="47" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>2053</v>
       </c>
@@ -42598,8 +42604,8 @@
       <c r="BC47" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD47" s="97"/>
-      <c r="BE47" s="97"/>
+      <c r="BD47" s="83"/>
+      <c r="BE47" s="83"/>
       <c r="BF47" s="38" t="s">
         <v>176</v>
       </c>
@@ -42683,7 +42689,7 @@
       <c r="EF47" s="3"/>
       <c r="EG47" s="3"/>
     </row>
-    <row r="48" spans="1:137">
+    <row r="48" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>2054</v>
       </c>
@@ -42839,8 +42845,8 @@
       <c r="BC48" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD48" s="97"/>
-      <c r="BE48" s="97"/>
+      <c r="BD48" s="83"/>
+      <c r="BE48" s="83"/>
       <c r="BF48" s="38" t="s">
         <v>176</v>
       </c>
@@ -42924,7 +42930,7 @@
       <c r="EF48" s="3"/>
       <c r="EG48" s="3"/>
     </row>
-    <row r="49" spans="1:137">
+    <row r="49" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>2055</v>
       </c>
@@ -43080,8 +43086,8 @@
       <c r="BC49" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD49" s="97"/>
-      <c r="BE49" s="97"/>
+      <c r="BD49" s="83"/>
+      <c r="BE49" s="83"/>
       <c r="BF49" s="38" t="s">
         <v>176</v>
       </c>
@@ -43165,7 +43171,7 @@
       <c r="EF49" s="3"/>
       <c r="EG49" s="3"/>
     </row>
-    <row r="50" spans="1:137">
+    <row r="50" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>2056</v>
       </c>
@@ -43321,8 +43327,8 @@
       <c r="BC50" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD50" s="97"/>
-      <c r="BE50" s="97"/>
+      <c r="BD50" s="83"/>
+      <c r="BE50" s="83"/>
       <c r="BF50" s="38" t="s">
         <v>176</v>
       </c>
@@ -43406,7 +43412,7 @@
       <c r="EF50" s="3"/>
       <c r="EG50" s="3"/>
     </row>
-    <row r="51" spans="1:137">
+    <row r="51" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>2057</v>
       </c>
@@ -43562,8 +43568,8 @@
       <c r="BC51" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD51" s="97"/>
-      <c r="BE51" s="97"/>
+      <c r="BD51" s="83"/>
+      <c r="BE51" s="83"/>
       <c r="BF51" s="38" t="s">
         <v>176</v>
       </c>
@@ -43647,7 +43653,7 @@
       <c r="EF51" s="3"/>
       <c r="EG51" s="3"/>
     </row>
-    <row r="52" spans="1:137">
+    <row r="52" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>2058</v>
       </c>
@@ -43803,8 +43809,8 @@
       <c r="BC52" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD52" s="97"/>
-      <c r="BE52" s="97"/>
+      <c r="BD52" s="83"/>
+      <c r="BE52" s="83"/>
       <c r="BF52" s="38" t="s">
         <v>176</v>
       </c>
@@ -43888,7 +43894,7 @@
       <c r="EF52" s="3"/>
       <c r="EG52" s="3"/>
     </row>
-    <row r="53" spans="1:137">
+    <row r="53" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>2059</v>
       </c>
@@ -44044,8 +44050,8 @@
       <c r="BC53" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD53" s="97"/>
-      <c r="BE53" s="97"/>
+      <c r="BD53" s="83"/>
+      <c r="BE53" s="83"/>
       <c r="BF53" s="38" t="s">
         <v>176</v>
       </c>
@@ -44129,7 +44135,7 @@
       <c r="EF53" s="3"/>
       <c r="EG53" s="3"/>
     </row>
-    <row r="54" spans="1:137">
+    <row r="54" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>2060</v>
       </c>
@@ -44285,8 +44291,8 @@
       <c r="BC54" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD54" s="97"/>
-      <c r="BE54" s="97"/>
+      <c r="BD54" s="83"/>
+      <c r="BE54" s="83"/>
       <c r="BF54" s="38" t="s">
         <v>176</v>
       </c>
@@ -44370,7 +44376,7 @@
       <c r="EF54" s="3"/>
       <c r="EG54" s="3"/>
     </row>
-    <row r="55" spans="1:137">
+    <row r="55" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>2061</v>
       </c>
@@ -44526,8 +44532,8 @@
       <c r="BC55" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD55" s="97"/>
-      <c r="BE55" s="97"/>
+      <c r="BD55" s="83"/>
+      <c r="BE55" s="83"/>
       <c r="BF55" s="38" t="s">
         <v>176</v>
       </c>
@@ -44611,7 +44617,7 @@
       <c r="EF55" s="3"/>
       <c r="EG55" s="3"/>
     </row>
-    <row r="56" spans="1:137">
+    <row r="56" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>2062</v>
       </c>
@@ -44767,8 +44773,8 @@
       <c r="BC56" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD56" s="97"/>
-      <c r="BE56" s="97"/>
+      <c r="BD56" s="83"/>
+      <c r="BE56" s="83"/>
       <c r="BF56" s="38" t="s">
         <v>176</v>
       </c>
@@ -44852,7 +44858,7 @@
       <c r="EF56" s="3"/>
       <c r="EG56" s="3"/>
     </row>
-    <row r="57" spans="1:137">
+    <row r="57" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>2063</v>
       </c>
@@ -45008,8 +45014,8 @@
       <c r="BC57" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD57" s="97"/>
-      <c r="BE57" s="97"/>
+      <c r="BD57" s="83"/>
+      <c r="BE57" s="83"/>
       <c r="BF57" s="38" t="s">
         <v>176</v>
       </c>
@@ -45093,7 +45099,7 @@
       <c r="EF57" s="3"/>
       <c r="EG57" s="3"/>
     </row>
-    <row r="58" spans="1:137">
+    <row r="58" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>2064</v>
       </c>
@@ -45249,8 +45255,8 @@
       <c r="BC58" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD58" s="97"/>
-      <c r="BE58" s="97"/>
+      <c r="BD58" s="83"/>
+      <c r="BE58" s="83"/>
       <c r="BF58" s="38" t="s">
         <v>176</v>
       </c>
@@ -45334,7 +45340,7 @@
       <c r="EF58" s="3"/>
       <c r="EG58" s="3"/>
     </row>
-    <row r="59" spans="1:137">
+    <row r="59" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>2065</v>
       </c>
@@ -45490,8 +45496,8 @@
       <c r="BC59" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD59" s="97"/>
-      <c r="BE59" s="97"/>
+      <c r="BD59" s="83"/>
+      <c r="BE59" s="83"/>
       <c r="BF59" s="38" t="s">
         <v>176</v>
       </c>
@@ -45575,7 +45581,7 @@
       <c r="EF59" s="3"/>
       <c r="EG59" s="3"/>
     </row>
-    <row r="60" spans="1:137">
+    <row r="60" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>2066</v>
       </c>
@@ -45731,8 +45737,8 @@
       <c r="BC60" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD60" s="97"/>
-      <c r="BE60" s="97"/>
+      <c r="BD60" s="83"/>
+      <c r="BE60" s="83"/>
       <c r="BF60" s="38" t="s">
         <v>176</v>
       </c>
@@ -45816,7 +45822,7 @@
       <c r="EF60" s="3"/>
       <c r="EG60" s="3"/>
     </row>
-    <row r="61" spans="1:137">
+    <row r="61" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>2067</v>
       </c>
@@ -45972,8 +45978,8 @@
       <c r="BC61" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD61" s="97"/>
-      <c r="BE61" s="97"/>
+      <c r="BD61" s="83"/>
+      <c r="BE61" s="83"/>
       <c r="BF61" s="38" t="s">
         <v>176</v>
       </c>
@@ -46057,7 +46063,7 @@
       <c r="EF61" s="3"/>
       <c r="EG61" s="3"/>
     </row>
-    <row r="62" spans="1:137">
+    <row r="62" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>2068</v>
       </c>
@@ -46213,8 +46219,8 @@
       <c r="BC62" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD62" s="97"/>
-      <c r="BE62" s="97"/>
+      <c r="BD62" s="83"/>
+      <c r="BE62" s="83"/>
       <c r="BF62" s="38" t="s">
         <v>176</v>
       </c>
@@ -46298,7 +46304,7 @@
       <c r="EF62" s="3"/>
       <c r="EG62" s="3"/>
     </row>
-    <row r="63" spans="1:137">
+    <row r="63" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>2069</v>
       </c>
@@ -46454,8 +46460,8 @@
       <c r="BC63" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD63" s="97"/>
-      <c r="BE63" s="97"/>
+      <c r="BD63" s="83"/>
+      <c r="BE63" s="83"/>
       <c r="BF63" s="38" t="s">
         <v>176</v>
       </c>
@@ -46539,7 +46545,7 @@
       <c r="EF63" s="3"/>
       <c r="EG63" s="3"/>
     </row>
-    <row r="64" spans="1:137">
+    <row r="64" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>2070</v>
       </c>
@@ -46695,8 +46701,8 @@
       <c r="BC64" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD64" s="97"/>
-      <c r="BE64" s="97"/>
+      <c r="BD64" s="83"/>
+      <c r="BE64" s="83"/>
       <c r="BF64" s="38" t="s">
         <v>176</v>
       </c>
@@ -46780,7 +46786,7 @@
       <c r="EF64" s="3"/>
       <c r="EG64" s="3"/>
     </row>
-    <row r="65" spans="1:137">
+    <row r="65" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>2071</v>
       </c>
@@ -46936,8 +46942,8 @@
       <c r="BC65" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD65" s="97"/>
-      <c r="BE65" s="97"/>
+      <c r="BD65" s="83"/>
+      <c r="BE65" s="83"/>
       <c r="BF65" s="38" t="s">
         <v>176</v>
       </c>
@@ -47021,7 +47027,7 @@
       <c r="EF65" s="3"/>
       <c r="EG65" s="3"/>
     </row>
-    <row r="66" spans="1:137">
+    <row r="66" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>2072</v>
       </c>
@@ -47177,8 +47183,8 @@
       <c r="BC66" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD66" s="97"/>
-      <c r="BE66" s="97"/>
+      <c r="BD66" s="83"/>
+      <c r="BE66" s="83"/>
       <c r="BF66" s="38" t="s">
         <v>176</v>
       </c>
@@ -47262,7 +47268,7 @@
       <c r="EF66" s="3"/>
       <c r="EG66" s="3"/>
     </row>
-    <row r="67" spans="1:137">
+    <row r="67" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>2073</v>
       </c>
@@ -47418,8 +47424,8 @@
       <c r="BC67" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD67" s="97"/>
-      <c r="BE67" s="97"/>
+      <c r="BD67" s="83"/>
+      <c r="BE67" s="83"/>
       <c r="BF67" s="38" t="s">
         <v>176</v>
       </c>
@@ -47503,7 +47509,7 @@
       <c r="EF67" s="3"/>
       <c r="EG67" s="3"/>
     </row>
-    <row r="68" spans="1:137">
+    <row r="68" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>2074</v>
       </c>
@@ -47659,8 +47665,8 @@
       <c r="BC68" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD68" s="97"/>
-      <c r="BE68" s="97"/>
+      <c r="BD68" s="83"/>
+      <c r="BE68" s="83"/>
       <c r="BF68" s="38" t="s">
         <v>176</v>
       </c>
@@ -47744,7 +47750,7 @@
       <c r="EF68" s="3"/>
       <c r="EG68" s="3"/>
     </row>
-    <row r="69" spans="1:137">
+    <row r="69" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>2075</v>
       </c>
@@ -47900,8 +47906,8 @@
       <c r="BC69" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="BD69" s="97"/>
-      <c r="BE69" s="97"/>
+      <c r="BD69" s="83"/>
+      <c r="BE69" s="83"/>
       <c r="BF69" s="38" t="s">
         <v>176</v>
       </c>
@@ -47985,7 +47991,7 @@
       <c r="EF69" s="3"/>
       <c r="EG69" s="3"/>
     </row>
-    <row r="70" spans="1:137">
+    <row r="70" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -48041,8 +48047,8 @@
       <c r="BA70" s="3"/>
       <c r="BB70" s="3"/>
       <c r="BC70" s="3"/>
-      <c r="BD70" s="97"/>
-      <c r="BE70" s="97"/>
+      <c r="BD70" s="83"/>
+      <c r="BE70" s="83"/>
       <c r="BF70" s="3"/>
       <c r="BG70" s="3"/>
       <c r="BH70" s="3"/>
@@ -48124,7 +48130,7 @@
       <c r="EF70" s="3"/>
       <c r="EG70" s="3"/>
     </row>
-    <row r="71" spans="1:137">
+    <row r="71" spans="1:137" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -48180,8 +48186,8 @@
       <c r="BA71" s="3"/>
       <c r="BB71" s="3"/>
       <c r="BC71" s="3"/>
-      <c r="BD71" s="97"/>
-      <c r="BE71" s="97"/>
+      <c r="BD71" s="83"/>
+      <c r="BE71" s="83"/>
       <c r="BF71" s="3"/>
       <c r="BG71" s="3"/>
       <c r="BH71" s="3"/>
@@ -48265,55 +48271,182 @@
     </row>
   </sheetData>
   <mergeCells count="249">
-    <mergeCell ref="BD71:BE71"/>
-    <mergeCell ref="BD65:BE65"/>
-    <mergeCell ref="BD66:BE66"/>
-    <mergeCell ref="BD67:BE67"/>
-    <mergeCell ref="BD68:BE68"/>
-    <mergeCell ref="BD69:BE69"/>
-    <mergeCell ref="BD70:BE70"/>
-    <mergeCell ref="BD59:BE59"/>
-    <mergeCell ref="BD60:BE60"/>
-    <mergeCell ref="BD61:BE61"/>
-    <mergeCell ref="BD62:BE62"/>
-    <mergeCell ref="BD63:BE63"/>
-    <mergeCell ref="BD64:BE64"/>
-    <mergeCell ref="BD53:BE53"/>
-    <mergeCell ref="BD54:BE54"/>
-    <mergeCell ref="BD55:BE55"/>
-    <mergeCell ref="BD56:BE56"/>
-    <mergeCell ref="BD57:BE57"/>
-    <mergeCell ref="BD58:BE58"/>
-    <mergeCell ref="BD47:BE47"/>
-    <mergeCell ref="BD48:BE48"/>
-    <mergeCell ref="BD49:BE49"/>
-    <mergeCell ref="BD50:BE50"/>
-    <mergeCell ref="BD51:BE51"/>
-    <mergeCell ref="BD52:BE52"/>
-    <mergeCell ref="BD41:BE41"/>
-    <mergeCell ref="BD42:BE42"/>
-    <mergeCell ref="BD43:BE43"/>
-    <mergeCell ref="BD44:BE44"/>
-    <mergeCell ref="BD45:BE45"/>
-    <mergeCell ref="BD46:BE46"/>
-    <mergeCell ref="BD35:BE35"/>
-    <mergeCell ref="BD36:BE36"/>
-    <mergeCell ref="BD37:BE37"/>
-    <mergeCell ref="BD38:BE38"/>
-    <mergeCell ref="BD39:BE39"/>
-    <mergeCell ref="BD40:BE40"/>
-    <mergeCell ref="BD29:BE29"/>
-    <mergeCell ref="BD30:BE30"/>
-    <mergeCell ref="BD31:BE31"/>
-    <mergeCell ref="BD32:BE32"/>
-    <mergeCell ref="BD33:BE33"/>
-    <mergeCell ref="BD34:BE34"/>
-    <mergeCell ref="BD23:BE23"/>
-    <mergeCell ref="BD24:BE24"/>
-    <mergeCell ref="BD25:BE25"/>
-    <mergeCell ref="BD26:BE26"/>
-    <mergeCell ref="BD27:BE27"/>
-    <mergeCell ref="BD28:BE28"/>
+    <mergeCell ref="E1:J1"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="AN2:AO2"/>
+    <mergeCell ref="BD2:BE2"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="AN3:AO3"/>
+    <mergeCell ref="BD3:BE3"/>
+    <mergeCell ref="AD4:AE4"/>
+    <mergeCell ref="AF4:AG4"/>
+    <mergeCell ref="AL4:AM4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="BD4:BE4"/>
+    <mergeCell ref="AD7:AE7"/>
+    <mergeCell ref="AF7:AG7"/>
+    <mergeCell ref="BD7:BE7"/>
+    <mergeCell ref="AD8:AE8"/>
+    <mergeCell ref="AF8:AG8"/>
+    <mergeCell ref="BD8:BE8"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="AF5:AG5"/>
+    <mergeCell ref="BD5:BE5"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="AF6:AG6"/>
+    <mergeCell ref="BD6:BE6"/>
+    <mergeCell ref="AD9:AE9"/>
+    <mergeCell ref="AF9:AG9"/>
+    <mergeCell ref="AN9:AO9"/>
+    <mergeCell ref="BD9:BE9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="AC10:AD10"/>
+    <mergeCell ref="AF10:AG10"/>
+    <mergeCell ref="AN10:AO10"/>
+    <mergeCell ref="BD10:BE10"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="AC13:AD13"/>
+    <mergeCell ref="AF13:AG13"/>
+    <mergeCell ref="AN13:AO13"/>
+    <mergeCell ref="BD13:BE13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="AC14:AD14"/>
+    <mergeCell ref="AF14:AG14"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="AC11:AD11"/>
+    <mergeCell ref="AF11:AG11"/>
+    <mergeCell ref="AN11:AO11"/>
+    <mergeCell ref="BD11:BE11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="AD12:AE12"/>
+    <mergeCell ref="AF12:AG12"/>
+    <mergeCell ref="AN12:AO12"/>
+    <mergeCell ref="BD12:BE12"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="AC15:AD15"/>
+    <mergeCell ref="AF15:AG15"/>
+    <mergeCell ref="BE15:BF15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="O16:O17"/>
+    <mergeCell ref="P16:P17"/>
+    <mergeCell ref="Q16:Q17"/>
+    <mergeCell ref="R16:R17"/>
+    <mergeCell ref="S16:S17"/>
+    <mergeCell ref="T16:T17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="I16:I17"/>
+    <mergeCell ref="J16:J17"/>
+    <mergeCell ref="K16:K17"/>
+    <mergeCell ref="L16:M17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="AA16:AA17"/>
+    <mergeCell ref="AB16:AB17"/>
+    <mergeCell ref="AC16:AC17"/>
+    <mergeCell ref="AD16:AD17"/>
+    <mergeCell ref="AE16:AE17"/>
+    <mergeCell ref="AF16:AF17"/>
+    <mergeCell ref="U16:U17"/>
+    <mergeCell ref="V16:V17"/>
+    <mergeCell ref="W16:W17"/>
+    <mergeCell ref="X16:X17"/>
+    <mergeCell ref="Y16:Y17"/>
+    <mergeCell ref="Z16:Z17"/>
+    <mergeCell ref="AM16:AM17"/>
+    <mergeCell ref="AN16:AN17"/>
+    <mergeCell ref="AO16:AO17"/>
+    <mergeCell ref="AP16:AP17"/>
+    <mergeCell ref="AQ16:AQ17"/>
+    <mergeCell ref="AR16:AR17"/>
+    <mergeCell ref="AG16:AG17"/>
+    <mergeCell ref="AH16:AH17"/>
+    <mergeCell ref="AI16:AI17"/>
+    <mergeCell ref="AJ16:AJ17"/>
+    <mergeCell ref="AK16:AK17"/>
+    <mergeCell ref="AL16:AL17"/>
+    <mergeCell ref="AY16:AY17"/>
+    <mergeCell ref="AZ16:AZ17"/>
+    <mergeCell ref="BA16:BA17"/>
+    <mergeCell ref="BB16:BB17"/>
+    <mergeCell ref="BC16:BC17"/>
+    <mergeCell ref="BD16:BD17"/>
+    <mergeCell ref="AS16:AS17"/>
+    <mergeCell ref="AT16:AT17"/>
+    <mergeCell ref="AU16:AU17"/>
+    <mergeCell ref="AV16:AV17"/>
+    <mergeCell ref="AW16:AW17"/>
+    <mergeCell ref="AX16:AX17"/>
+    <mergeCell ref="BK16:BK17"/>
+    <mergeCell ref="BL16:BL17"/>
+    <mergeCell ref="BM16:BM17"/>
+    <mergeCell ref="BN16:BN17"/>
+    <mergeCell ref="BO16:BO17"/>
+    <mergeCell ref="BP16:BP17"/>
+    <mergeCell ref="BE16:BE17"/>
+    <mergeCell ref="BF16:BF17"/>
+    <mergeCell ref="BG16:BG17"/>
+    <mergeCell ref="BH16:BH17"/>
+    <mergeCell ref="BI16:BI17"/>
+    <mergeCell ref="BJ16:BJ17"/>
+    <mergeCell ref="BW16:BW17"/>
+    <mergeCell ref="BX16:BX17"/>
+    <mergeCell ref="BY16:BY17"/>
+    <mergeCell ref="BZ16:BZ17"/>
+    <mergeCell ref="CA16:CA17"/>
+    <mergeCell ref="CB16:CB17"/>
+    <mergeCell ref="BQ16:BQ17"/>
+    <mergeCell ref="BR16:BR17"/>
+    <mergeCell ref="BS16:BS17"/>
+    <mergeCell ref="BT16:BT17"/>
+    <mergeCell ref="BU16:BU17"/>
+    <mergeCell ref="BV16:BV17"/>
+    <mergeCell ref="CI16:CI17"/>
+    <mergeCell ref="CJ16:CJ17"/>
+    <mergeCell ref="CK16:CK17"/>
+    <mergeCell ref="CL16:CL17"/>
+    <mergeCell ref="CM16:CM17"/>
+    <mergeCell ref="CN16:CN17"/>
+    <mergeCell ref="CC16:CC17"/>
+    <mergeCell ref="CD16:CD17"/>
+    <mergeCell ref="CE16:CE17"/>
+    <mergeCell ref="CF16:CF17"/>
+    <mergeCell ref="CG16:CG17"/>
+    <mergeCell ref="CH16:CH17"/>
+    <mergeCell ref="CU16:CU17"/>
+    <mergeCell ref="CV16:CV17"/>
+    <mergeCell ref="CW16:CW17"/>
+    <mergeCell ref="CX16:CX17"/>
+    <mergeCell ref="CY16:CY17"/>
+    <mergeCell ref="CZ16:CZ17"/>
+    <mergeCell ref="CO16:CO17"/>
+    <mergeCell ref="CP16:CP17"/>
+    <mergeCell ref="CQ16:CQ17"/>
+    <mergeCell ref="CR16:CR17"/>
+    <mergeCell ref="CS16:CS17"/>
+    <mergeCell ref="CT16:CT17"/>
+    <mergeCell ref="DG16:DG17"/>
+    <mergeCell ref="DH16:DH17"/>
+    <mergeCell ref="DI16:DI17"/>
+    <mergeCell ref="DJ16:DJ17"/>
+    <mergeCell ref="DK16:DK17"/>
+    <mergeCell ref="DL16:DL17"/>
+    <mergeCell ref="DA16:DA17"/>
+    <mergeCell ref="DB16:DB17"/>
+    <mergeCell ref="DC16:DC17"/>
+    <mergeCell ref="DD16:DD17"/>
+    <mergeCell ref="DE16:DE17"/>
+    <mergeCell ref="DF16:DF17"/>
     <mergeCell ref="EE16:EE17"/>
     <mergeCell ref="EF16:EF17"/>
     <mergeCell ref="EG16:EG17"/>
@@ -48338,182 +48471,55 @@
     <mergeCell ref="DP16:DP17"/>
     <mergeCell ref="DQ16:DQ17"/>
     <mergeCell ref="DR16:DR17"/>
-    <mergeCell ref="DG16:DG17"/>
-    <mergeCell ref="DH16:DH17"/>
-    <mergeCell ref="DI16:DI17"/>
-    <mergeCell ref="DJ16:DJ17"/>
-    <mergeCell ref="DK16:DK17"/>
-    <mergeCell ref="DL16:DL17"/>
-    <mergeCell ref="DA16:DA17"/>
-    <mergeCell ref="DB16:DB17"/>
-    <mergeCell ref="DC16:DC17"/>
-    <mergeCell ref="DD16:DD17"/>
-    <mergeCell ref="DE16:DE17"/>
-    <mergeCell ref="DF16:DF17"/>
-    <mergeCell ref="CU16:CU17"/>
-    <mergeCell ref="CV16:CV17"/>
-    <mergeCell ref="CW16:CW17"/>
-    <mergeCell ref="CX16:CX17"/>
-    <mergeCell ref="CY16:CY17"/>
-    <mergeCell ref="CZ16:CZ17"/>
-    <mergeCell ref="CO16:CO17"/>
-    <mergeCell ref="CP16:CP17"/>
-    <mergeCell ref="CQ16:CQ17"/>
-    <mergeCell ref="CR16:CR17"/>
-    <mergeCell ref="CS16:CS17"/>
-    <mergeCell ref="CT16:CT17"/>
-    <mergeCell ref="CI16:CI17"/>
-    <mergeCell ref="CJ16:CJ17"/>
-    <mergeCell ref="CK16:CK17"/>
-    <mergeCell ref="CL16:CL17"/>
-    <mergeCell ref="CM16:CM17"/>
-    <mergeCell ref="CN16:CN17"/>
-    <mergeCell ref="CC16:CC17"/>
-    <mergeCell ref="CD16:CD17"/>
-    <mergeCell ref="CE16:CE17"/>
-    <mergeCell ref="CF16:CF17"/>
-    <mergeCell ref="CG16:CG17"/>
-    <mergeCell ref="CH16:CH17"/>
-    <mergeCell ref="BW16:BW17"/>
-    <mergeCell ref="BX16:BX17"/>
-    <mergeCell ref="BY16:BY17"/>
-    <mergeCell ref="BZ16:BZ17"/>
-    <mergeCell ref="CA16:CA17"/>
-    <mergeCell ref="CB16:CB17"/>
-    <mergeCell ref="BQ16:BQ17"/>
-    <mergeCell ref="BR16:BR17"/>
-    <mergeCell ref="BS16:BS17"/>
-    <mergeCell ref="BT16:BT17"/>
-    <mergeCell ref="BU16:BU17"/>
-    <mergeCell ref="BV16:BV17"/>
-    <mergeCell ref="BK16:BK17"/>
-    <mergeCell ref="BL16:BL17"/>
-    <mergeCell ref="BM16:BM17"/>
-    <mergeCell ref="BN16:BN17"/>
-    <mergeCell ref="BO16:BO17"/>
-    <mergeCell ref="BP16:BP17"/>
-    <mergeCell ref="BE16:BE17"/>
-    <mergeCell ref="BF16:BF17"/>
-    <mergeCell ref="BG16:BG17"/>
-    <mergeCell ref="BH16:BH17"/>
-    <mergeCell ref="BI16:BI17"/>
-    <mergeCell ref="BJ16:BJ17"/>
-    <mergeCell ref="AY16:AY17"/>
-    <mergeCell ref="AZ16:AZ17"/>
-    <mergeCell ref="BA16:BA17"/>
-    <mergeCell ref="BB16:BB17"/>
-    <mergeCell ref="BC16:BC17"/>
-    <mergeCell ref="BD16:BD17"/>
-    <mergeCell ref="AS16:AS17"/>
-    <mergeCell ref="AT16:AT17"/>
-    <mergeCell ref="AU16:AU17"/>
-    <mergeCell ref="AV16:AV17"/>
-    <mergeCell ref="AW16:AW17"/>
-    <mergeCell ref="AX16:AX17"/>
-    <mergeCell ref="AM16:AM17"/>
-    <mergeCell ref="AN16:AN17"/>
-    <mergeCell ref="AO16:AO17"/>
-    <mergeCell ref="AP16:AP17"/>
-    <mergeCell ref="AQ16:AQ17"/>
-    <mergeCell ref="AR16:AR17"/>
-    <mergeCell ref="AG16:AG17"/>
-    <mergeCell ref="AH16:AH17"/>
-    <mergeCell ref="AI16:AI17"/>
-    <mergeCell ref="AJ16:AJ17"/>
-    <mergeCell ref="AK16:AK17"/>
-    <mergeCell ref="AL16:AL17"/>
-    <mergeCell ref="AC16:AC17"/>
-    <mergeCell ref="AD16:AD17"/>
-    <mergeCell ref="AE16:AE17"/>
-    <mergeCell ref="AF16:AF17"/>
-    <mergeCell ref="U16:U17"/>
-    <mergeCell ref="V16:V17"/>
-    <mergeCell ref="W16:W17"/>
-    <mergeCell ref="X16:X17"/>
-    <mergeCell ref="Y16:Y17"/>
-    <mergeCell ref="Z16:Z17"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="AC15:AD15"/>
-    <mergeCell ref="AF15:AG15"/>
-    <mergeCell ref="BE15:BF15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="O16:O17"/>
-    <mergeCell ref="P16:P17"/>
-    <mergeCell ref="Q16:Q17"/>
-    <mergeCell ref="R16:R17"/>
-    <mergeCell ref="S16:S17"/>
-    <mergeCell ref="T16:T17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="I16:I17"/>
-    <mergeCell ref="J16:J17"/>
-    <mergeCell ref="K16:K17"/>
-    <mergeCell ref="L16:M17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="AA16:AA17"/>
-    <mergeCell ref="AB16:AB17"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="AC13:AD13"/>
-    <mergeCell ref="AF13:AG13"/>
-    <mergeCell ref="AN13:AO13"/>
-    <mergeCell ref="BD13:BE13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="AC14:AD14"/>
-    <mergeCell ref="AF14:AG14"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="AC11:AD11"/>
-    <mergeCell ref="AF11:AG11"/>
-    <mergeCell ref="AN11:AO11"/>
-    <mergeCell ref="BD11:BE11"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="AD12:AE12"/>
-    <mergeCell ref="AF12:AG12"/>
-    <mergeCell ref="AN12:AO12"/>
-    <mergeCell ref="BD12:BE12"/>
-    <mergeCell ref="AD9:AE9"/>
-    <mergeCell ref="AF9:AG9"/>
-    <mergeCell ref="AN9:AO9"/>
-    <mergeCell ref="BD9:BE9"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="AC10:AD10"/>
-    <mergeCell ref="AF10:AG10"/>
-    <mergeCell ref="AN10:AO10"/>
-    <mergeCell ref="BD10:BE10"/>
-    <mergeCell ref="AD7:AE7"/>
-    <mergeCell ref="AF7:AG7"/>
-    <mergeCell ref="BD7:BE7"/>
-    <mergeCell ref="AD8:AE8"/>
-    <mergeCell ref="AF8:AG8"/>
-    <mergeCell ref="BD8:BE8"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="AF5:AG5"/>
-    <mergeCell ref="BD5:BE5"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="AF6:AG6"/>
-    <mergeCell ref="BD6:BE6"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="AN3:AO3"/>
-    <mergeCell ref="BD3:BE3"/>
-    <mergeCell ref="AD4:AE4"/>
-    <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AL4:AM4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="BD4:BE4"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AF1:AG1"/>
-    <mergeCell ref="AN1:AO1"/>
-    <mergeCell ref="BD1:BE1"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="AN2:AO2"/>
-    <mergeCell ref="BD2:BE2"/>
+    <mergeCell ref="BD29:BE29"/>
+    <mergeCell ref="BD30:BE30"/>
+    <mergeCell ref="BD31:BE31"/>
+    <mergeCell ref="BD32:BE32"/>
+    <mergeCell ref="BD33:BE33"/>
+    <mergeCell ref="BD34:BE34"/>
+    <mergeCell ref="BD23:BE23"/>
+    <mergeCell ref="BD24:BE24"/>
+    <mergeCell ref="BD25:BE25"/>
+    <mergeCell ref="BD26:BE26"/>
+    <mergeCell ref="BD27:BE27"/>
+    <mergeCell ref="BD28:BE28"/>
+    <mergeCell ref="BD41:BE41"/>
+    <mergeCell ref="BD42:BE42"/>
+    <mergeCell ref="BD43:BE43"/>
+    <mergeCell ref="BD44:BE44"/>
+    <mergeCell ref="BD45:BE45"/>
+    <mergeCell ref="BD46:BE46"/>
+    <mergeCell ref="BD35:BE35"/>
+    <mergeCell ref="BD36:BE36"/>
+    <mergeCell ref="BD37:BE37"/>
+    <mergeCell ref="BD38:BE38"/>
+    <mergeCell ref="BD39:BE39"/>
+    <mergeCell ref="BD40:BE40"/>
+    <mergeCell ref="BD53:BE53"/>
+    <mergeCell ref="BD54:BE54"/>
+    <mergeCell ref="BD55:BE55"/>
+    <mergeCell ref="BD56:BE56"/>
+    <mergeCell ref="BD57:BE57"/>
+    <mergeCell ref="BD58:BE58"/>
+    <mergeCell ref="BD47:BE47"/>
+    <mergeCell ref="BD48:BE48"/>
+    <mergeCell ref="BD49:BE49"/>
+    <mergeCell ref="BD50:BE50"/>
+    <mergeCell ref="BD51:BE51"/>
+    <mergeCell ref="BD52:BE52"/>
+    <mergeCell ref="BD71:BE71"/>
+    <mergeCell ref="BD65:BE65"/>
+    <mergeCell ref="BD66:BE66"/>
+    <mergeCell ref="BD67:BE67"/>
+    <mergeCell ref="BD68:BE68"/>
+    <mergeCell ref="BD69:BE69"/>
+    <mergeCell ref="BD70:BE70"/>
+    <mergeCell ref="BD59:BE59"/>
+    <mergeCell ref="BD60:BE60"/>
+    <mergeCell ref="BD61:BE61"/>
+    <mergeCell ref="BD62:BE62"/>
+    <mergeCell ref="BD63:BE63"/>
+    <mergeCell ref="BD64:BE64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -48522,12 +48528,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1752B9D-3FDA-4092-ABEF-8AB424D35D4A}">
   <dimension ref="A1:AW269"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="17" max="17" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" s="45"/>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
@@ -48578,7 +48584,7 @@
       <c r="AV1" s="45"/>
       <c r="AW1" s="45"/>
     </row>
-    <row r="2" spans="1:49">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" s="45"/>
       <c r="B2" s="3"/>
       <c r="C2" s="6" t="s">
@@ -48594,8 +48600,8 @@
       <c r="G2" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="97"/>
-      <c r="I2" s="97"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
       <c r="J2" s="45"/>
       <c r="K2" s="45"/>
       <c r="L2" s="45"/>
@@ -48637,7 +48643,7 @@
       <c r="AV2" s="45"/>
       <c r="AW2" s="45"/>
     </row>
-    <row r="3" spans="1:49" ht="23.25">
+    <row r="3" spans="1:49" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A3" s="45"/>
       <c r="B3" s="3"/>
       <c r="C3" s="12" t="s">
@@ -48649,12 +48655,12 @@
       <c r="E3" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="82" t="s">
+      <c r="F3" s="101" t="s">
         <v>191</v>
       </c>
-      <c r="G3" s="83"/>
-      <c r="H3" s="97"/>
-      <c r="I3" s="97"/>
+      <c r="G3" s="102"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
       <c r="J3" s="33" t="s">
         <v>257</v>
       </c>
@@ -48700,7 +48706,7 @@
       <c r="AV3" s="45"/>
       <c r="AW3" s="45"/>
     </row>
-    <row r="4" spans="1:49">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" s="45"/>
       <c r="B4" s="3" t="s">
         <v>193</v>
@@ -48771,7 +48777,7 @@
       <c r="AV4" s="45"/>
       <c r="AW4" s="45"/>
     </row>
-    <row r="5" spans="1:49">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A5" s="45"/>
       <c r="B5" s="3" t="s">
         <v>198</v>
@@ -48838,7 +48844,7 @@
       <c r="AV5" s="45"/>
       <c r="AW5" s="45"/>
     </row>
-    <row r="6" spans="1:49">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="45"/>
       <c r="B6" s="3" t="s">
         <v>202</v>
@@ -48909,7 +48915,7 @@
       <c r="AV6" s="45"/>
       <c r="AW6" s="45"/>
     </row>
-    <row r="7" spans="1:49">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="45"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -48970,7 +48976,7 @@
       <c r="AV7" s="45"/>
       <c r="AW7" s="45"/>
     </row>
-    <row r="8" spans="1:49">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" s="45"/>
       <c r="B8" s="3"/>
       <c r="C8" s="25"/>
@@ -48982,8 +48988,8 @@
       <c r="G8" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
       <c r="J8" s="45"/>
       <c r="K8" s="45"/>
       <c r="L8" s="45"/>
@@ -49025,7 +49031,7 @@
       <c r="AV8" s="45"/>
       <c r="AW8" s="45"/>
     </row>
-    <row r="9" spans="1:49">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" s="45"/>
       <c r="B9" s="45"/>
       <c r="C9" s="45"/>
@@ -49078,7 +49084,7 @@
       <c r="AV9" s="45"/>
       <c r="AW9" s="45"/>
     </row>
-    <row r="10" spans="1:49">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" s="45"/>
       <c r="B10" s="45"/>
       <c r="C10" s="45"/>
@@ -49131,7 +49137,7 @@
       <c r="AV10" s="45"/>
       <c r="AW10" s="45"/>
     </row>
-    <row r="11" spans="1:49">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" s="45"/>
       <c r="B11" s="45"/>
       <c r="C11" s="45"/>
@@ -49182,7 +49188,7 @@
       <c r="AV11" s="45"/>
       <c r="AW11" s="45"/>
     </row>
-    <row r="12" spans="1:49">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" s="45"/>
       <c r="B12" s="49" t="s">
         <v>263</v>
@@ -49295,7 +49301,7 @@
       <c r="AV12" s="45"/>
       <c r="AW12" s="45"/>
     </row>
-    <row r="13" spans="1:49">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" s="45"/>
       <c r="B13" s="3" t="s">
         <v>212</v>
@@ -49370,7 +49376,7 @@
       <c r="AV13" s="45"/>
       <c r="AW13" s="45"/>
     </row>
-    <row r="14" spans="1:49">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" s="45"/>
       <c r="B14" s="6" t="s">
         <v>226</v>
@@ -49453,24 +49459,24 @@
       <c r="AV14" s="45"/>
       <c r="AW14" s="45"/>
     </row>
-    <row r="15" spans="1:49">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" s="45"/>
-      <c r="B15" s="88" t="s">
+      <c r="B15" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="91" t="s">
+      <c r="C15" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="91" t="s">
+      <c r="D15" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="E15" s="91" t="s">
+      <c r="E15" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="F15" s="91" t="s">
+      <c r="F15" s="84" t="s">
         <v>241</v>
       </c>
-      <c r="G15" s="90" t="s">
+      <c r="G15" s="86" t="s">
         <v>242</v>
       </c>
       <c r="H15" s="45"/>
@@ -49479,22 +49485,22 @@
       <c r="K15" s="45"/>
       <c r="L15" s="45"/>
       <c r="M15" s="45"/>
-      <c r="N15" s="88" t="s">
+      <c r="N15" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="O15" s="91" t="s">
+      <c r="O15" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="P15" s="91" t="s">
+      <c r="P15" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="Q15" s="91" t="s">
+      <c r="Q15" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="R15" s="91" t="s">
+      <c r="R15" s="84" t="s">
         <v>241</v>
       </c>
-      <c r="S15" s="90" t="s">
+      <c r="S15" s="86" t="s">
         <v>242</v>
       </c>
       <c r="T15" s="45"/>
@@ -49546,26 +49552,26 @@
       <c r="AV15" s="45"/>
       <c r="AW15" s="45"/>
     </row>
-    <row r="16" spans="1:49">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" s="45"/>
-      <c r="B16" s="88"/>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="90"/>
+      <c r="B16" s="85"/>
+      <c r="C16" s="84"/>
+      <c r="D16" s="84"/>
+      <c r="E16" s="84"/>
+      <c r="F16" s="84"/>
+      <c r="G16" s="86"/>
       <c r="H16" s="45"/>
       <c r="I16" s="45"/>
       <c r="J16" s="45"/>
       <c r="K16" s="45"/>
       <c r="L16" s="45"/>
       <c r="M16" s="45"/>
-      <c r="N16" s="88"/>
-      <c r="O16" s="91"/>
-      <c r="P16" s="91"/>
-      <c r="Q16" s="91"/>
-      <c r="R16" s="91"/>
-      <c r="S16" s="90"/>
+      <c r="N16" s="85"/>
+      <c r="O16" s="84"/>
+      <c r="P16" s="84"/>
+      <c r="Q16" s="84"/>
+      <c r="R16" s="84"/>
+      <c r="S16" s="86"/>
       <c r="T16" s="45"/>
       <c r="U16" s="45"/>
       <c r="V16" s="45"/>
@@ -49599,7 +49605,7 @@
       <c r="AV16" s="105"/>
       <c r="AW16" s="45"/>
     </row>
-    <row r="17" spans="1:49" ht="43.5">
+    <row r="17" spans="1:49" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="45"/>
       <c r="B17" s="34" t="s">
         <v>176</v>
@@ -49696,7 +49702,7 @@
       </c>
       <c r="AW17" s="45"/>
     </row>
-    <row r="18" spans="1:49">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" s="45"/>
       <c r="B18" s="34" t="s">
         <v>195</v>
@@ -49809,7 +49815,7 @@
       </c>
       <c r="AW18" s="45"/>
     </row>
-    <row r="19" spans="1:49">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>2020</v>
       </c>
@@ -49926,7 +49932,7 @@
       </c>
       <c r="AW19" s="45"/>
     </row>
-    <row r="20" spans="1:49">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>2021</v>
       </c>
@@ -50043,7 +50049,7 @@
       </c>
       <c r="AW20" s="45"/>
     </row>
-    <row r="21" spans="1:49">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>2022</v>
       </c>
@@ -50160,7 +50166,7 @@
       </c>
       <c r="AW21" s="45"/>
     </row>
-    <row r="22" spans="1:49">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>2023</v>
       </c>
@@ -50277,7 +50283,7 @@
       </c>
       <c r="AW22" s="45"/>
     </row>
-    <row r="23" spans="1:49">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>2024</v>
       </c>
@@ -50394,7 +50400,7 @@
       </c>
       <c r="AW23" s="45"/>
     </row>
-    <row r="24" spans="1:49">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>2025</v>
       </c>
@@ -50491,7 +50497,7 @@
       <c r="AV24" s="45"/>
       <c r="AW24" s="45"/>
     </row>
-    <row r="25" spans="1:49">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2026</v>
       </c>
@@ -50592,7 +50598,7 @@
       <c r="AV25" s="45"/>
       <c r="AW25" s="45"/>
     </row>
-    <row r="26" spans="1:49">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>2027</v>
       </c>
@@ -50695,7 +50701,7 @@
       <c r="AV26" s="45"/>
       <c r="AW26" s="45"/>
     </row>
-    <row r="27" spans="1:49">
+    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>2028</v>
       </c>
@@ -50794,7 +50800,7 @@
       <c r="AV27" s="45"/>
       <c r="AW27" s="45"/>
     </row>
-    <row r="28" spans="1:49">
+    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>2029</v>
       </c>
@@ -50893,7 +50899,7 @@
       <c r="AV28" s="45"/>
       <c r="AW28" s="45"/>
     </row>
-    <row r="29" spans="1:49">
+    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>2030</v>
       </c>
@@ -50992,7 +50998,7 @@
       <c r="AV29" s="45"/>
       <c r="AW29" s="45"/>
     </row>
-    <row r="30" spans="1:49">
+    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>2031</v>
       </c>
@@ -51091,7 +51097,7 @@
       <c r="AV30" s="45"/>
       <c r="AW30" s="45"/>
     </row>
-    <row r="31" spans="1:49">
+    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>2032</v>
       </c>
@@ -51190,7 +51196,7 @@
       <c r="AV31" s="45"/>
       <c r="AW31" s="45"/>
     </row>
-    <row r="32" spans="1:49">
+    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>2033</v>
       </c>
@@ -51289,7 +51295,7 @@
       <c r="AV32" s="45"/>
       <c r="AW32" s="45"/>
     </row>
-    <row r="33" spans="1:49">
+    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>2034</v>
       </c>
@@ -51388,7 +51394,7 @@
       <c r="AV33" s="45"/>
       <c r="AW33" s="45"/>
     </row>
-    <row r="34" spans="1:49">
+    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>2035</v>
       </c>
@@ -51487,7 +51493,7 @@
       <c r="AV34" s="45"/>
       <c r="AW34" s="45"/>
     </row>
-    <row r="35" spans="1:49">
+    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>2036</v>
       </c>
@@ -51586,7 +51592,7 @@
       <c r="AV35" s="45"/>
       <c r="AW35" s="45"/>
     </row>
-    <row r="36" spans="1:49">
+    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>2037</v>
       </c>
@@ -51685,7 +51691,7 @@
       <c r="AV36" s="45"/>
       <c r="AW36" s="45"/>
     </row>
-    <row r="37" spans="1:49">
+    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>2038</v>
       </c>
@@ -51784,7 +51790,7 @@
       <c r="AV37" s="45"/>
       <c r="AW37" s="45"/>
     </row>
-    <row r="38" spans="1:49">
+    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>2039</v>
       </c>
@@ -51883,7 +51889,7 @@
       <c r="AV38" s="45"/>
       <c r="AW38" s="45"/>
     </row>
-    <row r="39" spans="1:49">
+    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>2040</v>
       </c>
@@ -51982,7 +51988,7 @@
       <c r="AV39" s="45"/>
       <c r="AW39" s="45"/>
     </row>
-    <row r="40" spans="1:49">
+    <row r="40" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>2041</v>
       </c>
@@ -52081,7 +52087,7 @@
       <c r="AV40" s="45"/>
       <c r="AW40" s="45"/>
     </row>
-    <row r="41" spans="1:49">
+    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>2042</v>
       </c>
@@ -52180,7 +52186,7 @@
       <c r="AV41" s="45"/>
       <c r="AW41" s="45"/>
     </row>
-    <row r="42" spans="1:49">
+    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A42" s="4">
         <v>2043</v>
       </c>
@@ -52279,7 +52285,7 @@
       <c r="AV42" s="45"/>
       <c r="AW42" s="45"/>
     </row>
-    <row r="43" spans="1:49">
+    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>2044</v>
       </c>
@@ -52378,7 +52384,7 @@
       <c r="AV43" s="45"/>
       <c r="AW43" s="45"/>
     </row>
-    <row r="44" spans="1:49">
+    <row r="44" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>2045</v>
       </c>
@@ -52477,7 +52483,7 @@
       <c r="AV44" s="45"/>
       <c r="AW44" s="45"/>
     </row>
-    <row r="45" spans="1:49">
+    <row r="45" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>2046</v>
       </c>
@@ -52580,7 +52586,7 @@
       <c r="AV45" s="45"/>
       <c r="AW45" s="45"/>
     </row>
-    <row r="46" spans="1:49">
+    <row r="46" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>2047</v>
       </c>
@@ -52679,7 +52685,7 @@
       <c r="AV46" s="45"/>
       <c r="AW46" s="45"/>
     </row>
-    <row r="47" spans="1:49">
+    <row r="47" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>2048</v>
       </c>
@@ -52778,7 +52784,7 @@
       <c r="AV47" s="45"/>
       <c r="AW47" s="45"/>
     </row>
-    <row r="48" spans="1:49">
+    <row r="48" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>2049</v>
       </c>
@@ -52877,7 +52883,7 @@
       <c r="AV48" s="45"/>
       <c r="AW48" s="45"/>
     </row>
-    <row r="49" spans="1:49">
+    <row r="49" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A49" s="4">
         <v>2050</v>
       </c>
@@ -52976,7 +52982,7 @@
       <c r="AV49" s="45"/>
       <c r="AW49" s="45"/>
     </row>
-    <row r="50" spans="1:49">
+    <row r="50" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A50" s="4">
         <v>2051</v>
       </c>
@@ -53071,7 +53077,7 @@
       <c r="AV50" s="45"/>
       <c r="AW50" s="45"/>
     </row>
-    <row r="51" spans="1:49">
+    <row r="51" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A51" s="4">
         <v>2052</v>
       </c>
@@ -53166,7 +53172,7 @@
       <c r="AV51" s="45"/>
       <c r="AW51" s="45"/>
     </row>
-    <row r="52" spans="1:49">
+    <row r="52" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A52" s="4">
         <v>2053</v>
       </c>
@@ -53261,7 +53267,7 @@
       <c r="AV52" s="45"/>
       <c r="AW52" s="45"/>
     </row>
-    <row r="53" spans="1:49">
+    <row r="53" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A53" s="4">
         <v>2054</v>
       </c>
@@ -53356,7 +53362,7 @@
       <c r="AV53" s="45"/>
       <c r="AW53" s="45"/>
     </row>
-    <row r="54" spans="1:49">
+    <row r="54" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A54" s="4">
         <v>2055</v>
       </c>
@@ -53451,7 +53457,7 @@
       <c r="AV54" s="45"/>
       <c r="AW54" s="45"/>
     </row>
-    <row r="55" spans="1:49">
+    <row r="55" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A55" s="4">
         <v>2056</v>
       </c>
@@ -53546,7 +53552,7 @@
       <c r="AV55" s="45"/>
       <c r="AW55" s="45"/>
     </row>
-    <row r="56" spans="1:49">
+    <row r="56" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A56" s="4">
         <v>2057</v>
       </c>
@@ -53641,7 +53647,7 @@
       <c r="AV56" s="45"/>
       <c r="AW56" s="45"/>
     </row>
-    <row r="57" spans="1:49">
+    <row r="57" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A57" s="4">
         <v>2058</v>
       </c>
@@ -53736,7 +53742,7 @@
       <c r="AV57" s="45"/>
       <c r="AW57" s="45"/>
     </row>
-    <row r="58" spans="1:49">
+    <row r="58" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A58" s="4">
         <v>2059</v>
       </c>
@@ -53831,7 +53837,7 @@
       <c r="AV58" s="45"/>
       <c r="AW58" s="45"/>
     </row>
-    <row r="59" spans="1:49">
+    <row r="59" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A59" s="4">
         <v>2060</v>
       </c>
@@ -53926,7 +53932,7 @@
       <c r="AV59" s="45"/>
       <c r="AW59" s="45"/>
     </row>
-    <row r="60" spans="1:49">
+    <row r="60" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A60" s="4">
         <v>2061</v>
       </c>
@@ -54021,7 +54027,7 @@
       <c r="AV60" s="45"/>
       <c r="AW60" s="45"/>
     </row>
-    <row r="61" spans="1:49">
+    <row r="61" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A61" s="4">
         <v>2062</v>
       </c>
@@ -54116,7 +54122,7 @@
       <c r="AV61" s="45"/>
       <c r="AW61" s="45"/>
     </row>
-    <row r="62" spans="1:49">
+    <row r="62" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A62" s="4">
         <v>2063</v>
       </c>
@@ -54211,7 +54217,7 @@
       <c r="AV62" s="45"/>
       <c r="AW62" s="45"/>
     </row>
-    <row r="63" spans="1:49">
+    <row r="63" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A63" s="4">
         <v>2064</v>
       </c>
@@ -54306,7 +54312,7 @@
       <c r="AV63" s="45"/>
       <c r="AW63" s="45"/>
     </row>
-    <row r="64" spans="1:49">
+    <row r="64" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A64" s="4">
         <v>2065</v>
       </c>
@@ -54401,7 +54407,7 @@
       <c r="AV64" s="45"/>
       <c r="AW64" s="45"/>
     </row>
-    <row r="65" spans="1:49">
+    <row r="65" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A65" s="4">
         <v>2066</v>
       </c>
@@ -54496,7 +54502,7 @@
       <c r="AV65" s="45"/>
       <c r="AW65" s="45"/>
     </row>
-    <row r="66" spans="1:49">
+    <row r="66" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A66" s="4">
         <v>2067</v>
       </c>
@@ -54591,7 +54597,7 @@
       <c r="AV66" s="45"/>
       <c r="AW66" s="45"/>
     </row>
-    <row r="67" spans="1:49">
+    <row r="67" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A67" s="4">
         <v>2068</v>
       </c>
@@ -54686,7 +54692,7 @@
       <c r="AV67" s="45"/>
       <c r="AW67" s="45"/>
     </row>
-    <row r="68" spans="1:49">
+    <row r="68" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A68" s="4">
         <v>2069</v>
       </c>
@@ -54781,7 +54787,7 @@
       <c r="AV68" s="45"/>
       <c r="AW68" s="45"/>
     </row>
-    <row r="69" spans="1:49">
+    <row r="69" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A69" s="4">
         <v>2070</v>
       </c>
@@ -54876,7 +54882,7 @@
       <c r="AV69" s="45"/>
       <c r="AW69" s="45"/>
     </row>
-    <row r="70" spans="1:49">
+    <row r="70" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
         <v>2071</v>
       </c>
@@ -54971,7 +54977,7 @@
       <c r="AV70" s="45"/>
       <c r="AW70" s="45"/>
     </row>
-    <row r="71" spans="1:49">
+    <row r="71" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>2072</v>
       </c>
@@ -55066,7 +55072,7 @@
       <c r="AV71" s="45"/>
       <c r="AW71" s="45"/>
     </row>
-    <row r="72" spans="1:49">
+    <row r="72" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
         <v>2073</v>
       </c>
@@ -55161,7 +55167,7 @@
       <c r="AV72" s="45"/>
       <c r="AW72" s="45"/>
     </row>
-    <row r="73" spans="1:49">
+    <row r="73" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>2074</v>
       </c>
@@ -55256,7 +55262,7 @@
       <c r="AV73" s="45"/>
       <c r="AW73" s="45"/>
     </row>
-    <row r="74" spans="1:49">
+    <row r="74" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>2075</v>
       </c>
@@ -55351,7 +55357,7 @@
       <c r="AV74" s="45"/>
       <c r="AW74" s="45"/>
     </row>
-    <row r="75" spans="1:49">
+    <row r="75" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A75" s="45"/>
       <c r="B75" s="45"/>
       <c r="C75" s="45"/>
@@ -55402,7 +55408,7 @@
       <c r="AV75" s="45"/>
       <c r="AW75" s="45"/>
     </row>
-    <row r="76" spans="1:49">
+    <row r="76" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A76" s="45"/>
       <c r="B76" s="49" t="s">
         <v>273</v>
@@ -55515,7 +55521,7 @@
       <c r="AV76" s="45"/>
       <c r="AW76" s="45"/>
     </row>
-    <row r="77" spans="1:49">
+    <row r="77" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A77" s="45"/>
       <c r="B77" s="3" t="s">
         <v>212</v>
@@ -55590,7 +55596,7 @@
       <c r="AV77" s="45"/>
       <c r="AW77" s="45"/>
     </row>
-    <row r="78" spans="1:49">
+    <row r="78" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A78" s="45"/>
       <c r="B78" s="6" t="s">
         <v>226</v>
@@ -55673,24 +55679,24 @@
       <c r="AV78" s="45"/>
       <c r="AW78" s="45"/>
     </row>
-    <row r="79" spans="1:49">
+    <row r="79" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A79" s="45"/>
-      <c r="B79" s="88" t="s">
+      <c r="B79" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="C79" s="91" t="s">
+      <c r="C79" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="D79" s="91" t="s">
+      <c r="D79" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="E79" s="91" t="s">
+      <c r="E79" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="F79" s="91" t="s">
+      <c r="F79" s="84" t="s">
         <v>241</v>
       </c>
-      <c r="G79" s="90" t="s">
+      <c r="G79" s="86" t="s">
         <v>242</v>
       </c>
       <c r="H79" s="45"/>
@@ -55699,22 +55705,22 @@
       <c r="K79" s="45"/>
       <c r="L79" s="45"/>
       <c r="M79" s="45"/>
-      <c r="N79" s="88" t="s">
+      <c r="N79" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="O79" s="91" t="s">
+      <c r="O79" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="P79" s="91" t="s">
+      <c r="P79" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="Q79" s="91" t="s">
+      <c r="Q79" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="R79" s="91" t="s">
+      <c r="R79" s="84" t="s">
         <v>241</v>
       </c>
-      <c r="S79" s="90" t="s">
+      <c r="S79" s="86" t="s">
         <v>242</v>
       </c>
       <c r="T79" s="45"/>
@@ -55766,26 +55772,26 @@
       <c r="AV79" s="45"/>
       <c r="AW79" s="45"/>
     </row>
-    <row r="80" spans="1:49">
+    <row r="80" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A80" s="45"/>
-      <c r="B80" s="88"/>
-      <c r="C80" s="91"/>
-      <c r="D80" s="91"/>
-      <c r="E80" s="91"/>
-      <c r="F80" s="91"/>
-      <c r="G80" s="90"/>
+      <c r="B80" s="85"/>
+      <c r="C80" s="84"/>
+      <c r="D80" s="84"/>
+      <c r="E80" s="84"/>
+      <c r="F80" s="84"/>
+      <c r="G80" s="86"/>
       <c r="H80" s="45"/>
       <c r="I80" s="45"/>
       <c r="J80" s="45"/>
       <c r="K80" s="45"/>
       <c r="L80" s="45"/>
       <c r="M80" s="45"/>
-      <c r="N80" s="88"/>
-      <c r="O80" s="91"/>
-      <c r="P80" s="91"/>
-      <c r="Q80" s="91"/>
-      <c r="R80" s="91"/>
-      <c r="S80" s="90"/>
+      <c r="N80" s="85"/>
+      <c r="O80" s="84"/>
+      <c r="P80" s="84"/>
+      <c r="Q80" s="84"/>
+      <c r="R80" s="84"/>
+      <c r="S80" s="86"/>
       <c r="T80" s="45"/>
       <c r="U80" s="45"/>
       <c r="V80" s="45"/>
@@ -55817,7 +55823,7 @@
       <c r="AV80" s="45"/>
       <c r="AW80" s="45"/>
     </row>
-    <row r="81" spans="1:49">
+    <row r="81" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A81" s="45"/>
       <c r="B81" s="34" t="s">
         <v>176</v>
@@ -55894,7 +55900,7 @@
       <c r="AV81" s="45"/>
       <c r="AW81" s="45"/>
     </row>
-    <row r="82" spans="1:49">
+    <row r="82" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A82" s="45"/>
       <c r="B82" s="34" t="s">
         <v>195</v>
@@ -55987,7 +55993,7 @@
       <c r="AV82" s="45"/>
       <c r="AW82" s="45"/>
     </row>
-    <row r="83" spans="1:49">
+    <row r="83" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
         <v>2020</v>
       </c>
@@ -56084,7 +56090,7 @@
       <c r="AV83" s="45"/>
       <c r="AW83" s="45"/>
     </row>
-    <row r="84" spans="1:49">
+    <row r="84" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A84" s="4">
         <v>2021</v>
       </c>
@@ -56181,7 +56187,7 @@
       <c r="AV84" s="45"/>
       <c r="AW84" s="45"/>
     </row>
-    <row r="85" spans="1:49">
+    <row r="85" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A85" s="4">
         <v>2022</v>
       </c>
@@ -56278,7 +56284,7 @@
       <c r="AV85" s="45"/>
       <c r="AW85" s="45"/>
     </row>
-    <row r="86" spans="1:49">
+    <row r="86" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A86" s="4">
         <v>2023</v>
       </c>
@@ -56375,7 +56381,7 @@
       <c r="AV86" s="45"/>
       <c r="AW86" s="45"/>
     </row>
-    <row r="87" spans="1:49">
+    <row r="87" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A87" s="4">
         <v>2024</v>
       </c>
@@ -56472,7 +56478,7 @@
       <c r="AV87" s="45"/>
       <c r="AW87" s="45"/>
     </row>
-    <row r="88" spans="1:49">
+    <row r="88" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A88" s="4">
         <v>2025</v>
       </c>
@@ -56569,7 +56575,7 @@
       <c r="AV88" s="45"/>
       <c r="AW88" s="45"/>
     </row>
-    <row r="89" spans="1:49">
+    <row r="89" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A89" s="37">
         <v>2026</v>
       </c>
@@ -56668,7 +56674,7 @@
       <c r="AV89" s="45"/>
       <c r="AW89" s="45"/>
     </row>
-    <row r="90" spans="1:49">
+    <row r="90" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A90" s="4">
         <v>2027</v>
       </c>
@@ -56769,7 +56775,7 @@
       <c r="AV90" s="45"/>
       <c r="AW90" s="45"/>
     </row>
-    <row r="91" spans="1:49">
+    <row r="91" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A91" s="4">
         <v>2028</v>
       </c>
@@ -56868,7 +56874,7 @@
       <c r="AV91" s="45"/>
       <c r="AW91" s="45"/>
     </row>
-    <row r="92" spans="1:49">
+    <row r="92" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A92" s="4">
         <v>2029</v>
       </c>
@@ -56967,7 +56973,7 @@
       <c r="AV92" s="45"/>
       <c r="AW92" s="45"/>
     </row>
-    <row r="93" spans="1:49">
+    <row r="93" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A93" s="4">
         <v>2030</v>
       </c>
@@ -57066,7 +57072,7 @@
       <c r="AV93" s="45"/>
       <c r="AW93" s="45"/>
     </row>
-    <row r="94" spans="1:49">
+    <row r="94" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A94" s="4">
         <v>2031</v>
       </c>
@@ -57165,7 +57171,7 @@
       <c r="AV94" s="45"/>
       <c r="AW94" s="45"/>
     </row>
-    <row r="95" spans="1:49">
+    <row r="95" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A95" s="4">
         <v>2032</v>
       </c>
@@ -57264,7 +57270,7 @@
       <c r="AV95" s="45"/>
       <c r="AW95" s="45"/>
     </row>
-    <row r="96" spans="1:49">
+    <row r="96" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A96" s="4">
         <v>2033</v>
       </c>
@@ -57363,7 +57369,7 @@
       <c r="AV96" s="45"/>
       <c r="AW96" s="45"/>
     </row>
-    <row r="97" spans="1:49">
+    <row r="97" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A97" s="4">
         <v>2034</v>
       </c>
@@ -57462,7 +57468,7 @@
       <c r="AV97" s="45"/>
       <c r="AW97" s="45"/>
     </row>
-    <row r="98" spans="1:49">
+    <row r="98" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A98" s="4">
         <v>2035</v>
       </c>
@@ -57561,7 +57567,7 @@
       <c r="AV98" s="45"/>
       <c r="AW98" s="45"/>
     </row>
-    <row r="99" spans="1:49">
+    <row r="99" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A99" s="4">
         <v>2036</v>
       </c>
@@ -57660,7 +57666,7 @@
       <c r="AV99" s="45"/>
       <c r="AW99" s="45"/>
     </row>
-    <row r="100" spans="1:49">
+    <row r="100" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A100" s="4">
         <v>2037</v>
       </c>
@@ -57759,7 +57765,7 @@
       <c r="AV100" s="45"/>
       <c r="AW100" s="45"/>
     </row>
-    <row r="101" spans="1:49">
+    <row r="101" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A101" s="4">
         <v>2038</v>
       </c>
@@ -57858,7 +57864,7 @@
       <c r="AV101" s="45"/>
       <c r="AW101" s="45"/>
     </row>
-    <row r="102" spans="1:49">
+    <row r="102" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A102" s="4">
         <v>2039</v>
       </c>
@@ -57957,7 +57963,7 @@
       <c r="AV102" s="45"/>
       <c r="AW102" s="45"/>
     </row>
-    <row r="103" spans="1:49">
+    <row r="103" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A103" s="4">
         <v>2040</v>
       </c>
@@ -58056,7 +58062,7 @@
       <c r="AV103" s="45"/>
       <c r="AW103" s="45"/>
     </row>
-    <row r="104" spans="1:49">
+    <row r="104" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A104" s="4">
         <v>2041</v>
       </c>
@@ -58155,7 +58161,7 @@
       <c r="AV104" s="45"/>
       <c r="AW104" s="45"/>
     </row>
-    <row r="105" spans="1:49">
+    <row r="105" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A105" s="4">
         <v>2042</v>
       </c>
@@ -58254,7 +58260,7 @@
       <c r="AV105" s="45"/>
       <c r="AW105" s="45"/>
     </row>
-    <row r="106" spans="1:49">
+    <row r="106" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A106" s="4">
         <v>2043</v>
       </c>
@@ -58353,7 +58359,7 @@
       <c r="AV106" s="45"/>
       <c r="AW106" s="45"/>
     </row>
-    <row r="107" spans="1:49">
+    <row r="107" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A107" s="4">
         <v>2044</v>
       </c>
@@ -58452,7 +58458,7 @@
       <c r="AV107" s="45"/>
       <c r="AW107" s="45"/>
     </row>
-    <row r="108" spans="1:49">
+    <row r="108" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A108" s="4">
         <v>2045</v>
       </c>
@@ -58551,7 +58557,7 @@
       <c r="AV108" s="45"/>
       <c r="AW108" s="45"/>
     </row>
-    <row r="109" spans="1:49">
+    <row r="109" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A109" s="4">
         <v>2046</v>
       </c>
@@ -58654,7 +58660,7 @@
       <c r="AV109" s="45"/>
       <c r="AW109" s="45"/>
     </row>
-    <row r="110" spans="1:49">
+    <row r="110" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A110" s="4">
         <v>2047</v>
       </c>
@@ -58753,7 +58759,7 @@
       <c r="AV110" s="45"/>
       <c r="AW110" s="45"/>
     </row>
-    <row r="111" spans="1:49">
+    <row r="111" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A111" s="4">
         <v>2048</v>
       </c>
@@ -58852,7 +58858,7 @@
       <c r="AV111" s="45"/>
       <c r="AW111" s="45"/>
     </row>
-    <row r="112" spans="1:49">
+    <row r="112" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
         <v>2049</v>
       </c>
@@ -58951,7 +58957,7 @@
       <c r="AV112" s="45"/>
       <c r="AW112" s="45"/>
     </row>
-    <row r="113" spans="1:49">
+    <row r="113" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A113" s="4">
         <v>2050</v>
       </c>
@@ -59050,7 +59056,7 @@
       <c r="AV113" s="45"/>
       <c r="AW113" s="45"/>
     </row>
-    <row r="114" spans="1:49">
+    <row r="114" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A114" s="4">
         <v>2051</v>
       </c>
@@ -59145,7 +59151,7 @@
       <c r="AV114" s="45"/>
       <c r="AW114" s="45"/>
     </row>
-    <row r="115" spans="1:49">
+    <row r="115" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A115" s="4">
         <v>2052</v>
       </c>
@@ -59240,7 +59246,7 @@
       <c r="AV115" s="45"/>
       <c r="AW115" s="45"/>
     </row>
-    <row r="116" spans="1:49">
+    <row r="116" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A116" s="4">
         <v>2053</v>
       </c>
@@ -59335,7 +59341,7 @@
       <c r="AV116" s="45"/>
       <c r="AW116" s="45"/>
     </row>
-    <row r="117" spans="1:49">
+    <row r="117" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A117" s="4">
         <v>2054</v>
       </c>
@@ -59430,7 +59436,7 @@
       <c r="AV117" s="45"/>
       <c r="AW117" s="45"/>
     </row>
-    <row r="118" spans="1:49">
+    <row r="118" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A118" s="4">
         <v>2055</v>
       </c>
@@ -59525,7 +59531,7 @@
       <c r="AV118" s="45"/>
       <c r="AW118" s="45"/>
     </row>
-    <row r="119" spans="1:49">
+    <row r="119" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A119" s="4">
         <v>2056</v>
       </c>
@@ -59620,7 +59626,7 @@
       <c r="AV119" s="45"/>
       <c r="AW119" s="45"/>
     </row>
-    <row r="120" spans="1:49">
+    <row r="120" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A120" s="4">
         <v>2057</v>
       </c>
@@ -59715,7 +59721,7 @@
       <c r="AV120" s="45"/>
       <c r="AW120" s="45"/>
     </row>
-    <row r="121" spans="1:49">
+    <row r="121" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A121" s="4">
         <v>2058</v>
       </c>
@@ -59810,7 +59816,7 @@
       <c r="AV121" s="45"/>
       <c r="AW121" s="45"/>
     </row>
-    <row r="122" spans="1:49">
+    <row r="122" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A122" s="4">
         <v>2059</v>
       </c>
@@ -59905,7 +59911,7 @@
       <c r="AV122" s="45"/>
       <c r="AW122" s="45"/>
     </row>
-    <row r="123" spans="1:49">
+    <row r="123" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A123" s="4">
         <v>2060</v>
       </c>
@@ -60000,7 +60006,7 @@
       <c r="AV123" s="45"/>
       <c r="AW123" s="45"/>
     </row>
-    <row r="124" spans="1:49">
+    <row r="124" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A124" s="4">
         <v>2061</v>
       </c>
@@ -60095,7 +60101,7 @@
       <c r="AV124" s="45"/>
       <c r="AW124" s="45"/>
     </row>
-    <row r="125" spans="1:49">
+    <row r="125" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A125" s="4">
         <v>2062</v>
       </c>
@@ -60190,7 +60196,7 @@
       <c r="AV125" s="45"/>
       <c r="AW125" s="45"/>
     </row>
-    <row r="126" spans="1:49">
+    <row r="126" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A126" s="4">
         <v>2063</v>
       </c>
@@ -60285,7 +60291,7 @@
       <c r="AV126" s="45"/>
       <c r="AW126" s="45"/>
     </row>
-    <row r="127" spans="1:49">
+    <row r="127" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A127" s="4">
         <v>2064</v>
       </c>
@@ -60380,7 +60386,7 @@
       <c r="AV127" s="45"/>
       <c r="AW127" s="45"/>
     </row>
-    <row r="128" spans="1:49">
+    <row r="128" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A128" s="4">
         <v>2065</v>
       </c>
@@ -60475,7 +60481,7 @@
       <c r="AV128" s="45"/>
       <c r="AW128" s="45"/>
     </row>
-    <row r="129" spans="1:49">
+    <row r="129" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A129" s="4">
         <v>2066</v>
       </c>
@@ -60570,7 +60576,7 @@
       <c r="AV129" s="45"/>
       <c r="AW129" s="45"/>
     </row>
-    <row r="130" spans="1:49">
+    <row r="130" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
         <v>2067</v>
       </c>
@@ -60665,7 +60671,7 @@
       <c r="AV130" s="45"/>
       <c r="AW130" s="45"/>
     </row>
-    <row r="131" spans="1:49">
+    <row r="131" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A131" s="4">
         <v>2068</v>
       </c>
@@ -60760,7 +60766,7 @@
       <c r="AV131" s="45"/>
       <c r="AW131" s="45"/>
     </row>
-    <row r="132" spans="1:49">
+    <row r="132" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A132" s="4">
         <v>2069</v>
       </c>
@@ -60855,7 +60861,7 @@
       <c r="AV132" s="45"/>
       <c r="AW132" s="45"/>
     </row>
-    <row r="133" spans="1:49">
+    <row r="133" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A133" s="4">
         <v>2070</v>
       </c>
@@ -60950,7 +60956,7 @@
       <c r="AV133" s="45"/>
       <c r="AW133" s="45"/>
     </row>
-    <row r="134" spans="1:49">
+    <row r="134" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A134" s="4">
         <v>2071</v>
       </c>
@@ -61045,7 +61051,7 @@
       <c r="AV134" s="45"/>
       <c r="AW134" s="45"/>
     </row>
-    <row r="135" spans="1:49">
+    <row r="135" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A135" s="4">
         <v>2072</v>
       </c>
@@ -61140,7 +61146,7 @@
       <c r="AV135" s="45"/>
       <c r="AW135" s="45"/>
     </row>
-    <row r="136" spans="1:49">
+    <row r="136" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A136" s="4">
         <v>2073</v>
       </c>
@@ -61235,7 +61241,7 @@
       <c r="AV136" s="45"/>
       <c r="AW136" s="45"/>
     </row>
-    <row r="137" spans="1:49">
+    <row r="137" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A137" s="4">
         <v>2074</v>
       </c>
@@ -61330,7 +61336,7 @@
       <c r="AV137" s="45"/>
       <c r="AW137" s="45"/>
     </row>
-    <row r="138" spans="1:49">
+    <row r="138" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A138" s="4">
         <v>2075</v>
       </c>
@@ -61425,7 +61431,7 @@
       <c r="AV138" s="45"/>
       <c r="AW138" s="45"/>
     </row>
-    <row r="139" spans="1:49">
+    <row r="139" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A139" s="45"/>
       <c r="B139" s="45"/>
       <c r="C139" s="45"/>
@@ -61476,7 +61482,7 @@
       <c r="AV139" s="45"/>
       <c r="AW139" s="45"/>
     </row>
-    <row r="140" spans="1:49">
+    <row r="140" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A140" s="45"/>
       <c r="B140" s="49" t="s">
         <v>99</v>
@@ -61589,7 +61595,7 @@
       <c r="AV140" s="45"/>
       <c r="AW140" s="45"/>
     </row>
-    <row r="141" spans="1:49">
+    <row r="141" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A141" s="45"/>
       <c r="B141" s="3" t="s">
         <v>212</v>
@@ -61664,7 +61670,7 @@
       <c r="AV141" s="45"/>
       <c r="AW141" s="45"/>
     </row>
-    <row r="142" spans="1:49">
+    <row r="142" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A142" s="45"/>
       <c r="B142" s="6" t="s">
         <v>226</v>
@@ -61747,24 +61753,24 @@
       <c r="AV142" s="45"/>
       <c r="AW142" s="45"/>
     </row>
-    <row r="143" spans="1:49">
+    <row r="143" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A143" s="45"/>
-      <c r="B143" s="88" t="s">
+      <c r="B143" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="C143" s="91" t="s">
+      <c r="C143" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="D143" s="91" t="s">
+      <c r="D143" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="E143" s="91" t="s">
+      <c r="E143" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="F143" s="91" t="s">
+      <c r="F143" s="84" t="s">
         <v>241</v>
       </c>
-      <c r="G143" s="90" t="s">
+      <c r="G143" s="86" t="s">
         <v>242</v>
       </c>
       <c r="H143" s="45"/>
@@ -61773,22 +61779,22 @@
       <c r="K143" s="45"/>
       <c r="L143" s="45"/>
       <c r="M143" s="45"/>
-      <c r="N143" s="88" t="s">
+      <c r="N143" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="O143" s="91" t="s">
+      <c r="O143" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="P143" s="91" t="s">
+      <c r="P143" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="Q143" s="91" t="s">
+      <c r="Q143" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="R143" s="91" t="s">
+      <c r="R143" s="84" t="s">
         <v>241</v>
       </c>
-      <c r="S143" s="90" t="s">
+      <c r="S143" s="86" t="s">
         <v>242</v>
       </c>
       <c r="T143" s="45"/>
@@ -61840,26 +61846,26 @@
       <c r="AV143" s="45"/>
       <c r="AW143" s="45"/>
     </row>
-    <row r="144" spans="1:49">
+    <row r="144" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A144" s="45"/>
-      <c r="B144" s="88"/>
-      <c r="C144" s="91"/>
-      <c r="D144" s="91"/>
-      <c r="E144" s="91"/>
-      <c r="F144" s="91"/>
-      <c r="G144" s="90"/>
+      <c r="B144" s="85"/>
+      <c r="C144" s="84"/>
+      <c r="D144" s="84"/>
+      <c r="E144" s="84"/>
+      <c r="F144" s="84"/>
+      <c r="G144" s="86"/>
       <c r="H144" s="45"/>
       <c r="I144" s="45"/>
       <c r="J144" s="45"/>
       <c r="K144" s="45"/>
       <c r="L144" s="45"/>
       <c r="M144" s="45"/>
-      <c r="N144" s="88"/>
-      <c r="O144" s="91"/>
-      <c r="P144" s="91"/>
-      <c r="Q144" s="91"/>
-      <c r="R144" s="91"/>
-      <c r="S144" s="90"/>
+      <c r="N144" s="85"/>
+      <c r="O144" s="84"/>
+      <c r="P144" s="84"/>
+      <c r="Q144" s="84"/>
+      <c r="R144" s="84"/>
+      <c r="S144" s="86"/>
       <c r="T144" s="45"/>
       <c r="U144" s="45"/>
       <c r="V144" s="45"/>
@@ -61891,7 +61897,7 @@
       <c r="AV144" s="45"/>
       <c r="AW144" s="45"/>
     </row>
-    <row r="145" spans="1:49">
+    <row r="145" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A145" s="45"/>
       <c r="B145" s="34" t="s">
         <v>176</v>
@@ -61968,7 +61974,7 @@
       <c r="AV145" s="45"/>
       <c r="AW145" s="45"/>
     </row>
-    <row r="146" spans="1:49">
+    <row r="146" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A146" s="45"/>
       <c r="B146" s="34" t="s">
         <v>195</v>
@@ -62061,7 +62067,7 @@
       <c r="AV146" s="45"/>
       <c r="AW146" s="45"/>
     </row>
-    <row r="147" spans="1:49">
+    <row r="147" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A147" s="4">
         <v>2020</v>
       </c>
@@ -62158,7 +62164,7 @@
       <c r="AV147" s="45"/>
       <c r="AW147" s="45"/>
     </row>
-    <row r="148" spans="1:49">
+    <row r="148" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A148" s="4">
         <v>2021</v>
       </c>
@@ -62255,7 +62261,7 @@
       <c r="AV148" s="45"/>
       <c r="AW148" s="45"/>
     </row>
-    <row r="149" spans="1:49">
+    <row r="149" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A149" s="4">
         <v>2022</v>
       </c>
@@ -62352,7 +62358,7 @@
       <c r="AV149" s="45"/>
       <c r="AW149" s="45"/>
     </row>
-    <row r="150" spans="1:49">
+    <row r="150" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A150" s="4">
         <v>2023</v>
       </c>
@@ -62449,7 +62455,7 @@
       <c r="AV150" s="45"/>
       <c r="AW150" s="45"/>
     </row>
-    <row r="151" spans="1:49">
+    <row r="151" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A151" s="4">
         <v>2024</v>
       </c>
@@ -62546,7 +62552,7 @@
       <c r="AV151" s="45"/>
       <c r="AW151" s="45"/>
     </row>
-    <row r="152" spans="1:49">
+    <row r="152" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A152" s="4">
         <v>2025</v>
       </c>
@@ -62643,7 +62649,7 @@
       <c r="AV152" s="45"/>
       <c r="AW152" s="45"/>
     </row>
-    <row r="153" spans="1:49">
+    <row r="153" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A153" s="37">
         <v>2026</v>
       </c>
@@ -62742,7 +62748,7 @@
       <c r="AV153" s="45"/>
       <c r="AW153" s="45"/>
     </row>
-    <row r="154" spans="1:49">
+    <row r="154" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A154" s="4">
         <v>2027</v>
       </c>
@@ -62843,7 +62849,7 @@
       <c r="AV154" s="45"/>
       <c r="AW154" s="45"/>
     </row>
-    <row r="155" spans="1:49">
+    <row r="155" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A155" s="4">
         <v>2028</v>
       </c>
@@ -62942,7 +62948,7 @@
       <c r="AV155" s="45"/>
       <c r="AW155" s="45"/>
     </row>
-    <row r="156" spans="1:49">
+    <row r="156" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A156" s="4">
         <v>2029</v>
       </c>
@@ -63041,7 +63047,7 @@
       <c r="AV156" s="45"/>
       <c r="AW156" s="45"/>
     </row>
-    <row r="157" spans="1:49">
+    <row r="157" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A157" s="4">
         <v>2030</v>
       </c>
@@ -63140,7 +63146,7 @@
       <c r="AV157" s="45"/>
       <c r="AW157" s="45"/>
     </row>
-    <row r="158" spans="1:49">
+    <row r="158" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A158" s="4">
         <v>2031</v>
       </c>
@@ -63239,7 +63245,7 @@
       <c r="AV158" s="45"/>
       <c r="AW158" s="45"/>
     </row>
-    <row r="159" spans="1:49">
+    <row r="159" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A159" s="4">
         <v>2032</v>
       </c>
@@ -63338,7 +63344,7 @@
       <c r="AV159" s="45"/>
       <c r="AW159" s="45"/>
     </row>
-    <row r="160" spans="1:49">
+    <row r="160" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A160" s="4">
         <v>2033</v>
       </c>
@@ -63437,7 +63443,7 @@
       <c r="AV160" s="45"/>
       <c r="AW160" s="45"/>
     </row>
-    <row r="161" spans="1:49">
+    <row r="161" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A161" s="4">
         <v>2034</v>
       </c>
@@ -63536,7 +63542,7 @@
       <c r="AV161" s="45"/>
       <c r="AW161" s="45"/>
     </row>
-    <row r="162" spans="1:49">
+    <row r="162" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A162" s="4">
         <v>2035</v>
       </c>
@@ -63635,7 +63641,7 @@
       <c r="AV162" s="45"/>
       <c r="AW162" s="45"/>
     </row>
-    <row r="163" spans="1:49">
+    <row r="163" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A163" s="4">
         <v>2036</v>
       </c>
@@ -63734,7 +63740,7 @@
       <c r="AV163" s="45"/>
       <c r="AW163" s="45"/>
     </row>
-    <row r="164" spans="1:49">
+    <row r="164" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A164" s="4">
         <v>2037</v>
       </c>
@@ -63833,7 +63839,7 @@
       <c r="AV164" s="45"/>
       <c r="AW164" s="45"/>
     </row>
-    <row r="165" spans="1:49">
+    <row r="165" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A165" s="4">
         <v>2038</v>
       </c>
@@ -63932,7 +63938,7 @@
       <c r="AV165" s="45"/>
       <c r="AW165" s="45"/>
     </row>
-    <row r="166" spans="1:49">
+    <row r="166" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A166" s="4">
         <v>2039</v>
       </c>
@@ -64031,7 +64037,7 @@
       <c r="AV166" s="45"/>
       <c r="AW166" s="45"/>
     </row>
-    <row r="167" spans="1:49">
+    <row r="167" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A167" s="4">
         <v>2040</v>
       </c>
@@ -64130,7 +64136,7 @@
       <c r="AV167" s="45"/>
       <c r="AW167" s="45"/>
     </row>
-    <row r="168" spans="1:49">
+    <row r="168" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A168" s="4">
         <v>2041</v>
       </c>
@@ -64229,7 +64235,7 @@
       <c r="AV168" s="45"/>
       <c r="AW168" s="45"/>
     </row>
-    <row r="169" spans="1:49">
+    <row r="169" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A169" s="4">
         <v>2042</v>
       </c>
@@ -64328,7 +64334,7 @@
       <c r="AV169" s="45"/>
       <c r="AW169" s="45"/>
     </row>
-    <row r="170" spans="1:49">
+    <row r="170" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A170" s="4">
         <v>2043</v>
       </c>
@@ -64427,7 +64433,7 @@
       <c r="AV170" s="45"/>
       <c r="AW170" s="45"/>
     </row>
-    <row r="171" spans="1:49">
+    <row r="171" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A171" s="4">
         <v>2044</v>
       </c>
@@ -64526,7 +64532,7 @@
       <c r="AV171" s="45"/>
       <c r="AW171" s="45"/>
     </row>
-    <row r="172" spans="1:49">
+    <row r="172" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A172" s="4">
         <v>2045</v>
       </c>
@@ -64625,7 +64631,7 @@
       <c r="AV172" s="45"/>
       <c r="AW172" s="45"/>
     </row>
-    <row r="173" spans="1:49">
+    <row r="173" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A173" s="4">
         <v>2046</v>
       </c>
@@ -64728,7 +64734,7 @@
       <c r="AV173" s="45"/>
       <c r="AW173" s="45"/>
     </row>
-    <row r="174" spans="1:49">
+    <row r="174" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A174" s="4">
         <v>2047</v>
       </c>
@@ -64827,7 +64833,7 @@
       <c r="AV174" s="45"/>
       <c r="AW174" s="45"/>
     </row>
-    <row r="175" spans="1:49">
+    <row r="175" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A175" s="4">
         <v>2048</v>
       </c>
@@ -64926,7 +64932,7 @@
       <c r="AV175" s="45"/>
       <c r="AW175" s="45"/>
     </row>
-    <row r="176" spans="1:49">
+    <row r="176" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A176" s="4">
         <v>2049</v>
       </c>
@@ -65025,7 +65031,7 @@
       <c r="AV176" s="45"/>
       <c r="AW176" s="45"/>
     </row>
-    <row r="177" spans="1:49">
+    <row r="177" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A177" s="4">
         <v>2050</v>
       </c>
@@ -65124,7 +65130,7 @@
       <c r="AV177" s="45"/>
       <c r="AW177" s="45"/>
     </row>
-    <row r="178" spans="1:49">
+    <row r="178" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A178" s="4">
         <v>2051</v>
       </c>
@@ -65219,7 +65225,7 @@
       <c r="AV178" s="45"/>
       <c r="AW178" s="45"/>
     </row>
-    <row r="179" spans="1:49">
+    <row r="179" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A179" s="4">
         <v>2052</v>
       </c>
@@ -65314,7 +65320,7 @@
       <c r="AV179" s="45"/>
       <c r="AW179" s="45"/>
     </row>
-    <row r="180" spans="1:49">
+    <row r="180" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A180" s="4">
         <v>2053</v>
       </c>
@@ -65409,7 +65415,7 @@
       <c r="AV180" s="45"/>
       <c r="AW180" s="45"/>
     </row>
-    <row r="181" spans="1:49">
+    <row r="181" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A181" s="4">
         <v>2054</v>
       </c>
@@ -65504,7 +65510,7 @@
       <c r="AV181" s="45"/>
       <c r="AW181" s="45"/>
     </row>
-    <row r="182" spans="1:49">
+    <row r="182" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A182" s="4">
         <v>2055</v>
       </c>
@@ -65599,7 +65605,7 @@
       <c r="AV182" s="45"/>
       <c r="AW182" s="45"/>
     </row>
-    <row r="183" spans="1:49">
+    <row r="183" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A183" s="4">
         <v>2056</v>
       </c>
@@ -65694,7 +65700,7 @@
       <c r="AV183" s="45"/>
       <c r="AW183" s="45"/>
     </row>
-    <row r="184" spans="1:49">
+    <row r="184" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A184" s="4">
         <v>2057</v>
       </c>
@@ -65789,7 +65795,7 @@
       <c r="AV184" s="45"/>
       <c r="AW184" s="45"/>
     </row>
-    <row r="185" spans="1:49">
+    <row r="185" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A185" s="4">
         <v>2058</v>
       </c>
@@ -65884,7 +65890,7 @@
       <c r="AV185" s="45"/>
       <c r="AW185" s="45"/>
     </row>
-    <row r="186" spans="1:49">
+    <row r="186" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A186" s="4">
         <v>2059</v>
       </c>
@@ -65979,7 +65985,7 @@
       <c r="AV186" s="45"/>
       <c r="AW186" s="45"/>
     </row>
-    <row r="187" spans="1:49">
+    <row r="187" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
         <v>2060</v>
       </c>
@@ -66074,7 +66080,7 @@
       <c r="AV187" s="45"/>
       <c r="AW187" s="45"/>
     </row>
-    <row r="188" spans="1:49">
+    <row r="188" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A188" s="4">
         <v>2061</v>
       </c>
@@ -66169,7 +66175,7 @@
       <c r="AV188" s="45"/>
       <c r="AW188" s="45"/>
     </row>
-    <row r="189" spans="1:49">
+    <row r="189" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A189" s="4">
         <v>2062</v>
       </c>
@@ -66264,7 +66270,7 @@
       <c r="AV189" s="45"/>
       <c r="AW189" s="45"/>
     </row>
-    <row r="190" spans="1:49">
+    <row r="190" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A190" s="4">
         <v>2063</v>
       </c>
@@ -66359,7 +66365,7 @@
       <c r="AV190" s="45"/>
       <c r="AW190" s="45"/>
     </row>
-    <row r="191" spans="1:49">
+    <row r="191" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A191" s="4">
         <v>2064</v>
       </c>
@@ -66454,7 +66460,7 @@
       <c r="AV191" s="45"/>
       <c r="AW191" s="45"/>
     </row>
-    <row r="192" spans="1:49">
+    <row r="192" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A192" s="4">
         <v>2065</v>
       </c>
@@ -66549,7 +66555,7 @@
       <c r="AV192" s="45"/>
       <c r="AW192" s="45"/>
     </row>
-    <row r="193" spans="1:49">
+    <row r="193" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A193" s="4">
         <v>2066</v>
       </c>
@@ -66644,7 +66650,7 @@
       <c r="AV193" s="45"/>
       <c r="AW193" s="45"/>
     </row>
-    <row r="194" spans="1:49">
+    <row r="194" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A194" s="4">
         <v>2067</v>
       </c>
@@ -66739,7 +66745,7 @@
       <c r="AV194" s="45"/>
       <c r="AW194" s="45"/>
     </row>
-    <row r="195" spans="1:49">
+    <row r="195" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A195" s="4">
         <v>2068</v>
       </c>
@@ -66834,7 +66840,7 @@
       <c r="AV195" s="45"/>
       <c r="AW195" s="45"/>
     </row>
-    <row r="196" spans="1:49">
+    <row r="196" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A196" s="4">
         <v>2069</v>
       </c>
@@ -66929,7 +66935,7 @@
       <c r="AV196" s="45"/>
       <c r="AW196" s="45"/>
     </row>
-    <row r="197" spans="1:49">
+    <row r="197" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A197" s="4">
         <v>2070</v>
       </c>
@@ -67024,7 +67030,7 @@
       <c r="AV197" s="45"/>
       <c r="AW197" s="45"/>
     </row>
-    <row r="198" spans="1:49">
+    <row r="198" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A198" s="4">
         <v>2071</v>
       </c>
@@ -67119,7 +67125,7 @@
       <c r="AV198" s="45"/>
       <c r="AW198" s="45"/>
     </row>
-    <row r="199" spans="1:49">
+    <row r="199" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A199" s="4">
         <v>2072</v>
       </c>
@@ -67214,7 +67220,7 @@
       <c r="AV199" s="45"/>
       <c r="AW199" s="45"/>
     </row>
-    <row r="200" spans="1:49">
+    <row r="200" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A200" s="4">
         <v>2073</v>
       </c>
@@ -67309,7 +67315,7 @@
       <c r="AV200" s="45"/>
       <c r="AW200" s="45"/>
     </row>
-    <row r="201" spans="1:49">
+    <row r="201" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A201" s="4">
         <v>2074</v>
       </c>
@@ -67404,7 +67410,7 @@
       <c r="AV201" s="45"/>
       <c r="AW201" s="45"/>
     </row>
-    <row r="202" spans="1:49">
+    <row r="202" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A202" s="4">
         <v>2075</v>
       </c>
@@ -67499,7 +67505,7 @@
       <c r="AV202" s="45"/>
       <c r="AW202" s="45"/>
     </row>
-    <row r="203" spans="1:49">
+    <row r="203" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A203" s="45"/>
       <c r="B203" s="45"/>
       <c r="C203" s="45"/>
@@ -67550,7 +67556,7 @@
       <c r="AV203" s="45"/>
       <c r="AW203" s="45"/>
     </row>
-    <row r="204" spans="1:49">
+    <row r="204" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A204" s="45"/>
       <c r="B204" s="45"/>
       <c r="C204" s="45"/>
@@ -67621,7 +67627,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="205" spans="1:49">
+    <row r="205" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A205" s="76" t="s">
         <v>176</v>
       </c>
@@ -67750,7 +67756,7 @@
       <c r="AV205" s="45"/>
       <c r="AW205" s="45"/>
     </row>
-    <row r="206" spans="1:49">
+    <row r="206" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A206" s="45"/>
       <c r="B206" s="45"/>
       <c r="C206" s="45"/>
@@ -67801,7 +67807,7 @@
       <c r="AV206" s="45"/>
       <c r="AW206" s="45"/>
     </row>
-    <row r="207" spans="1:49">
+    <row r="207" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A207" s="45"/>
       <c r="B207" s="49" t="s">
         <v>274</v>
@@ -67922,7 +67928,7 @@
       <c r="AV207" s="45"/>
       <c r="AW207" s="45"/>
     </row>
-    <row r="208" spans="1:49">
+    <row r="208" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A208" s="45"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -67973,7 +67979,7 @@
       <c r="AV208" s="45"/>
       <c r="AW208" s="45"/>
     </row>
-    <row r="209" spans="1:49">
+    <row r="209" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A209" s="45"/>
       <c r="B209" s="6" t="s">
         <v>176</v>
@@ -68054,24 +68060,24 @@
       <c r="AV209" s="45"/>
       <c r="AW209" s="45"/>
     </row>
-    <row r="210" spans="1:49">
+    <row r="210" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A210" s="45"/>
-      <c r="B210" s="88" t="s">
+      <c r="B210" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="C210" s="91" t="s">
+      <c r="C210" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="D210" s="91" t="s">
+      <c r="D210" s="84" t="s">
         <v>183</v>
       </c>
-      <c r="E210" s="91" t="s">
+      <c r="E210" s="84" t="s">
         <v>184</v>
       </c>
-      <c r="F210" s="91" t="s">
+      <c r="F210" s="84" t="s">
         <v>241</v>
       </c>
-      <c r="G210" s="90" t="s">
+      <c r="G210" s="86" t="s">
         <v>242</v>
       </c>
       <c r="H210" s="45"/>
@@ -68080,12 +68086,12 @@
       <c r="K210" s="45"/>
       <c r="L210" s="45"/>
       <c r="M210" s="45"/>
-      <c r="N210" s="91"/>
-      <c r="O210" s="91"/>
-      <c r="P210" s="91"/>
-      <c r="Q210" s="91"/>
-      <c r="R210" s="91"/>
-      <c r="S210" s="91"/>
+      <c r="N210" s="84"/>
+      <c r="O210" s="84"/>
+      <c r="P210" s="84"/>
+      <c r="Q210" s="84"/>
+      <c r="R210" s="84"/>
+      <c r="S210" s="84"/>
       <c r="T210" s="45"/>
       <c r="U210" s="45"/>
       <c r="V210" s="45"/>
@@ -68135,26 +68141,26 @@
       <c r="AV210" s="45"/>
       <c r="AW210" s="45"/>
     </row>
-    <row r="211" spans="1:49">
+    <row r="211" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A211" s="45"/>
-      <c r="B211" s="88"/>
-      <c r="C211" s="91"/>
-      <c r="D211" s="91"/>
-      <c r="E211" s="91"/>
-      <c r="F211" s="91"/>
-      <c r="G211" s="90"/>
+      <c r="B211" s="85"/>
+      <c r="C211" s="84"/>
+      <c r="D211" s="84"/>
+      <c r="E211" s="84"/>
+      <c r="F211" s="84"/>
+      <c r="G211" s="86"/>
       <c r="H211" s="45"/>
       <c r="I211" s="45"/>
       <c r="J211" s="45"/>
       <c r="K211" s="45"/>
       <c r="L211" s="45"/>
       <c r="M211" s="45"/>
-      <c r="N211" s="91"/>
-      <c r="O211" s="91"/>
-      <c r="P211" s="91"/>
-      <c r="Q211" s="91"/>
-      <c r="R211" s="91"/>
-      <c r="S211" s="91"/>
+      <c r="N211" s="84"/>
+      <c r="O211" s="84"/>
+      <c r="P211" s="84"/>
+      <c r="Q211" s="84"/>
+      <c r="R211" s="84"/>
+      <c r="S211" s="84"/>
       <c r="T211" s="45"/>
       <c r="U211" s="45"/>
       <c r="V211" s="45"/>
@@ -68186,7 +68192,7 @@
       <c r="AV211" s="45"/>
       <c r="AW211" s="45"/>
     </row>
-    <row r="212" spans="1:49">
+    <row r="212" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A212" s="45"/>
       <c r="B212" s="34" t="s">
         <v>176</v>
@@ -68259,7 +68265,7 @@
       <c r="AV212" s="45"/>
       <c r="AW212" s="45"/>
     </row>
-    <row r="213" spans="1:49">
+    <row r="213" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A213" s="45"/>
       <c r="B213" s="34" t="s">
         <v>195</v>
@@ -68340,7 +68346,7 @@
       <c r="AV213" s="45"/>
       <c r="AW213" s="45"/>
     </row>
-    <row r="214" spans="1:49">
+    <row r="214" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A214" s="4">
         <v>2020</v>
       </c>
@@ -68423,7 +68429,7 @@
       <c r="AV214" s="45"/>
       <c r="AW214" s="45"/>
     </row>
-    <row r="215" spans="1:49">
+    <row r="215" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A215" s="4">
         <v>2021</v>
       </c>
@@ -68506,7 +68512,7 @@
       <c r="AV215" s="45"/>
       <c r="AW215" s="45"/>
     </row>
-    <row r="216" spans="1:49">
+    <row r="216" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A216" s="4">
         <v>2022</v>
       </c>
@@ -68589,7 +68595,7 @@
       <c r="AV216" s="45"/>
       <c r="AW216" s="45"/>
     </row>
-    <row r="217" spans="1:49">
+    <row r="217" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A217" s="4">
         <v>2023</v>
       </c>
@@ -68672,7 +68678,7 @@
       <c r="AV217" s="45"/>
       <c r="AW217" s="45"/>
     </row>
-    <row r="218" spans="1:49">
+    <row r="218" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A218" s="4">
         <v>2024</v>
       </c>
@@ -68755,7 +68761,7 @@
       <c r="AV218" s="45"/>
       <c r="AW218" s="45"/>
     </row>
-    <row r="219" spans="1:49">
+    <row r="219" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A219" s="4">
         <v>2025</v>
       </c>
@@ -68838,7 +68844,7 @@
       <c r="AV219" s="45"/>
       <c r="AW219" s="45"/>
     </row>
-    <row r="220" spans="1:49">
+    <row r="220" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A220" s="37">
         <v>2026</v>
       </c>
@@ -68921,7 +68927,7 @@
       <c r="AV220" s="45"/>
       <c r="AW220" s="45"/>
     </row>
-    <row r="221" spans="1:49">
+    <row r="221" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
         <v>2027</v>
       </c>
@@ -69004,7 +69010,7 @@
       <c r="AV221" s="45"/>
       <c r="AW221" s="45"/>
     </row>
-    <row r="222" spans="1:49">
+    <row r="222" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A222" s="4">
         <v>2028</v>
       </c>
@@ -69087,7 +69093,7 @@
       <c r="AV222" s="45"/>
       <c r="AW222" s="45"/>
     </row>
-    <row r="223" spans="1:49">
+    <row r="223" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A223" s="4">
         <v>2029</v>
       </c>
@@ -69170,7 +69176,7 @@
       <c r="AV223" s="45"/>
       <c r="AW223" s="45"/>
     </row>
-    <row r="224" spans="1:49">
+    <row r="224" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A224" s="4">
         <v>2030</v>
       </c>
@@ -69253,7 +69259,7 @@
       <c r="AV224" s="45"/>
       <c r="AW224" s="45"/>
     </row>
-    <row r="225" spans="1:49">
+    <row r="225" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A225" s="4">
         <v>2031</v>
       </c>
@@ -69336,7 +69342,7 @@
       <c r="AV225" s="45"/>
       <c r="AW225" s="45"/>
     </row>
-    <row r="226" spans="1:49">
+    <row r="226" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A226" s="4">
         <v>2032</v>
       </c>
@@ -69419,7 +69425,7 @@
       <c r="AV226" s="45"/>
       <c r="AW226" s="45"/>
     </row>
-    <row r="227" spans="1:49">
+    <row r="227" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A227" s="4">
         <v>2033</v>
       </c>
@@ -69502,7 +69508,7 @@
       <c r="AV227" s="45"/>
       <c r="AW227" s="45"/>
     </row>
-    <row r="228" spans="1:49">
+    <row r="228" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A228" s="4">
         <v>2034</v>
       </c>
@@ -69585,7 +69591,7 @@
       <c r="AV228" s="45"/>
       <c r="AW228" s="45"/>
     </row>
-    <row r="229" spans="1:49">
+    <row r="229" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A229" s="4">
         <v>2035</v>
       </c>
@@ -69668,7 +69674,7 @@
       <c r="AV229" s="45"/>
       <c r="AW229" s="45"/>
     </row>
-    <row r="230" spans="1:49">
+    <row r="230" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A230" s="4">
         <v>2036</v>
       </c>
@@ -69751,7 +69757,7 @@
       <c r="AV230" s="45"/>
       <c r="AW230" s="45"/>
     </row>
-    <row r="231" spans="1:49">
+    <row r="231" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A231" s="4">
         <v>2037</v>
       </c>
@@ -69834,7 +69840,7 @@
       <c r="AV231" s="45"/>
       <c r="AW231" s="45"/>
     </row>
-    <row r="232" spans="1:49">
+    <row r="232" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A232" s="4">
         <v>2038</v>
       </c>
@@ -69917,7 +69923,7 @@
       <c r="AV232" s="45"/>
       <c r="AW232" s="45"/>
     </row>
-    <row r="233" spans="1:49">
+    <row r="233" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A233" s="4">
         <v>2039</v>
       </c>
@@ -70000,7 +70006,7 @@
       <c r="AV233" s="45"/>
       <c r="AW233" s="45"/>
     </row>
-    <row r="234" spans="1:49">
+    <row r="234" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A234" s="4">
         <v>2040</v>
       </c>
@@ -70083,7 +70089,7 @@
       <c r="AV234" s="45"/>
       <c r="AW234" s="45"/>
     </row>
-    <row r="235" spans="1:49">
+    <row r="235" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A235" s="4">
         <v>2041</v>
       </c>
@@ -70166,7 +70172,7 @@
       <c r="AV235" s="45"/>
       <c r="AW235" s="45"/>
     </row>
-    <row r="236" spans="1:49">
+    <row r="236" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A236" s="4">
         <v>2042</v>
       </c>
@@ -70249,7 +70255,7 @@
       <c r="AV236" s="45"/>
       <c r="AW236" s="45"/>
     </row>
-    <row r="237" spans="1:49">
+    <row r="237" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A237" s="4">
         <v>2043</v>
       </c>
@@ -70332,7 +70338,7 @@
       <c r="AV237" s="45"/>
       <c r="AW237" s="45"/>
     </row>
-    <row r="238" spans="1:49">
+    <row r="238" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A238" s="4">
         <v>2044</v>
       </c>
@@ -70415,7 +70421,7 @@
       <c r="AV238" s="45"/>
       <c r="AW238" s="45"/>
     </row>
-    <row r="239" spans="1:49">
+    <row r="239" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A239" s="4">
         <v>2045</v>
       </c>
@@ -70498,7 +70504,7 @@
       <c r="AV239" s="45"/>
       <c r="AW239" s="45"/>
     </row>
-    <row r="240" spans="1:49">
+    <row r="240" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A240" s="4">
         <v>2046</v>
       </c>
@@ -70581,7 +70587,7 @@
       <c r="AV240" s="45"/>
       <c r="AW240" s="45"/>
     </row>
-    <row r="241" spans="1:49">
+    <row r="241" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A241" s="4">
         <v>2047</v>
       </c>
@@ -70664,7 +70670,7 @@
       <c r="AV241" s="45"/>
       <c r="AW241" s="45"/>
     </row>
-    <row r="242" spans="1:49">
+    <row r="242" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A242" s="4">
         <v>2048</v>
       </c>
@@ -70747,7 +70753,7 @@
       <c r="AV242" s="45"/>
       <c r="AW242" s="45"/>
     </row>
-    <row r="243" spans="1:49">
+    <row r="243" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A243" s="4">
         <v>2049</v>
       </c>
@@ -70830,7 +70836,7 @@
       <c r="AV243" s="45"/>
       <c r="AW243" s="45"/>
     </row>
-    <row r="244" spans="1:49">
+    <row r="244" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A244" s="4">
         <v>2050</v>
       </c>
@@ -70913,7 +70919,7 @@
       <c r="AV244" s="45"/>
       <c r="AW244" s="45"/>
     </row>
-    <row r="245" spans="1:49">
+    <row r="245" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A245" s="4">
         <v>2051</v>
       </c>
@@ -70996,7 +71002,7 @@
       <c r="AV245" s="45"/>
       <c r="AW245" s="45"/>
     </row>
-    <row r="246" spans="1:49">
+    <row r="246" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A246" s="4">
         <v>2052</v>
       </c>
@@ -71079,7 +71085,7 @@
       <c r="AV246" s="45"/>
       <c r="AW246" s="45"/>
     </row>
-    <row r="247" spans="1:49">
+    <row r="247" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A247" s="4">
         <v>2053</v>
       </c>
@@ -71162,7 +71168,7 @@
       <c r="AV247" s="45"/>
       <c r="AW247" s="45"/>
     </row>
-    <row r="248" spans="1:49">
+    <row r="248" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A248" s="4">
         <v>2054</v>
       </c>
@@ -71245,7 +71251,7 @@
       <c r="AV248" s="45"/>
       <c r="AW248" s="45"/>
     </row>
-    <row r="249" spans="1:49">
+    <row r="249" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A249" s="4">
         <v>2055</v>
       </c>
@@ -71328,7 +71334,7 @@
       <c r="AV249" s="45"/>
       <c r="AW249" s="45"/>
     </row>
-    <row r="250" spans="1:49">
+    <row r="250" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
         <v>2056</v>
       </c>
@@ -71411,7 +71417,7 @@
       <c r="AV250" s="45"/>
       <c r="AW250" s="45"/>
     </row>
-    <row r="251" spans="1:49">
+    <row r="251" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A251" s="4">
         <v>2057</v>
       </c>
@@ -71494,7 +71500,7 @@
       <c r="AV251" s="45"/>
       <c r="AW251" s="45"/>
     </row>
-    <row r="252" spans="1:49">
+    <row r="252" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A252" s="4">
         <v>2058</v>
       </c>
@@ -71577,7 +71583,7 @@
       <c r="AV252" s="45"/>
       <c r="AW252" s="45"/>
     </row>
-    <row r="253" spans="1:49">
+    <row r="253" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A253" s="4">
         <v>2059</v>
       </c>
@@ -71660,7 +71666,7 @@
       <c r="AV253" s="45"/>
       <c r="AW253" s="45"/>
     </row>
-    <row r="254" spans="1:49">
+    <row r="254" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A254" s="4">
         <v>2060</v>
       </c>
@@ -71743,7 +71749,7 @@
       <c r="AV254" s="45"/>
       <c r="AW254" s="45"/>
     </row>
-    <row r="255" spans="1:49">
+    <row r="255" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A255" s="4">
         <v>2061</v>
       </c>
@@ -71826,7 +71832,7 @@
       <c r="AV255" s="45"/>
       <c r="AW255" s="45"/>
     </row>
-    <row r="256" spans="1:49">
+    <row r="256" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A256" s="4">
         <v>2062</v>
       </c>
@@ -71909,7 +71915,7 @@
       <c r="AV256" s="45"/>
       <c r="AW256" s="45"/>
     </row>
-    <row r="257" spans="1:49">
+    <row r="257" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A257" s="4">
         <v>2063</v>
       </c>
@@ -71992,7 +71998,7 @@
       <c r="AV257" s="45"/>
       <c r="AW257" s="45"/>
     </row>
-    <row r="258" spans="1:49">
+    <row r="258" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A258" s="4">
         <v>2064</v>
       </c>
@@ -72075,7 +72081,7 @@
       <c r="AV258" s="45"/>
       <c r="AW258" s="45"/>
     </row>
-    <row r="259" spans="1:49">
+    <row r="259" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A259" s="4">
         <v>2065</v>
       </c>
@@ -72158,7 +72164,7 @@
       <c r="AV259" s="45"/>
       <c r="AW259" s="45"/>
     </row>
-    <row r="260" spans="1:49">
+    <row r="260" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A260" s="4">
         <v>2066</v>
       </c>
@@ -72241,7 +72247,7 @@
       <c r="AV260" s="45"/>
       <c r="AW260" s="45"/>
     </row>
-    <row r="261" spans="1:49">
+    <row r="261" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A261" s="4">
         <v>2067</v>
       </c>
@@ -72324,7 +72330,7 @@
       <c r="AV261" s="45"/>
       <c r="AW261" s="45"/>
     </row>
-    <row r="262" spans="1:49">
+    <row r="262" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A262" s="4">
         <v>2068</v>
       </c>
@@ -72407,7 +72413,7 @@
       <c r="AV262" s="45"/>
       <c r="AW262" s="45"/>
     </row>
-    <row r="263" spans="1:49">
+    <row r="263" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A263" s="4">
         <v>2069</v>
       </c>
@@ -72490,7 +72496,7 @@
       <c r="AV263" s="45"/>
       <c r="AW263" s="45"/>
     </row>
-    <row r="264" spans="1:49">
+    <row r="264" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A264" s="4">
         <v>2070</v>
       </c>
@@ -72573,7 +72579,7 @@
       <c r="AV264" s="45"/>
       <c r="AW264" s="45"/>
     </row>
-    <row r="265" spans="1:49">
+    <row r="265" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A265" s="4">
         <v>2071</v>
       </c>
@@ -72656,7 +72662,7 @@
       <c r="AV265" s="45"/>
       <c r="AW265" s="45"/>
     </row>
-    <row r="266" spans="1:49">
+    <row r="266" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A266" s="4">
         <v>2072</v>
       </c>
@@ -72739,7 +72745,7 @@
       <c r="AV266" s="45"/>
       <c r="AW266" s="45"/>
     </row>
-    <row r="267" spans="1:49">
+    <row r="267" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A267" s="4">
         <v>2073</v>
       </c>
@@ -72822,7 +72828,7 @@
       <c r="AV267" s="45"/>
       <c r="AW267" s="45"/>
     </row>
-    <row r="268" spans="1:49">
+    <row r="268" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A268" s="4">
         <v>2074</v>
       </c>
@@ -72905,7 +72911,7 @@
       <c r="AV268" s="45"/>
       <c r="AW268" s="45"/>
     </row>
-    <row r="269" spans="1:49">
+    <row r="269" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A269" s="4">
         <v>2075</v>
       </c>
@@ -72990,33 +72996,16 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="S210:S211"/>
-    <mergeCell ref="G210:G211"/>
-    <mergeCell ref="N210:N211"/>
-    <mergeCell ref="O210:O211"/>
-    <mergeCell ref="P210:P211"/>
-    <mergeCell ref="Q210:Q211"/>
-    <mergeCell ref="R210:R211"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="C210:C211"/>
-    <mergeCell ref="D210:D211"/>
-    <mergeCell ref="E210:E211"/>
-    <mergeCell ref="F210:F211"/>
-    <mergeCell ref="Q79:Q80"/>
-    <mergeCell ref="R79:R80"/>
-    <mergeCell ref="S79:S80"/>
-    <mergeCell ref="B143:B144"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="D143:D144"/>
-    <mergeCell ref="E143:E144"/>
-    <mergeCell ref="F143:F144"/>
-    <mergeCell ref="G143:G144"/>
-    <mergeCell ref="N143:N144"/>
-    <mergeCell ref="O143:O144"/>
-    <mergeCell ref="P143:P144"/>
-    <mergeCell ref="Q143:Q144"/>
-    <mergeCell ref="R143:R144"/>
-    <mergeCell ref="S143:S144"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
     <mergeCell ref="AN16:AV16"/>
     <mergeCell ref="B79:B80"/>
     <mergeCell ref="C79:C80"/>
@@ -73033,16 +73022,33 @@
     <mergeCell ref="Q15:Q16"/>
     <mergeCell ref="R15:R16"/>
     <mergeCell ref="S15:S16"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="Q79:Q80"/>
+    <mergeCell ref="R79:R80"/>
+    <mergeCell ref="S79:S80"/>
+    <mergeCell ref="B143:B144"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="D143:D144"/>
+    <mergeCell ref="E143:E144"/>
+    <mergeCell ref="F143:F144"/>
+    <mergeCell ref="G143:G144"/>
+    <mergeCell ref="N143:N144"/>
+    <mergeCell ref="O143:O144"/>
+    <mergeCell ref="P143:P144"/>
+    <mergeCell ref="Q143:Q144"/>
+    <mergeCell ref="R143:R144"/>
+    <mergeCell ref="S143:S144"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="C210:C211"/>
+    <mergeCell ref="D210:D211"/>
+    <mergeCell ref="E210:E211"/>
+    <mergeCell ref="F210:F211"/>
+    <mergeCell ref="S210:S211"/>
+    <mergeCell ref="G210:G211"/>
+    <mergeCell ref="N210:N211"/>
+    <mergeCell ref="O210:O211"/>
+    <mergeCell ref="P210:P211"/>
+    <mergeCell ref="Q210:Q211"/>
+    <mergeCell ref="R210:R211"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="AI9" r:id="rId1" xr:uid="{0EFC2903-8744-43F2-8734-37B079A97BEB}"/>
@@ -73058,9 +73064,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -73208,22 +73217,42 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA33BABD-0214-41C1-A4CB-B37DFD159383}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{852A521B-1A83-4FBC-BB58-E0656534973A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42776E0B-7D19-408E-95F1-92695F3BD421}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42776E0B-7D19-408E-95F1-92695F3BD421}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79a1cdf2-2d4f-42d7-aee4-ff0e208e0f4a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{852A521B-1A83-4FBC-BB58-E0656534973A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA33BABD-0214-41C1-A4CB-B37DFD159383}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>